--- a/tool/track-aggregator/template/年度比較結果.xlsx
+++ b/tool/track-aggregator/template/年度比較結果.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ishid\Desktop\project_management\tool\track-aggregator\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74C4FF62-9ADA-4650-A6AD-2AD120604AF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24134632-FFFF-4673-AF70-0ED7AEF7ABF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1038,7 +1038,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="53">
+  <borders count="61">
     <border>
       <left/>
       <right/>
@@ -1631,16 +1631,40 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
+      <left/>
       <right style="thin">
         <color indexed="64"/>
       </right>
       <top style="thin">
         <color indexed="64"/>
       </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
       <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -1649,13 +1673,82 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="medium">
+      <right style="thin">
         <color indexed="64"/>
       </right>
       <top style="thin">
         <color indexed="64"/>
       </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
       <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -1665,10 +1758,10 @@
       <right style="thin">
         <color indexed="64"/>
       </right>
-      <top style="medium">
+      <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom style="thin">
+      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -1678,21 +1771,8 @@
       <right style="thin">
         <color indexed="64"/>
       </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
+      <top/>
+      <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -1701,13 +1781,43 @@
       <left style="medium">
         <color indexed="64"/>
       </left>
-      <right/>
-      <top style="thin">
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
         <color indexed="64"/>
       </top>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
@@ -1723,7 +1833,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="173">
+  <cellXfs count="172">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2015,21 +2125,6 @@
     <xf numFmtId="0" fontId="10" fillId="8" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="10" fillId="9" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="179" fontId="12" fillId="6" borderId="41" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2078,170 +2173,182 @@
     <xf numFmtId="0" fontId="10" fillId="7" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" textRotation="255"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="15" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="12" fillId="6" borderId="43" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="11" fillId="0" borderId="45" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="11" fillId="0" borderId="47" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="11" fillId="0" borderId="13" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="11" fillId="0" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="48" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="16" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="27" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="30" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="32" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="15" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
-    <xf numFmtId="179" fontId="11" fillId="6" borderId="41" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="23" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="15" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="12" fillId="6" borderId="43" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="11" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="11" fillId="3" borderId="47" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="11" fillId="3" borderId="48" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="11" fillId="0" borderId="45" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="11" fillId="0" borderId="46" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="15" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="21" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="19" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="40" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="18" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="23" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="39" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="22" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="5" fillId="3" borderId="38" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="5" fillId="3" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="5" fillId="3" borderId="37" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="5" fillId="8" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="5" fillId="8" borderId="21" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="5" fillId="8" borderId="20" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="11" fillId="0" borderId="49" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="11" fillId="3" borderId="13" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="11" fillId="0" borderId="50" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="11" fillId="0" borderId="13" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="11" fillId="0" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="51" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="179" fontId="11" fillId="0" borderId="51" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="11" fillId="0" borderId="52" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="16" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="10" fillId="9" borderId="53" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="10" fillId="9" borderId="54" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="55" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="56" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="8" borderId="50" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="52" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="10" fillId="9" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="55" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="11" fillId="0" borderId="57" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="59" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="11" fillId="3" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="11" fillId="3" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="11" fillId="6" borderId="44" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="11" fillId="6" borderId="42" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="27" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="30" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="32" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="11" fillId="0" borderId="58" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="11" fillId="0" borderId="46" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="60" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="11" fillId="0" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="11" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="49" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="16" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="15" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="15" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="21" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="19" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="40" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="18" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="23" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="39" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="22" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="5" fillId="3" borderId="38" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="5" fillId="3" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="5" fillId="3" borderId="37" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="5" fillId="8" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="5" fillId="8" borderId="21" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="5" fillId="8" borderId="20" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="179" fontId="12" fillId="6" borderId="44" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="12" fillId="6" borderId="41" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="12" fillId="6" borderId="42" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -2707,152 +2814,152 @@
       </c>
     </row>
     <row r="2" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B2" s="112" t="s">
+      <c r="B2" s="107" t="s">
         <v>53</v>
       </c>
-      <c r="C2" s="113"/>
-      <c r="D2" s="112" t="s">
+      <c r="C2" s="108"/>
+      <c r="D2" s="107" t="s">
         <v>54</v>
       </c>
-      <c r="E2" s="105" t="s">
+      <c r="E2" s="100" t="s">
         <v>55</v>
       </c>
-      <c r="F2" s="106"/>
-      <c r="G2" s="107"/>
-      <c r="H2" s="108" t="s">
+      <c r="F2" s="101"/>
+      <c r="G2" s="102"/>
+      <c r="H2" s="103" t="s">
         <v>56</v>
       </c>
-      <c r="I2" s="108"/>
-      <c r="J2" s="108"/>
-      <c r="K2" s="108"/>
-      <c r="L2" s="108"/>
-      <c r="M2" s="108"/>
-      <c r="N2" s="108"/>
-      <c r="O2" s="108"/>
-      <c r="P2" s="108"/>
-      <c r="Q2" s="109"/>
+      <c r="I2" s="103"/>
+      <c r="J2" s="103"/>
+      <c r="K2" s="103"/>
+      <c r="L2" s="103"/>
+      <c r="M2" s="103"/>
+      <c r="N2" s="103"/>
+      <c r="O2" s="103"/>
+      <c r="P2" s="103"/>
+      <c r="Q2" s="104"/>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.45">
-      <c r="B3" s="114"/>
-      <c r="C3" s="115"/>
-      <c r="D3" s="114"/>
-      <c r="E3" s="138" t="s">
+      <c r="B3" s="109"/>
+      <c r="C3" s="110"/>
+      <c r="D3" s="109"/>
+      <c r="E3" s="118" t="s">
         <v>96</v>
       </c>
-      <c r="F3" s="110"/>
-      <c r="G3" s="111"/>
-      <c r="H3" s="101"/>
-      <c r="I3" s="101"/>
-      <c r="J3" s="101"/>
-      <c r="K3" s="101"/>
-      <c r="L3" s="101"/>
-      <c r="M3" s="101"/>
-      <c r="N3" s="101"/>
-      <c r="O3" s="101"/>
-      <c r="P3" s="101"/>
+      <c r="F3" s="105"/>
+      <c r="G3" s="106"/>
+      <c r="H3" s="150"/>
+      <c r="I3" s="150"/>
+      <c r="J3" s="150"/>
+      <c r="K3" s="150"/>
+      <c r="L3" s="150"/>
+      <c r="M3" s="150"/>
+      <c r="N3" s="150"/>
+      <c r="O3" s="150"/>
+      <c r="P3" s="150"/>
       <c r="Q3" s="96"/>
     </row>
     <row r="4" spans="1:19" ht="36.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B4" s="116"/>
-      <c r="C4" s="115"/>
-      <c r="D4" s="114"/>
-      <c r="E4" s="139" t="s">
+      <c r="B4" s="111"/>
+      <c r="C4" s="154"/>
+      <c r="D4" s="111"/>
+      <c r="E4" s="155" t="s">
         <v>140</v>
       </c>
-      <c r="F4" s="97" t="s">
+      <c r="F4" s="156" t="s">
         <v>147</v>
       </c>
-      <c r="G4" s="98" t="s">
+      <c r="G4" s="157" t="s">
         <v>57</v>
       </c>
-      <c r="H4" s="137" t="s">
+      <c r="H4" s="158" t="s">
         <v>58</v>
       </c>
-      <c r="I4" s="99" t="s">
+      <c r="I4" s="159" t="s">
         <v>59</v>
       </c>
-      <c r="J4" s="99" t="s">
+      <c r="J4" s="159" t="s">
         <v>60</v>
       </c>
-      <c r="K4" s="99" t="s">
+      <c r="K4" s="159" t="s">
         <v>139</v>
       </c>
-      <c r="L4" s="99" t="s">
+      <c r="L4" s="159" t="s">
         <v>61</v>
       </c>
-      <c r="M4" s="99" t="s">
+      <c r="M4" s="159" t="s">
         <v>62</v>
       </c>
-      <c r="N4" s="99" t="s">
+      <c r="N4" s="159" t="s">
         <v>63</v>
       </c>
-      <c r="O4" s="99" t="s">
+      <c r="O4" s="159" t="s">
         <v>64</v>
       </c>
-      <c r="P4" s="99" t="s">
+      <c r="P4" s="159" t="s">
         <v>65</v>
       </c>
-      <c r="Q4" s="100" t="s">
+      <c r="Q4" s="160" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B5" s="118" t="s">
+      <c r="B5" s="151" t="s">
         <v>149</v>
       </c>
-      <c r="C5" s="127"/>
-      <c r="D5" s="120"/>
-      <c r="E5" s="123"/>
-      <c r="F5" s="122"/>
-      <c r="G5" s="124"/>
-      <c r="H5" s="130"/>
-      <c r="I5" s="125"/>
-      <c r="J5" s="125"/>
-      <c r="K5" s="125"/>
-      <c r="L5" s="125"/>
-      <c r="M5" s="125"/>
-      <c r="N5" s="125"/>
-      <c r="O5" s="125"/>
-      <c r="P5" s="125"/>
-      <c r="Q5" s="126"/>
+      <c r="C5" s="148"/>
+      <c r="D5" s="162"/>
+      <c r="E5" s="163"/>
+      <c r="F5" s="114"/>
+      <c r="G5" s="164"/>
+      <c r="H5" s="161"/>
+      <c r="I5" s="152"/>
+      <c r="J5" s="152"/>
+      <c r="K5" s="152"/>
+      <c r="L5" s="152"/>
+      <c r="M5" s="152"/>
+      <c r="N5" s="152"/>
+      <c r="O5" s="152"/>
+      <c r="P5" s="152"/>
+      <c r="Q5" s="153"/>
       <c r="S5" s="95"/>
     </row>
     <row r="6" spans="1:19" ht="20.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B6" s="117"/>
-      <c r="C6" s="128"/>
-      <c r="D6" s="131"/>
-      <c r="E6" s="140"/>
-      <c r="F6" s="132"/>
-      <c r="G6" s="141"/>
-      <c r="H6" s="133"/>
-      <c r="I6" s="134"/>
-      <c r="J6" s="134"/>
-      <c r="K6" s="134"/>
-      <c r="L6" s="134"/>
-      <c r="M6" s="134"/>
-      <c r="N6" s="134"/>
-      <c r="O6" s="134"/>
-      <c r="P6" s="134"/>
-      <c r="Q6" s="135"/>
+      <c r="B6" s="112"/>
+      <c r="C6" s="148"/>
+      <c r="D6" s="165"/>
+      <c r="E6" s="166"/>
+      <c r="F6" s="116"/>
+      <c r="G6" s="167"/>
+      <c r="H6" s="115"/>
+      <c r="I6" s="116"/>
+      <c r="J6" s="116"/>
+      <c r="K6" s="116"/>
+      <c r="L6" s="116"/>
+      <c r="M6" s="116"/>
+      <c r="N6" s="116"/>
+      <c r="O6" s="116"/>
+      <c r="P6" s="116"/>
+      <c r="Q6" s="117"/>
       <c r="S6" s="95"/>
     </row>
     <row r="7" spans="1:19" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B7" s="104"/>
-      <c r="C7" s="129"/>
-      <c r="D7" s="136"/>
-      <c r="E7" s="142"/>
-      <c r="F7" s="119"/>
-      <c r="G7" s="143"/>
-      <c r="H7" s="121"/>
-      <c r="I7" s="102"/>
-      <c r="J7" s="102"/>
-      <c r="K7" s="102"/>
-      <c r="L7" s="102"/>
-      <c r="M7" s="102"/>
-      <c r="N7" s="102"/>
-      <c r="O7" s="102"/>
-      <c r="P7" s="102"/>
-      <c r="Q7" s="103"/>
+      <c r="B7" s="99"/>
+      <c r="C7" s="149"/>
+      <c r="D7" s="168"/>
+      <c r="E7" s="169"/>
+      <c r="F7" s="170"/>
+      <c r="G7" s="171"/>
+      <c r="H7" s="113"/>
+      <c r="I7" s="97"/>
+      <c r="J7" s="97"/>
+      <c r="K7" s="97"/>
+      <c r="L7" s="97"/>
+      <c r="M7" s="97"/>
+      <c r="N7" s="97"/>
+      <c r="O7" s="97"/>
+      <c r="P7" s="97"/>
+      <c r="Q7" s="98"/>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.45">
       <c r="H8" s="94"/>
@@ -2924,40 +3031,40 @@
   <sheetData>
     <row r="1" spans="2:29" ht="15.6" thickBot="1" x14ac:dyDescent="0.5"/>
     <row r="2" spans="2:29" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B2" s="147" t="s">
+      <c r="B2" s="119" t="s">
         <v>53</v>
       </c>
-      <c r="C2" s="148"/>
-      <c r="D2" s="156" t="s">
+      <c r="C2" s="120"/>
+      <c r="D2" s="131" t="s">
         <v>54</v>
       </c>
-      <c r="E2" s="164" t="s">
+      <c r="E2" s="139" t="s">
         <v>55</v>
       </c>
-      <c r="F2" s="165"/>
-      <c r="G2" s="166"/>
-      <c r="H2" s="158" t="s">
+      <c r="F2" s="140"/>
+      <c r="G2" s="141"/>
+      <c r="H2" s="133" t="s">
         <v>56</v>
       </c>
-      <c r="I2" s="159"/>
-      <c r="J2" s="159"/>
-      <c r="K2" s="159"/>
-      <c r="L2" s="159"/>
-      <c r="M2" s="159"/>
-      <c r="N2" s="159"/>
-      <c r="O2" s="159"/>
-      <c r="P2" s="159"/>
-      <c r="Q2" s="160"/>
+      <c r="I2" s="134"/>
+      <c r="J2" s="134"/>
+      <c r="K2" s="134"/>
+      <c r="L2" s="134"/>
+      <c r="M2" s="134"/>
+      <c r="N2" s="134"/>
+      <c r="O2" s="134"/>
+      <c r="P2" s="134"/>
+      <c r="Q2" s="135"/>
     </row>
     <row r="3" spans="2:29" x14ac:dyDescent="0.45">
-      <c r="B3" s="149"/>
-      <c r="C3" s="150"/>
-      <c r="D3" s="157"/>
-      <c r="E3" s="161" t="s">
+      <c r="B3" s="121"/>
+      <c r="C3" s="122"/>
+      <c r="D3" s="132"/>
+      <c r="E3" s="136" t="s">
         <v>96</v>
       </c>
-      <c r="F3" s="162"/>
-      <c r="G3" s="163"/>
+      <c r="F3" s="137"/>
+      <c r="G3" s="138"/>
       <c r="H3" s="22"/>
       <c r="I3" s="21"/>
       <c r="J3" s="21"/>
@@ -2970,9 +3077,9 @@
       <c r="Q3" s="20"/>
     </row>
     <row r="4" spans="2:29" ht="30.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B4" s="151"/>
-      <c r="C4" s="152"/>
-      <c r="D4" s="157"/>
+      <c r="B4" s="123"/>
+      <c r="C4" s="124"/>
+      <c r="D4" s="132"/>
       <c r="E4" s="85" t="s">
         <v>140</v>
       </c>
@@ -3014,10 +3121,10 @@
       </c>
     </row>
     <row r="5" spans="2:29" x14ac:dyDescent="0.45">
-      <c r="B5" s="153" t="s">
+      <c r="B5" s="128" t="s">
         <v>89</v>
       </c>
-      <c r="C5" s="144" t="s">
+      <c r="C5" s="125" t="s">
         <v>137</v>
       </c>
       <c r="D5" s="33" t="s">
@@ -3071,8 +3178,8 @@
       </c>
     </row>
     <row r="6" spans="2:29" x14ac:dyDescent="0.45">
-      <c r="B6" s="154"/>
-      <c r="C6" s="145"/>
+      <c r="B6" s="129"/>
+      <c r="C6" s="126"/>
       <c r="D6" s="26" t="s">
         <v>102</v>
       </c>
@@ -3125,8 +3232,8 @@
       <c r="AC6" s="19"/>
     </row>
     <row r="7" spans="2:29" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B7" s="154"/>
-      <c r="C7" s="146"/>
+      <c r="B7" s="129"/>
+      <c r="C7" s="127"/>
       <c r="D7" s="83" t="s">
         <v>70</v>
       </c>
@@ -3177,7 +3284,7 @@
       <c r="AC7" s="19"/>
     </row>
     <row r="8" spans="2:29" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B8" s="154"/>
+      <c r="B8" s="129"/>
       <c r="C8" s="36" t="s">
         <v>91</v>
       </c>
@@ -3231,8 +3338,8 @@
       </c>
     </row>
     <row r="9" spans="2:29" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B9" s="154"/>
-      <c r="C9" s="144" t="s">
+      <c r="B9" s="129"/>
+      <c r="C9" s="125" t="s">
         <v>101</v>
       </c>
       <c r="D9" s="33" t="s">
@@ -3283,8 +3390,8 @@
       </c>
     </row>
     <row r="10" spans="2:29" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B10" s="154"/>
-      <c r="C10" s="145"/>
+      <c r="B10" s="129"/>
+      <c r="C10" s="126"/>
       <c r="D10" s="26" t="s">
         <v>102</v>
       </c>
@@ -3335,8 +3442,8 @@
       <c r="AC10" s="19"/>
     </row>
     <row r="11" spans="2:29" ht="15.6" hidden="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B11" s="154"/>
-      <c r="C11" s="146"/>
+      <c r="B11" s="129"/>
+      <c r="C11" s="127"/>
       <c r="D11" s="34" t="s">
         <v>70</v>
       </c>
@@ -3387,7 +3494,7 @@
       <c r="AC11" s="19"/>
     </row>
     <row r="12" spans="2:29" ht="15.6" hidden="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B12" s="154"/>
+      <c r="B12" s="129"/>
       <c r="C12" s="36" t="s">
         <v>91</v>
       </c>
@@ -3441,8 +3548,8 @@
       </c>
     </row>
     <row r="13" spans="2:29" x14ac:dyDescent="0.45">
-      <c r="B13" s="154"/>
-      <c r="C13" s="144" t="s">
+      <c r="B13" s="129"/>
+      <c r="C13" s="125" t="s">
         <v>142</v>
       </c>
       <c r="D13" s="33" t="s">
@@ -3493,8 +3600,8 @@
       </c>
     </row>
     <row r="14" spans="2:29" x14ac:dyDescent="0.45">
-      <c r="B14" s="154"/>
-      <c r="C14" s="145"/>
+      <c r="B14" s="129"/>
+      <c r="C14" s="126"/>
       <c r="D14" s="26" t="s">
         <v>102</v>
       </c>
@@ -3545,8 +3652,8 @@
       <c r="AC14" s="19"/>
     </row>
     <row r="15" spans="2:29" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B15" s="154"/>
-      <c r="C15" s="146"/>
+      <c r="B15" s="129"/>
+      <c r="C15" s="127"/>
       <c r="D15" s="83" t="s">
         <v>70</v>
       </c>
@@ -3597,7 +3704,7 @@
       <c r="AC15" s="19"/>
     </row>
     <row r="16" spans="2:29" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B16" s="155"/>
+      <c r="B16" s="130"/>
       <c r="C16" s="32" t="s">
         <v>91</v>
       </c>
@@ -3663,40 +3770,40 @@
       <c r="Q17" s="12"/>
     </row>
     <row r="18" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B18" s="147" t="s">
+      <c r="B18" s="119" t="s">
         <v>53</v>
       </c>
-      <c r="C18" s="148"/>
-      <c r="D18" s="156" t="s">
+      <c r="C18" s="120"/>
+      <c r="D18" s="131" t="s">
         <v>54</v>
       </c>
-      <c r="E18" s="164" t="s">
+      <c r="E18" s="139" t="s">
         <v>55</v>
       </c>
-      <c r="F18" s="165"/>
-      <c r="G18" s="166"/>
-      <c r="H18" s="170" t="s">
+      <c r="F18" s="140"/>
+      <c r="G18" s="141"/>
+      <c r="H18" s="145" t="s">
         <v>56</v>
       </c>
-      <c r="I18" s="171"/>
-      <c r="J18" s="171"/>
-      <c r="K18" s="171"/>
-      <c r="L18" s="171"/>
-      <c r="M18" s="171"/>
-      <c r="N18" s="171"/>
-      <c r="O18" s="171"/>
-      <c r="P18" s="171"/>
-      <c r="Q18" s="172"/>
+      <c r="I18" s="146"/>
+      <c r="J18" s="146"/>
+      <c r="K18" s="146"/>
+      <c r="L18" s="146"/>
+      <c r="M18" s="146"/>
+      <c r="N18" s="146"/>
+      <c r="O18" s="146"/>
+      <c r="P18" s="146"/>
+      <c r="Q18" s="147"/>
     </row>
     <row r="19" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B19" s="149"/>
-      <c r="C19" s="150"/>
-      <c r="D19" s="157"/>
-      <c r="E19" s="161" t="s">
+      <c r="B19" s="121"/>
+      <c r="C19" s="122"/>
+      <c r="D19" s="132"/>
+      <c r="E19" s="136" t="s">
         <v>96</v>
       </c>
-      <c r="F19" s="162"/>
-      <c r="G19" s="163"/>
+      <c r="F19" s="137"/>
+      <c r="G19" s="138"/>
       <c r="H19" s="67"/>
       <c r="I19" s="68"/>
       <c r="J19" s="68"/>
@@ -3709,9 +3816,9 @@
       <c r="Q19" s="69"/>
     </row>
     <row r="20" spans="2:28" ht="30.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B20" s="151"/>
-      <c r="C20" s="152"/>
-      <c r="D20" s="157"/>
+      <c r="B20" s="123"/>
+      <c r="C20" s="124"/>
+      <c r="D20" s="132"/>
       <c r="E20" s="85" t="s">
         <v>140</v>
       </c>
@@ -3753,10 +3860,10 @@
       </c>
     </row>
     <row r="21" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B21" s="153" t="s">
+      <c r="B21" s="128" t="s">
         <v>100</v>
       </c>
-      <c r="C21" s="144" t="s">
+      <c r="C21" s="125" t="s">
         <v>99</v>
       </c>
       <c r="D21" s="33" t="s">
@@ -3816,8 +3923,8 @@
       </c>
     </row>
     <row r="22" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B22" s="154"/>
-      <c r="C22" s="145"/>
+      <c r="B22" s="129"/>
+      <c r="C22" s="126"/>
       <c r="D22" s="26" t="s">
         <v>102</v>
       </c>
@@ -3871,8 +3978,8 @@
       <c r="AB22" s="19"/>
     </row>
     <row r="23" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B23" s="154"/>
-      <c r="C23" s="146"/>
+      <c r="B23" s="129"/>
+      <c r="C23" s="127"/>
       <c r="D23" s="83" t="s">
         <v>70</v>
       </c>
@@ -3926,7 +4033,7 @@
       <c r="AB23" s="19"/>
     </row>
     <row r="24" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B24" s="154"/>
+      <c r="B24" s="129"/>
       <c r="C24" s="36" t="s">
         <v>91</v>
       </c>
@@ -3982,8 +4089,8 @@
       </c>
     </row>
     <row r="25" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B25" s="154"/>
-      <c r="C25" s="144" t="s">
+      <c r="B25" s="129"/>
+      <c r="C25" s="125" t="s">
         <v>98</v>
       </c>
       <c r="D25" s="33" t="s">
@@ -4043,8 +4150,8 @@
       </c>
     </row>
     <row r="26" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B26" s="154"/>
-      <c r="C26" s="145"/>
+      <c r="B26" s="129"/>
+      <c r="C26" s="126"/>
       <c r="D26" s="26" t="s">
         <v>102</v>
       </c>
@@ -4098,8 +4205,8 @@
       <c r="AB26" s="19"/>
     </row>
     <row r="27" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B27" s="154"/>
-      <c r="C27" s="146"/>
+      <c r="B27" s="129"/>
+      <c r="C27" s="127"/>
       <c r="D27" s="83" t="s">
         <v>70</v>
       </c>
@@ -4153,7 +4260,7 @@
       <c r="AB27" s="19"/>
     </row>
     <row r="28" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B28" s="154"/>
+      <c r="B28" s="129"/>
       <c r="C28" s="36" t="s">
         <v>91</v>
       </c>
@@ -4209,8 +4316,8 @@
       </c>
     </row>
     <row r="29" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B29" s="154"/>
-      <c r="C29" s="144" t="s">
+      <c r="B29" s="129"/>
+      <c r="C29" s="125" t="s">
         <v>97</v>
       </c>
       <c r="D29" s="33" t="s">
@@ -4270,8 +4377,8 @@
       </c>
     </row>
     <row r="30" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B30" s="154"/>
-      <c r="C30" s="145"/>
+      <c r="B30" s="129"/>
+      <c r="C30" s="126"/>
       <c r="D30" s="26" t="s">
         <v>102</v>
       </c>
@@ -4325,8 +4432,8 @@
       <c r="AB30" s="19"/>
     </row>
     <row r="31" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B31" s="154"/>
-      <c r="C31" s="146"/>
+      <c r="B31" s="129"/>
+      <c r="C31" s="127"/>
       <c r="D31" s="83" t="s">
         <v>70</v>
       </c>
@@ -4380,7 +4487,7 @@
       <c r="AB31" s="19"/>
     </row>
     <row r="32" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B32" s="155"/>
+      <c r="B32" s="130"/>
       <c r="C32" s="32" t="s">
         <v>91</v>
       </c>
@@ -4448,40 +4555,40 @@
       <c r="Q33" s="12"/>
     </row>
     <row r="34" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B34" s="147" t="s">
+      <c r="B34" s="119" t="s">
         <v>53</v>
       </c>
-      <c r="C34" s="148"/>
-      <c r="D34" s="156" t="s">
+      <c r="C34" s="120"/>
+      <c r="D34" s="131" t="s">
         <v>54</v>
       </c>
-      <c r="E34" s="164" t="s">
+      <c r="E34" s="139" t="s">
         <v>55</v>
       </c>
-      <c r="F34" s="165"/>
-      <c r="G34" s="166"/>
-      <c r="H34" s="170" t="s">
+      <c r="F34" s="140"/>
+      <c r="G34" s="141"/>
+      <c r="H34" s="145" t="s">
         <v>56</v>
       </c>
-      <c r="I34" s="171"/>
-      <c r="J34" s="171"/>
-      <c r="K34" s="171"/>
-      <c r="L34" s="171"/>
-      <c r="M34" s="171"/>
-      <c r="N34" s="171"/>
-      <c r="O34" s="171"/>
-      <c r="P34" s="171"/>
-      <c r="Q34" s="172"/>
+      <c r="I34" s="146"/>
+      <c r="J34" s="146"/>
+      <c r="K34" s="146"/>
+      <c r="L34" s="146"/>
+      <c r="M34" s="146"/>
+      <c r="N34" s="146"/>
+      <c r="O34" s="146"/>
+      <c r="P34" s="146"/>
+      <c r="Q34" s="147"/>
     </row>
     <row r="35" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B35" s="149"/>
-      <c r="C35" s="150"/>
-      <c r="D35" s="157"/>
-      <c r="E35" s="161" t="s">
+      <c r="B35" s="121"/>
+      <c r="C35" s="122"/>
+      <c r="D35" s="132"/>
+      <c r="E35" s="136" t="s">
         <v>96</v>
       </c>
-      <c r="F35" s="162"/>
-      <c r="G35" s="163"/>
+      <c r="F35" s="137"/>
+      <c r="G35" s="138"/>
       <c r="H35" s="67"/>
       <c r="I35" s="68"/>
       <c r="J35" s="68"/>
@@ -4494,9 +4601,9 @@
       <c r="Q35" s="69"/>
     </row>
     <row r="36" spans="2:28" ht="30.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B36" s="151"/>
-      <c r="C36" s="152"/>
-      <c r="D36" s="157"/>
+      <c r="B36" s="123"/>
+      <c r="C36" s="124"/>
+      <c r="D36" s="132"/>
       <c r="E36" s="85" t="s">
         <v>140</v>
       </c>
@@ -4538,10 +4645,10 @@
       </c>
     </row>
     <row r="37" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B37" s="153" t="s">
+      <c r="B37" s="128" t="s">
         <v>95</v>
       </c>
-      <c r="C37" s="144" t="s">
+      <c r="C37" s="125" t="s">
         <v>94</v>
       </c>
       <c r="D37" s="33" t="s">
@@ -4601,8 +4708,8 @@
       </c>
     </row>
     <row r="38" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B38" s="154"/>
-      <c r="C38" s="145"/>
+      <c r="B38" s="129"/>
+      <c r="C38" s="126"/>
       <c r="D38" s="26" t="s">
         <v>102</v>
       </c>
@@ -4656,8 +4763,8 @@
       <c r="AB38" s="19"/>
     </row>
     <row r="39" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B39" s="154"/>
-      <c r="C39" s="146"/>
+      <c r="B39" s="129"/>
+      <c r="C39" s="127"/>
       <c r="D39" s="83" t="s">
         <v>70</v>
       </c>
@@ -4711,7 +4818,7 @@
       <c r="AB39" s="19"/>
     </row>
     <row r="40" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B40" s="154"/>
+      <c r="B40" s="129"/>
       <c r="C40" s="36" t="s">
         <v>91</v>
       </c>
@@ -4767,8 +4874,8 @@
       </c>
     </row>
     <row r="41" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B41" s="154"/>
-      <c r="C41" s="144" t="s">
+      <c r="B41" s="129"/>
+      <c r="C41" s="125" t="s">
         <v>79</v>
       </c>
       <c r="D41" s="33" t="s">
@@ -4828,8 +4935,8 @@
       </c>
     </row>
     <row r="42" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B42" s="154"/>
-      <c r="C42" s="145"/>
+      <c r="B42" s="129"/>
+      <c r="C42" s="126"/>
       <c r="D42" s="26" t="s">
         <v>102</v>
       </c>
@@ -4883,8 +4990,8 @@
       <c r="AB42" s="19"/>
     </row>
     <row r="43" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B43" s="154"/>
-      <c r="C43" s="146"/>
+      <c r="B43" s="129"/>
+      <c r="C43" s="127"/>
       <c r="D43" s="83" t="s">
         <v>70</v>
       </c>
@@ -4938,7 +5045,7 @@
       <c r="AB43" s="19"/>
     </row>
     <row r="44" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B44" s="154"/>
+      <c r="B44" s="129"/>
       <c r="C44" s="36" t="s">
         <v>91</v>
       </c>
@@ -4994,8 +5101,8 @@
       </c>
     </row>
     <row r="45" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B45" s="154"/>
-      <c r="C45" s="144" t="s">
+      <c r="B45" s="129"/>
+      <c r="C45" s="125" t="s">
         <v>93</v>
       </c>
       <c r="D45" s="33" t="s">
@@ -5055,8 +5162,8 @@
       </c>
     </row>
     <row r="46" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B46" s="154"/>
-      <c r="C46" s="145"/>
+      <c r="B46" s="129"/>
+      <c r="C46" s="126"/>
       <c r="D46" s="26" t="s">
         <v>102</v>
       </c>
@@ -5110,8 +5217,8 @@
       <c r="AB46" s="19"/>
     </row>
     <row r="47" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B47" s="154"/>
-      <c r="C47" s="146"/>
+      <c r="B47" s="129"/>
+      <c r="C47" s="127"/>
       <c r="D47" s="83" t="s">
         <v>70</v>
       </c>
@@ -5165,7 +5272,7 @@
       <c r="AB47" s="19"/>
     </row>
     <row r="48" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B48" s="154"/>
+      <c r="B48" s="129"/>
       <c r="C48" s="36" t="s">
         <v>91</v>
       </c>
@@ -5221,14 +5328,14 @@
       </c>
     </row>
     <row r="49" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B49" s="154"/>
-      <c r="C49" s="144" t="s">
+      <c r="B49" s="129"/>
+      <c r="C49" s="125" t="s">
         <v>92</v>
       </c>
       <c r="D49" s="33" t="s">
         <v>143</v>
       </c>
-      <c r="E49" s="167"/>
+      <c r="E49" s="142"/>
       <c r="F49" s="87"/>
       <c r="G49" s="31"/>
       <c r="H49" s="64" t="e">
@@ -5273,12 +5380,12 @@
       </c>
     </row>
     <row r="50" spans="2:28" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B50" s="154"/>
-      <c r="C50" s="145"/>
+      <c r="B50" s="129"/>
+      <c r="C50" s="126"/>
       <c r="D50" s="26" t="s">
         <v>102</v>
       </c>
-      <c r="E50" s="168"/>
+      <c r="E50" s="143"/>
       <c r="F50" s="88"/>
       <c r="G50" s="28"/>
       <c r="H50" s="73">
@@ -5324,12 +5431,12 @@
       <c r="AB50" s="19"/>
     </row>
     <row r="51" spans="2:28" ht="18.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B51" s="154"/>
-      <c r="C51" s="146"/>
+      <c r="B51" s="129"/>
+      <c r="C51" s="127"/>
       <c r="D51" s="83" t="s">
         <v>70</v>
       </c>
-      <c r="E51" s="169"/>
+      <c r="E51" s="144"/>
       <c r="F51" s="89"/>
       <c r="G51" s="54"/>
       <c r="H51" s="75">
@@ -5375,7 +5482,7 @@
       <c r="AB51" s="19"/>
     </row>
     <row r="52" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B52" s="155"/>
+      <c r="B52" s="130"/>
       <c r="C52" s="32" t="s">
         <v>91</v>
       </c>
@@ -5827,16 +5934,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B2:C4"/>
-    <mergeCell ref="C9:C11"/>
-    <mergeCell ref="C13:C15"/>
-    <mergeCell ref="C21:C23"/>
-    <mergeCell ref="B18:C20"/>
-    <mergeCell ref="B5:B16"/>
-    <mergeCell ref="B21:B32"/>
-    <mergeCell ref="C5:C7"/>
-    <mergeCell ref="C29:C31"/>
-    <mergeCell ref="C25:C27"/>
+    <mergeCell ref="C41:C43"/>
+    <mergeCell ref="C45:C47"/>
+    <mergeCell ref="C49:C51"/>
+    <mergeCell ref="B34:C36"/>
+    <mergeCell ref="B37:B52"/>
+    <mergeCell ref="C37:C39"/>
     <mergeCell ref="D2:D4"/>
     <mergeCell ref="H2:Q2"/>
     <mergeCell ref="E3:G3"/>
@@ -5850,12 +5953,16 @@
     <mergeCell ref="D18:D20"/>
     <mergeCell ref="E18:G18"/>
     <mergeCell ref="E19:G19"/>
-    <mergeCell ref="C41:C43"/>
-    <mergeCell ref="C45:C47"/>
-    <mergeCell ref="C49:C51"/>
-    <mergeCell ref="B34:C36"/>
-    <mergeCell ref="B37:B52"/>
-    <mergeCell ref="C37:C39"/>
+    <mergeCell ref="B2:C4"/>
+    <mergeCell ref="C9:C11"/>
+    <mergeCell ref="C13:C15"/>
+    <mergeCell ref="C21:C23"/>
+    <mergeCell ref="B18:C20"/>
+    <mergeCell ref="B5:B16"/>
+    <mergeCell ref="B21:B32"/>
+    <mergeCell ref="C5:C7"/>
+    <mergeCell ref="C29:C31"/>
+    <mergeCell ref="C25:C27"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <conditionalFormatting sqref="H5:Q7">

--- a/tool/track-aggregator/template/年度比較結果.xlsx
+++ b/tool/track-aggregator/template/年度比較結果.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ishid\Desktop\project_management\tool\track-aggregator\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24134632-FFFF-4673-AF70-0ED7AEF7ABF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A4D5D3B-5DCD-46AA-BEE3-F9A955EBB6DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
     <sheet name="ビジネス基礎（Day5)" sheetId="13" state="hidden" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">経年比較!$B$2:$Q$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">経年比較!$B$2:$Q$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'経年比較（前年同じFMT）'!$B$2:$Q$16</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -1038,7 +1038,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="61">
+  <borders count="55">
     <border>
       <left/>
       <right/>
@@ -1601,16 +1601,29 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left style="medium">
         <color indexed="64"/>
       </left>
-      <right style="thin">
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
         <color indexed="64"/>
       </right>
       <top style="medium">
         <color indexed="64"/>
       </top>
-      <bottom style="thin">
+      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -1619,13 +1632,56 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="medium">
+      <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom style="thin">
+      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -1638,18 +1694,7 @@
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
+      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -1658,166 +1703,31 @@
       <left style="medium">
         <color indexed="64"/>
       </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
+      <right/>
       <top/>
       <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
+      <right/>
+      <top/>
+      <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
-      <right style="thin">
+      <right style="medium">
         <color indexed="64"/>
       </right>
       <top/>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
       <diagonal/>
     </border>
   </borders>
@@ -1833,7 +1743,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="172">
+  <cellXfs count="169">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2122,9 +2032,6 @@
     <xf numFmtId="178" fontId="11" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="179" fontId="12" fillId="6" borderId="41" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2134,61 +2041,46 @@
     <xf numFmtId="0" fontId="10" fillId="7" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" textRotation="255"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="23" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="39" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="22" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="21" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="40" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="18" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" textRotation="255"/>
-    </xf>
     <xf numFmtId="179" fontId="12" fillId="6" borderId="43" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="11" fillId="0" borderId="45" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="179" fontId="10" fillId="9" borderId="48" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="10" fillId="9" borderId="49" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="50" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="51" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="47" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="50" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="46" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="12" fillId="6" borderId="44" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="11" fillId="0" borderId="47" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="12" fillId="6" borderId="41" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="11" fillId="0" borderId="13" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="11" fillId="0" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="48" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="12" fillId="6" borderId="42" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2278,77 +2170,86 @@
     <xf numFmtId="179" fontId="5" fillId="8" borderId="20" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="46" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="179" fontId="11" fillId="0" borderId="44" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="11" fillId="0" borderId="41" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="11" fillId="0" borderId="42" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="11" fillId="0" borderId="43" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="11" fillId="0" borderId="42" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="16" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="15" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="7" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="179" fontId="11" fillId="0" borderId="51" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="11" fillId="0" borderId="52" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="16" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="10" fillId="9" borderId="53" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="10" fillId="9" borderId="54" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="55" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="23" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="56" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="50" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="55" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="11" fillId="0" borderId="57" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="59" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="39" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="11" fillId="0" borderId="58" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="11" fillId="0" borderId="46" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="60" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="22" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="11" fillId="0" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="11" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="49" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="45" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="12" fillId="6" borderId="44" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="12" fillId="6" borderId="41" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="12" fillId="6" borderId="42" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="40" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="18" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="21" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="52" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="53" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="54" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -2794,7 +2695,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{738A7942-48C0-418C-A267-8ECE9048A1F1}">
-  <dimension ref="A1:S8"/>
+  <dimension ref="A1:S7"/>
   <sheetFormatPr defaultColWidth="8.19921875" defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="2.59765625" style="93" customWidth="1"/>
@@ -2814,168 +2715,156 @@
       </c>
     </row>
     <row r="2" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B2" s="107" t="s">
+      <c r="B2" s="148" t="s">
         <v>53</v>
       </c>
-      <c r="C2" s="108"/>
-      <c r="D2" s="107" t="s">
+      <c r="C2" s="149"/>
+      <c r="D2" s="154" t="s">
         <v>54</v>
       </c>
-      <c r="E2" s="100" t="s">
+      <c r="E2" s="157" t="s">
         <v>55</v>
       </c>
-      <c r="F2" s="101"/>
-      <c r="G2" s="102"/>
-      <c r="H2" s="103" t="s">
+      <c r="F2" s="158"/>
+      <c r="G2" s="159"/>
+      <c r="H2" s="164" t="s">
         <v>56</v>
       </c>
-      <c r="I2" s="103"/>
-      <c r="J2" s="103"/>
-      <c r="K2" s="103"/>
-      <c r="L2" s="103"/>
-      <c r="M2" s="103"/>
-      <c r="N2" s="103"/>
-      <c r="O2" s="103"/>
-      <c r="P2" s="103"/>
-      <c r="Q2" s="104"/>
+      <c r="I2" s="163"/>
+      <c r="J2" s="163"/>
+      <c r="K2" s="163"/>
+      <c r="L2" s="163"/>
+      <c r="M2" s="163"/>
+      <c r="N2" s="163"/>
+      <c r="O2" s="163"/>
+      <c r="P2" s="163"/>
+      <c r="Q2" s="165"/>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.45">
-      <c r="B3" s="109"/>
-      <c r="C3" s="110"/>
-      <c r="D3" s="109"/>
-      <c r="E3" s="118" t="s">
+      <c r="B3" s="150"/>
+      <c r="C3" s="151"/>
+      <c r="D3" s="155"/>
+      <c r="E3" s="160" t="s">
         <v>96</v>
       </c>
-      <c r="F3" s="105"/>
-      <c r="G3" s="106"/>
-      <c r="H3" s="150"/>
-      <c r="I3" s="150"/>
-      <c r="J3" s="150"/>
-      <c r="K3" s="150"/>
-      <c r="L3" s="150"/>
-      <c r="M3" s="150"/>
-      <c r="N3" s="150"/>
-      <c r="O3" s="150"/>
-      <c r="P3" s="150"/>
-      <c r="Q3" s="96"/>
+      <c r="F3" s="161"/>
+      <c r="G3" s="162"/>
+      <c r="H3" s="166"/>
+      <c r="I3" s="167"/>
+      <c r="J3" s="167"/>
+      <c r="K3" s="167"/>
+      <c r="L3" s="167"/>
+      <c r="M3" s="167"/>
+      <c r="N3" s="167"/>
+      <c r="O3" s="167"/>
+      <c r="P3" s="167"/>
+      <c r="Q3" s="168"/>
     </row>
     <row r="4" spans="1:19" ht="36.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B4" s="111"/>
-      <c r="C4" s="154"/>
-      <c r="D4" s="111"/>
-      <c r="E4" s="155" t="s">
+      <c r="B4" s="152"/>
+      <c r="C4" s="153"/>
+      <c r="D4" s="156"/>
+      <c r="E4" s="103" t="s">
         <v>140</v>
       </c>
-      <c r="F4" s="156" t="s">
+      <c r="F4" s="104" t="s">
         <v>147</v>
       </c>
-      <c r="G4" s="157" t="s">
+      <c r="G4" s="105" t="s">
         <v>57</v>
       </c>
-      <c r="H4" s="158" t="s">
+      <c r="H4" s="106" t="s">
         <v>58</v>
       </c>
-      <c r="I4" s="159" t="s">
+      <c r="I4" s="107" t="s">
         <v>59</v>
       </c>
-      <c r="J4" s="159" t="s">
+      <c r="J4" s="107" t="s">
         <v>60</v>
       </c>
-      <c r="K4" s="159" t="s">
+      <c r="K4" s="107" t="s">
         <v>139</v>
       </c>
-      <c r="L4" s="159" t="s">
+      <c r="L4" s="107" t="s">
         <v>61</v>
       </c>
-      <c r="M4" s="159" t="s">
+      <c r="M4" s="107" t="s">
         <v>62</v>
       </c>
-      <c r="N4" s="159" t="s">
+      <c r="N4" s="107" t="s">
         <v>63</v>
       </c>
-      <c r="O4" s="159" t="s">
+      <c r="O4" s="107" t="s">
         <v>64</v>
       </c>
-      <c r="P4" s="159" t="s">
+      <c r="P4" s="107" t="s">
         <v>65</v>
       </c>
-      <c r="Q4" s="160" t="s">
+      <c r="Q4" s="108" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="5" spans="1:19" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B5" s="151" t="s">
+    <row r="5" spans="1:19" ht="20.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B5" s="102" t="s">
         <v>149</v>
       </c>
-      <c r="C5" s="148"/>
-      <c r="D5" s="162"/>
-      <c r="E5" s="163"/>
-      <c r="F5" s="114"/>
-      <c r="G5" s="164"/>
-      <c r="H5" s="161"/>
-      <c r="I5" s="152"/>
-      <c r="J5" s="152"/>
-      <c r="K5" s="152"/>
-      <c r="L5" s="152"/>
-      <c r="M5" s="152"/>
-      <c r="N5" s="152"/>
-      <c r="O5" s="152"/>
-      <c r="P5" s="152"/>
-      <c r="Q5" s="153"/>
+      <c r="C5" s="100"/>
+      <c r="D5" s="142"/>
+      <c r="E5" s="143"/>
+      <c r="F5" s="144"/>
+      <c r="G5" s="145"/>
+      <c r="H5" s="146"/>
+      <c r="I5" s="144"/>
+      <c r="J5" s="144"/>
+      <c r="K5" s="144"/>
+      <c r="L5" s="144"/>
+      <c r="M5" s="144"/>
+      <c r="N5" s="144"/>
+      <c r="O5" s="144"/>
+      <c r="P5" s="144"/>
+      <c r="Q5" s="147"/>
       <c r="S5" s="95"/>
     </row>
-    <row r="6" spans="1:19" ht="20.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B6" s="112"/>
-      <c r="C6" s="148"/>
-      <c r="D6" s="165"/>
-      <c r="E6" s="166"/>
-      <c r="F6" s="116"/>
-      <c r="G6" s="167"/>
-      <c r="H6" s="115"/>
-      <c r="I6" s="116"/>
-      <c r="J6" s="116"/>
-      <c r="K6" s="116"/>
-      <c r="L6" s="116"/>
-      <c r="M6" s="116"/>
-      <c r="N6" s="116"/>
-      <c r="O6" s="116"/>
-      <c r="P6" s="116"/>
-      <c r="Q6" s="117"/>
-      <c r="S6" s="95"/>
-    </row>
-    <row r="7" spans="1:19" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B7" s="99"/>
-      <c r="C7" s="149"/>
-      <c r="D7" s="168"/>
-      <c r="E7" s="169"/>
-      <c r="F7" s="170"/>
-      <c r="G7" s="171"/>
-      <c r="H7" s="113"/>
-      <c r="I7" s="97"/>
-      <c r="J7" s="97"/>
-      <c r="K7" s="97"/>
-      <c r="L7" s="97"/>
-      <c r="M7" s="97"/>
-      <c r="N7" s="97"/>
-      <c r="O7" s="97"/>
-      <c r="P7" s="97"/>
-      <c r="Q7" s="98"/>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.45">
-      <c r="H8" s="94"/>
-      <c r="I8" s="94"/>
-      <c r="J8" s="94"/>
-      <c r="K8" s="94"/>
-      <c r="L8" s="94"/>
-      <c r="M8" s="94"/>
-      <c r="N8" s="94"/>
-      <c r="O8" s="94"/>
-      <c r="P8" s="94"/>
-      <c r="Q8" s="94"/>
+    <row r="6" spans="1:19" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B6" s="98"/>
+      <c r="C6" s="101"/>
+      <c r="D6" s="109"/>
+      <c r="E6" s="110"/>
+      <c r="F6" s="111"/>
+      <c r="G6" s="112"/>
+      <c r="H6" s="99"/>
+      <c r="I6" s="96"/>
+      <c r="J6" s="96"/>
+      <c r="K6" s="96"/>
+      <c r="L6" s="96"/>
+      <c r="M6" s="96"/>
+      <c r="N6" s="96"/>
+      <c r="O6" s="96"/>
+      <c r="P6" s="96"/>
+      <c r="Q6" s="97"/>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="H7" s="94"/>
+      <c r="I7" s="94"/>
+      <c r="J7" s="94"/>
+      <c r="K7" s="94"/>
+      <c r="L7" s="94"/>
+      <c r="M7" s="94"/>
+      <c r="N7" s="94"/>
+      <c r="O7" s="94"/>
+      <c r="P7" s="94"/>
+      <c r="Q7" s="94"/>
     </row>
   </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="B2:C4"/>
+    <mergeCell ref="D2:D4"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="E3:G3"/>
+    <mergeCell ref="H2:Q3"/>
+  </mergeCells>
   <phoneticPr fontId="1"/>
-  <conditionalFormatting sqref="H5:Q6">
+  <conditionalFormatting sqref="H5:Q5">
     <cfRule type="cellIs" dxfId="15" priority="1" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
@@ -3002,7 +2891,7 @@
               <x14:cfIcon iconSet="3Arrows" iconId="2"/>
             </x14:iconSet>
           </x14:cfRule>
-          <xm:sqref>H7:Q7</xm:sqref>
+          <xm:sqref>H6:Q6</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
@@ -3031,40 +2920,40 @@
   <sheetData>
     <row r="1" spans="2:29" ht="15.6" thickBot="1" x14ac:dyDescent="0.5"/>
     <row r="2" spans="2:29" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B2" s="119" t="s">
+      <c r="B2" s="113" t="s">
         <v>53</v>
       </c>
-      <c r="C2" s="120"/>
-      <c r="D2" s="131" t="s">
+      <c r="C2" s="114"/>
+      <c r="D2" s="125" t="s">
         <v>54</v>
       </c>
-      <c r="E2" s="139" t="s">
+      <c r="E2" s="133" t="s">
         <v>55</v>
       </c>
-      <c r="F2" s="140"/>
-      <c r="G2" s="141"/>
-      <c r="H2" s="133" t="s">
+      <c r="F2" s="134"/>
+      <c r="G2" s="135"/>
+      <c r="H2" s="127" t="s">
         <v>56</v>
       </c>
-      <c r="I2" s="134"/>
-      <c r="J2" s="134"/>
-      <c r="K2" s="134"/>
-      <c r="L2" s="134"/>
-      <c r="M2" s="134"/>
-      <c r="N2" s="134"/>
-      <c r="O2" s="134"/>
-      <c r="P2" s="134"/>
-      <c r="Q2" s="135"/>
+      <c r="I2" s="128"/>
+      <c r="J2" s="128"/>
+      <c r="K2" s="128"/>
+      <c r="L2" s="128"/>
+      <c r="M2" s="128"/>
+      <c r="N2" s="128"/>
+      <c r="O2" s="128"/>
+      <c r="P2" s="128"/>
+      <c r="Q2" s="129"/>
     </row>
     <row r="3" spans="2:29" x14ac:dyDescent="0.45">
-      <c r="B3" s="121"/>
-      <c r="C3" s="122"/>
-      <c r="D3" s="132"/>
-      <c r="E3" s="136" t="s">
+      <c r="B3" s="115"/>
+      <c r="C3" s="116"/>
+      <c r="D3" s="126"/>
+      <c r="E3" s="130" t="s">
         <v>96</v>
       </c>
-      <c r="F3" s="137"/>
-      <c r="G3" s="138"/>
+      <c r="F3" s="131"/>
+      <c r="G3" s="132"/>
       <c r="H3" s="22"/>
       <c r="I3" s="21"/>
       <c r="J3" s="21"/>
@@ -3077,9 +2966,9 @@
       <c r="Q3" s="20"/>
     </row>
     <row r="4" spans="2:29" ht="30.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B4" s="123"/>
-      <c r="C4" s="124"/>
-      <c r="D4" s="132"/>
+      <c r="B4" s="117"/>
+      <c r="C4" s="118"/>
+      <c r="D4" s="126"/>
       <c r="E4" s="85" t="s">
         <v>140</v>
       </c>
@@ -3121,10 +3010,10 @@
       </c>
     </row>
     <row r="5" spans="2:29" x14ac:dyDescent="0.45">
-      <c r="B5" s="128" t="s">
+      <c r="B5" s="122" t="s">
         <v>89</v>
       </c>
-      <c r="C5" s="125" t="s">
+      <c r="C5" s="119" t="s">
         <v>137</v>
       </c>
       <c r="D5" s="33" t="s">
@@ -3178,8 +3067,8 @@
       </c>
     </row>
     <row r="6" spans="2:29" x14ac:dyDescent="0.45">
-      <c r="B6" s="129"/>
-      <c r="C6" s="126"/>
+      <c r="B6" s="123"/>
+      <c r="C6" s="120"/>
       <c r="D6" s="26" t="s">
         <v>102</v>
       </c>
@@ -3232,8 +3121,8 @@
       <c r="AC6" s="19"/>
     </row>
     <row r="7" spans="2:29" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B7" s="129"/>
-      <c r="C7" s="127"/>
+      <c r="B7" s="123"/>
+      <c r="C7" s="121"/>
       <c r="D7" s="83" t="s">
         <v>70</v>
       </c>
@@ -3284,7 +3173,7 @@
       <c r="AC7" s="19"/>
     </row>
     <row r="8" spans="2:29" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B8" s="129"/>
+      <c r="B8" s="123"/>
       <c r="C8" s="36" t="s">
         <v>91</v>
       </c>
@@ -3338,8 +3227,8 @@
       </c>
     </row>
     <row r="9" spans="2:29" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B9" s="129"/>
-      <c r="C9" s="125" t="s">
+      <c r="B9" s="123"/>
+      <c r="C9" s="119" t="s">
         <v>101</v>
       </c>
       <c r="D9" s="33" t="s">
@@ -3390,8 +3279,8 @@
       </c>
     </row>
     <row r="10" spans="2:29" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B10" s="129"/>
-      <c r="C10" s="126"/>
+      <c r="B10" s="123"/>
+      <c r="C10" s="120"/>
       <c r="D10" s="26" t="s">
         <v>102</v>
       </c>
@@ -3442,8 +3331,8 @@
       <c r="AC10" s="19"/>
     </row>
     <row r="11" spans="2:29" ht="15.6" hidden="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B11" s="129"/>
-      <c r="C11" s="127"/>
+      <c r="B11" s="123"/>
+      <c r="C11" s="121"/>
       <c r="D11" s="34" t="s">
         <v>70</v>
       </c>
@@ -3494,7 +3383,7 @@
       <c r="AC11" s="19"/>
     </row>
     <row r="12" spans="2:29" ht="15.6" hidden="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B12" s="129"/>
+      <c r="B12" s="123"/>
       <c r="C12" s="36" t="s">
         <v>91</v>
       </c>
@@ -3548,8 +3437,8 @@
       </c>
     </row>
     <row r="13" spans="2:29" x14ac:dyDescent="0.45">
-      <c r="B13" s="129"/>
-      <c r="C13" s="125" t="s">
+      <c r="B13" s="123"/>
+      <c r="C13" s="119" t="s">
         <v>142</v>
       </c>
       <c r="D13" s="33" t="s">
@@ -3600,8 +3489,8 @@
       </c>
     </row>
     <row r="14" spans="2:29" x14ac:dyDescent="0.45">
-      <c r="B14" s="129"/>
-      <c r="C14" s="126"/>
+      <c r="B14" s="123"/>
+      <c r="C14" s="120"/>
       <c r="D14" s="26" t="s">
         <v>102</v>
       </c>
@@ -3652,8 +3541,8 @@
       <c r="AC14" s="19"/>
     </row>
     <row r="15" spans="2:29" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B15" s="129"/>
-      <c r="C15" s="127"/>
+      <c r="B15" s="123"/>
+      <c r="C15" s="121"/>
       <c r="D15" s="83" t="s">
         <v>70</v>
       </c>
@@ -3704,7 +3593,7 @@
       <c r="AC15" s="19"/>
     </row>
     <row r="16" spans="2:29" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B16" s="130"/>
+      <c r="B16" s="124"/>
       <c r="C16" s="32" t="s">
         <v>91</v>
       </c>
@@ -3770,40 +3659,40 @@
       <c r="Q17" s="12"/>
     </row>
     <row r="18" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B18" s="119" t="s">
+      <c r="B18" s="113" t="s">
         <v>53</v>
       </c>
-      <c r="C18" s="120"/>
-      <c r="D18" s="131" t="s">
+      <c r="C18" s="114"/>
+      <c r="D18" s="125" t="s">
         <v>54</v>
       </c>
-      <c r="E18" s="139" t="s">
+      <c r="E18" s="133" t="s">
         <v>55</v>
       </c>
-      <c r="F18" s="140"/>
-      <c r="G18" s="141"/>
-      <c r="H18" s="145" t="s">
+      <c r="F18" s="134"/>
+      <c r="G18" s="135"/>
+      <c r="H18" s="139" t="s">
         <v>56</v>
       </c>
-      <c r="I18" s="146"/>
-      <c r="J18" s="146"/>
-      <c r="K18" s="146"/>
-      <c r="L18" s="146"/>
-      <c r="M18" s="146"/>
-      <c r="N18" s="146"/>
-      <c r="O18" s="146"/>
-      <c r="P18" s="146"/>
-      <c r="Q18" s="147"/>
+      <c r="I18" s="140"/>
+      <c r="J18" s="140"/>
+      <c r="K18" s="140"/>
+      <c r="L18" s="140"/>
+      <c r="M18" s="140"/>
+      <c r="N18" s="140"/>
+      <c r="O18" s="140"/>
+      <c r="P18" s="140"/>
+      <c r="Q18" s="141"/>
     </row>
     <row r="19" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B19" s="121"/>
-      <c r="C19" s="122"/>
-      <c r="D19" s="132"/>
-      <c r="E19" s="136" t="s">
+      <c r="B19" s="115"/>
+      <c r="C19" s="116"/>
+      <c r="D19" s="126"/>
+      <c r="E19" s="130" t="s">
         <v>96</v>
       </c>
-      <c r="F19" s="137"/>
-      <c r="G19" s="138"/>
+      <c r="F19" s="131"/>
+      <c r="G19" s="132"/>
       <c r="H19" s="67"/>
       <c r="I19" s="68"/>
       <c r="J19" s="68"/>
@@ -3816,9 +3705,9 @@
       <c r="Q19" s="69"/>
     </row>
     <row r="20" spans="2:28" ht="30.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B20" s="123"/>
-      <c r="C20" s="124"/>
-      <c r="D20" s="132"/>
+      <c r="B20" s="117"/>
+      <c r="C20" s="118"/>
+      <c r="D20" s="126"/>
       <c r="E20" s="85" t="s">
         <v>140</v>
       </c>
@@ -3860,10 +3749,10 @@
       </c>
     </row>
     <row r="21" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B21" s="128" t="s">
+      <c r="B21" s="122" t="s">
         <v>100</v>
       </c>
-      <c r="C21" s="125" t="s">
+      <c r="C21" s="119" t="s">
         <v>99</v>
       </c>
       <c r="D21" s="33" t="s">
@@ -3923,8 +3812,8 @@
       </c>
     </row>
     <row r="22" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B22" s="129"/>
-      <c r="C22" s="126"/>
+      <c r="B22" s="123"/>
+      <c r="C22" s="120"/>
       <c r="D22" s="26" t="s">
         <v>102</v>
       </c>
@@ -3978,8 +3867,8 @@
       <c r="AB22" s="19"/>
     </row>
     <row r="23" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B23" s="129"/>
-      <c r="C23" s="127"/>
+      <c r="B23" s="123"/>
+      <c r="C23" s="121"/>
       <c r="D23" s="83" t="s">
         <v>70</v>
       </c>
@@ -4033,7 +3922,7 @@
       <c r="AB23" s="19"/>
     </row>
     <row r="24" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B24" s="129"/>
+      <c r="B24" s="123"/>
       <c r="C24" s="36" t="s">
         <v>91</v>
       </c>
@@ -4089,8 +3978,8 @@
       </c>
     </row>
     <row r="25" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B25" s="129"/>
-      <c r="C25" s="125" t="s">
+      <c r="B25" s="123"/>
+      <c r="C25" s="119" t="s">
         <v>98</v>
       </c>
       <c r="D25" s="33" t="s">
@@ -4150,8 +4039,8 @@
       </c>
     </row>
     <row r="26" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B26" s="129"/>
-      <c r="C26" s="126"/>
+      <c r="B26" s="123"/>
+      <c r="C26" s="120"/>
       <c r="D26" s="26" t="s">
         <v>102</v>
       </c>
@@ -4205,8 +4094,8 @@
       <c r="AB26" s="19"/>
     </row>
     <row r="27" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B27" s="129"/>
-      <c r="C27" s="127"/>
+      <c r="B27" s="123"/>
+      <c r="C27" s="121"/>
       <c r="D27" s="83" t="s">
         <v>70</v>
       </c>
@@ -4260,7 +4149,7 @@
       <c r="AB27" s="19"/>
     </row>
     <row r="28" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B28" s="129"/>
+      <c r="B28" s="123"/>
       <c r="C28" s="36" t="s">
         <v>91</v>
       </c>
@@ -4316,8 +4205,8 @@
       </c>
     </row>
     <row r="29" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B29" s="129"/>
-      <c r="C29" s="125" t="s">
+      <c r="B29" s="123"/>
+      <c r="C29" s="119" t="s">
         <v>97</v>
       </c>
       <c r="D29" s="33" t="s">
@@ -4377,8 +4266,8 @@
       </c>
     </row>
     <row r="30" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B30" s="129"/>
-      <c r="C30" s="126"/>
+      <c r="B30" s="123"/>
+      <c r="C30" s="120"/>
       <c r="D30" s="26" t="s">
         <v>102</v>
       </c>
@@ -4432,8 +4321,8 @@
       <c r="AB30" s="19"/>
     </row>
     <row r="31" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B31" s="129"/>
-      <c r="C31" s="127"/>
+      <c r="B31" s="123"/>
+      <c r="C31" s="121"/>
       <c r="D31" s="83" t="s">
         <v>70</v>
       </c>
@@ -4487,7 +4376,7 @@
       <c r="AB31" s="19"/>
     </row>
     <row r="32" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B32" s="130"/>
+      <c r="B32" s="124"/>
       <c r="C32" s="32" t="s">
         <v>91</v>
       </c>
@@ -4555,40 +4444,40 @@
       <c r="Q33" s="12"/>
     </row>
     <row r="34" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B34" s="119" t="s">
+      <c r="B34" s="113" t="s">
         <v>53</v>
       </c>
-      <c r="C34" s="120"/>
-      <c r="D34" s="131" t="s">
+      <c r="C34" s="114"/>
+      <c r="D34" s="125" t="s">
         <v>54</v>
       </c>
-      <c r="E34" s="139" t="s">
+      <c r="E34" s="133" t="s">
         <v>55</v>
       </c>
-      <c r="F34" s="140"/>
-      <c r="G34" s="141"/>
-      <c r="H34" s="145" t="s">
+      <c r="F34" s="134"/>
+      <c r="G34" s="135"/>
+      <c r="H34" s="139" t="s">
         <v>56</v>
       </c>
-      <c r="I34" s="146"/>
-      <c r="J34" s="146"/>
-      <c r="K34" s="146"/>
-      <c r="L34" s="146"/>
-      <c r="M34" s="146"/>
-      <c r="N34" s="146"/>
-      <c r="O34" s="146"/>
-      <c r="P34" s="146"/>
-      <c r="Q34" s="147"/>
+      <c r="I34" s="140"/>
+      <c r="J34" s="140"/>
+      <c r="K34" s="140"/>
+      <c r="L34" s="140"/>
+      <c r="M34" s="140"/>
+      <c r="N34" s="140"/>
+      <c r="O34" s="140"/>
+      <c r="P34" s="140"/>
+      <c r="Q34" s="141"/>
     </row>
     <row r="35" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B35" s="121"/>
-      <c r="C35" s="122"/>
-      <c r="D35" s="132"/>
-      <c r="E35" s="136" t="s">
+      <c r="B35" s="115"/>
+      <c r="C35" s="116"/>
+      <c r="D35" s="126"/>
+      <c r="E35" s="130" t="s">
         <v>96</v>
       </c>
-      <c r="F35" s="137"/>
-      <c r="G35" s="138"/>
+      <c r="F35" s="131"/>
+      <c r="G35" s="132"/>
       <c r="H35" s="67"/>
       <c r="I35" s="68"/>
       <c r="J35" s="68"/>
@@ -4601,9 +4490,9 @@
       <c r="Q35" s="69"/>
     </row>
     <row r="36" spans="2:28" ht="30.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B36" s="123"/>
-      <c r="C36" s="124"/>
-      <c r="D36" s="132"/>
+      <c r="B36" s="117"/>
+      <c r="C36" s="118"/>
+      <c r="D36" s="126"/>
       <c r="E36" s="85" t="s">
         <v>140</v>
       </c>
@@ -4645,10 +4534,10 @@
       </c>
     </row>
     <row r="37" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B37" s="128" t="s">
+      <c r="B37" s="122" t="s">
         <v>95</v>
       </c>
-      <c r="C37" s="125" t="s">
+      <c r="C37" s="119" t="s">
         <v>94</v>
       </c>
       <c r="D37" s="33" t="s">
@@ -4708,8 +4597,8 @@
       </c>
     </row>
     <row r="38" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B38" s="129"/>
-      <c r="C38" s="126"/>
+      <c r="B38" s="123"/>
+      <c r="C38" s="120"/>
       <c r="D38" s="26" t="s">
         <v>102</v>
       </c>
@@ -4763,8 +4652,8 @@
       <c r="AB38" s="19"/>
     </row>
     <row r="39" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B39" s="129"/>
-      <c r="C39" s="127"/>
+      <c r="B39" s="123"/>
+      <c r="C39" s="121"/>
       <c r="D39" s="83" t="s">
         <v>70</v>
       </c>
@@ -4818,7 +4707,7 @@
       <c r="AB39" s="19"/>
     </row>
     <row r="40" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B40" s="129"/>
+      <c r="B40" s="123"/>
       <c r="C40" s="36" t="s">
         <v>91</v>
       </c>
@@ -4874,8 +4763,8 @@
       </c>
     </row>
     <row r="41" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B41" s="129"/>
-      <c r="C41" s="125" t="s">
+      <c r="B41" s="123"/>
+      <c r="C41" s="119" t="s">
         <v>79</v>
       </c>
       <c r="D41" s="33" t="s">
@@ -4935,8 +4824,8 @@
       </c>
     </row>
     <row r="42" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B42" s="129"/>
-      <c r="C42" s="126"/>
+      <c r="B42" s="123"/>
+      <c r="C42" s="120"/>
       <c r="D42" s="26" t="s">
         <v>102</v>
       </c>
@@ -4990,8 +4879,8 @@
       <c r="AB42" s="19"/>
     </row>
     <row r="43" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B43" s="129"/>
-      <c r="C43" s="127"/>
+      <c r="B43" s="123"/>
+      <c r="C43" s="121"/>
       <c r="D43" s="83" t="s">
         <v>70</v>
       </c>
@@ -5045,7 +4934,7 @@
       <c r="AB43" s="19"/>
     </row>
     <row r="44" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B44" s="129"/>
+      <c r="B44" s="123"/>
       <c r="C44" s="36" t="s">
         <v>91</v>
       </c>
@@ -5101,8 +4990,8 @@
       </c>
     </row>
     <row r="45" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B45" s="129"/>
-      <c r="C45" s="125" t="s">
+      <c r="B45" s="123"/>
+      <c r="C45" s="119" t="s">
         <v>93</v>
       </c>
       <c r="D45" s="33" t="s">
@@ -5162,8 +5051,8 @@
       </c>
     </row>
     <row r="46" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B46" s="129"/>
-      <c r="C46" s="126"/>
+      <c r="B46" s="123"/>
+      <c r="C46" s="120"/>
       <c r="D46" s="26" t="s">
         <v>102</v>
       </c>
@@ -5217,8 +5106,8 @@
       <c r="AB46" s="19"/>
     </row>
     <row r="47" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B47" s="129"/>
-      <c r="C47" s="127"/>
+      <c r="B47" s="123"/>
+      <c r="C47" s="121"/>
       <c r="D47" s="83" t="s">
         <v>70</v>
       </c>
@@ -5272,7 +5161,7 @@
       <c r="AB47" s="19"/>
     </row>
     <row r="48" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B48" s="129"/>
+      <c r="B48" s="123"/>
       <c r="C48" s="36" t="s">
         <v>91</v>
       </c>
@@ -5328,14 +5217,14 @@
       </c>
     </row>
     <row r="49" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B49" s="129"/>
-      <c r="C49" s="125" t="s">
+      <c r="B49" s="123"/>
+      <c r="C49" s="119" t="s">
         <v>92</v>
       </c>
       <c r="D49" s="33" t="s">
         <v>143</v>
       </c>
-      <c r="E49" s="142"/>
+      <c r="E49" s="136"/>
       <c r="F49" s="87"/>
       <c r="G49" s="31"/>
       <c r="H49" s="64" t="e">
@@ -5380,12 +5269,12 @@
       </c>
     </row>
     <row r="50" spans="2:28" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B50" s="129"/>
-      <c r="C50" s="126"/>
+      <c r="B50" s="123"/>
+      <c r="C50" s="120"/>
       <c r="D50" s="26" t="s">
         <v>102</v>
       </c>
-      <c r="E50" s="143"/>
+      <c r="E50" s="137"/>
       <c r="F50" s="88"/>
       <c r="G50" s="28"/>
       <c r="H50" s="73">
@@ -5431,12 +5320,12 @@
       <c r="AB50" s="19"/>
     </row>
     <row r="51" spans="2:28" ht="18.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B51" s="129"/>
-      <c r="C51" s="127"/>
+      <c r="B51" s="123"/>
+      <c r="C51" s="121"/>
       <c r="D51" s="83" t="s">
         <v>70</v>
       </c>
-      <c r="E51" s="144"/>
+      <c r="E51" s="138"/>
       <c r="F51" s="89"/>
       <c r="G51" s="54"/>
       <c r="H51" s="75">
@@ -5482,7 +5371,7 @@
       <c r="AB51" s="19"/>
     </row>
     <row r="52" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B52" s="130"/>
+      <c r="B52" s="124"/>
       <c r="C52" s="32" t="s">
         <v>91</v>
       </c>

--- a/tool/track-aggregator/template/年度比較結果.xlsx
+++ b/tool/track-aggregator/template/年度比較結果.xlsx
@@ -8,18 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ishid\Desktop\project_management\tool\track-aggregator\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A4D5D3B-5DCD-46AA-BEE3-F9A955EBB6DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E3DDCFC-AB7E-411F-8E71-20B89197337C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="760" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="経年比較" sheetId="31" r:id="rId1"/>
-    <sheet name="経年比較（前年同じFMT）" sheetId="22" state="hidden" r:id="rId2"/>
-    <sheet name="ビジネス基礎（Day5)" sheetId="13" state="hidden" r:id="rId3"/>
+    <sheet name="経年比較-会社別" sheetId="32" r:id="rId2"/>
+    <sheet name="経年比較（前年同じFMT）" sheetId="22" state="hidden" r:id="rId3"/>
+    <sheet name="ビジネス基礎（Day5)" sheetId="13" state="hidden" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">経年比較!$B$2:$Q$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'経年比較（前年同じFMT）'!$B$2:$Q$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'経年比較（前年同じFMT）'!$B$2:$Q$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'経年比較-会社別'!$B$2:$R$6</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="151">
   <si>
     <t>目的達成</t>
     <rPh sb="0" eb="2">
@@ -870,6 +872,13 @@
   </si>
   <si>
     <t>{コースグループデータ}</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>会社名</t>
+    <rPh sb="0" eb="3">
+      <t>カイシャメイ</t>
+    </rPh>
     <phoneticPr fontId="3"/>
   </si>
 </sst>
@@ -2083,6 +2092,96 @@
     <xf numFmtId="177" fontId="12" fillId="6" borderId="42" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="46" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="11" fillId="0" borderId="44" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="11" fillId="0" borderId="41" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="11" fillId="0" borderId="42" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="11" fillId="0" borderId="43" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="11" fillId="0" borderId="42" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="16" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="15" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="23" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="39" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="22" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="45" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="40" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="18" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="21" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="52" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="53" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="54" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="27" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="30" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="32" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2101,15 +2200,6 @@
     <xf numFmtId="0" fontId="5" fillId="7" borderId="16" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="27" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="30" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="32" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="15" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
@@ -2168,87 +2258,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="179" fontId="5" fillId="8" borderId="20" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="46" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="11" fillId="0" borderId="44" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="11" fillId="0" borderId="41" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="11" fillId="0" borderId="42" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="11" fillId="0" borderId="43" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="11" fillId="0" borderId="42" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="16" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="15" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="23" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="39" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="22" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="45" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="40" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="18" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="21" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="52" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="53" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="54" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2258,7 +2267,7 @@
     <cellStyle name="標準" xfId="0" builtinId="0"/>
     <cellStyle name="標準 2" xfId="2" xr:uid="{35DECEAB-A874-4A31-B6F5-75B712B64A43}"/>
   </cellStyles>
-  <dxfs count="16">
+  <dxfs count="17">
     <dxf>
       <font>
         <color rgb="FFFF0000"/>
@@ -2380,6 +2389,16 @@
       <font>
         <color rgb="FFFF0000"/>
       </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -2715,55 +2734,55 @@
       </c>
     </row>
     <row r="2" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B2" s="148" t="s">
+      <c r="B2" s="119" t="s">
         <v>53</v>
       </c>
-      <c r="C2" s="149"/>
-      <c r="D2" s="154" t="s">
+      <c r="C2" s="120"/>
+      <c r="D2" s="125" t="s">
         <v>54</v>
       </c>
-      <c r="E2" s="157" t="s">
+      <c r="E2" s="128" t="s">
         <v>55</v>
       </c>
-      <c r="F2" s="158"/>
-      <c r="G2" s="159"/>
-      <c r="H2" s="164" t="s">
+      <c r="F2" s="129"/>
+      <c r="G2" s="130"/>
+      <c r="H2" s="134" t="s">
         <v>56</v>
       </c>
-      <c r="I2" s="163"/>
-      <c r="J2" s="163"/>
-      <c r="K2" s="163"/>
-      <c r="L2" s="163"/>
-      <c r="M2" s="163"/>
-      <c r="N2" s="163"/>
-      <c r="O2" s="163"/>
-      <c r="P2" s="163"/>
-      <c r="Q2" s="165"/>
+      <c r="I2" s="135"/>
+      <c r="J2" s="135"/>
+      <c r="K2" s="135"/>
+      <c r="L2" s="135"/>
+      <c r="M2" s="135"/>
+      <c r="N2" s="135"/>
+      <c r="O2" s="135"/>
+      <c r="P2" s="135"/>
+      <c r="Q2" s="136"/>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.45">
-      <c r="B3" s="150"/>
-      <c r="C3" s="151"/>
-      <c r="D3" s="155"/>
-      <c r="E3" s="160" t="s">
+      <c r="B3" s="121"/>
+      <c r="C3" s="122"/>
+      <c r="D3" s="126"/>
+      <c r="E3" s="131" t="s">
         <v>96</v>
       </c>
-      <c r="F3" s="161"/>
-      <c r="G3" s="162"/>
-      <c r="H3" s="166"/>
-      <c r="I3" s="167"/>
-      <c r="J3" s="167"/>
-      <c r="K3" s="167"/>
-      <c r="L3" s="167"/>
-      <c r="M3" s="167"/>
-      <c r="N3" s="167"/>
-      <c r="O3" s="167"/>
-      <c r="P3" s="167"/>
-      <c r="Q3" s="168"/>
+      <c r="F3" s="132"/>
+      <c r="G3" s="133"/>
+      <c r="H3" s="137"/>
+      <c r="I3" s="138"/>
+      <c r="J3" s="138"/>
+      <c r="K3" s="138"/>
+      <c r="L3" s="138"/>
+      <c r="M3" s="138"/>
+      <c r="N3" s="138"/>
+      <c r="O3" s="138"/>
+      <c r="P3" s="138"/>
+      <c r="Q3" s="139"/>
     </row>
     <row r="4" spans="1:19" ht="36.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B4" s="152"/>
-      <c r="C4" s="153"/>
-      <c r="D4" s="156"/>
+      <c r="B4" s="123"/>
+      <c r="C4" s="124"/>
+      <c r="D4" s="127"/>
       <c r="E4" s="103" t="s">
         <v>140</v>
       </c>
@@ -2809,20 +2828,20 @@
         <v>149</v>
       </c>
       <c r="C5" s="100"/>
-      <c r="D5" s="142"/>
-      <c r="E5" s="143"/>
-      <c r="F5" s="144"/>
-      <c r="G5" s="145"/>
-      <c r="H5" s="146"/>
-      <c r="I5" s="144"/>
-      <c r="J5" s="144"/>
-      <c r="K5" s="144"/>
-      <c r="L5" s="144"/>
-      <c r="M5" s="144"/>
-      <c r="N5" s="144"/>
-      <c r="O5" s="144"/>
-      <c r="P5" s="144"/>
-      <c r="Q5" s="147"/>
+      <c r="D5" s="113"/>
+      <c r="E5" s="114"/>
+      <c r="F5" s="115"/>
+      <c r="G5" s="116"/>
+      <c r="H5" s="117"/>
+      <c r="I5" s="115"/>
+      <c r="J5" s="115"/>
+      <c r="K5" s="115"/>
+      <c r="L5" s="115"/>
+      <c r="M5" s="115"/>
+      <c r="N5" s="115"/>
+      <c r="O5" s="115"/>
+      <c r="P5" s="115"/>
+      <c r="Q5" s="118"/>
       <c r="S5" s="95"/>
     </row>
     <row r="6" spans="1:19" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
@@ -2865,7 +2884,7 @@
   </mergeCells>
   <phoneticPr fontId="1"/>
   <conditionalFormatting sqref="H5:Q5">
-    <cfRule type="cellIs" dxfId="15" priority="1" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="16" priority="1" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2900,6 +2919,221 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{868F14A9-30FC-4B58-9081-A9045491D31C}">
+  <dimension ref="A1:T7"/>
+  <sheetFormatPr defaultColWidth="8.19921875" defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="2.59765625" style="93" customWidth="1"/>
+    <col min="2" max="2" width="2.796875" style="93" customWidth="1"/>
+    <col min="3" max="3" width="25.19921875" style="93" customWidth="1"/>
+    <col min="4" max="4" width="10.296875" style="93" customWidth="1"/>
+    <col min="5" max="5" width="40.69921875" style="93" customWidth="1"/>
+    <col min="6" max="7" width="10.69921875" style="94" customWidth="1"/>
+    <col min="8" max="8" width="10.69921875" style="93" customWidth="1"/>
+    <col min="9" max="9" width="14.19921875" style="93" bestFit="1" customWidth="1"/>
+    <col min="10" max="18" width="9.5" style="93" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="8.19921875" style="93"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:20" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A1" s="93" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B2" s="119" t="s">
+        <v>53</v>
+      </c>
+      <c r="C2" s="120"/>
+      <c r="D2" s="125" t="s">
+        <v>54</v>
+      </c>
+      <c r="E2" s="125" t="s">
+        <v>150</v>
+      </c>
+      <c r="F2" s="128" t="s">
+        <v>55</v>
+      </c>
+      <c r="G2" s="129"/>
+      <c r="H2" s="130"/>
+      <c r="I2" s="134" t="s">
+        <v>56</v>
+      </c>
+      <c r="J2" s="135"/>
+      <c r="K2" s="135"/>
+      <c r="L2" s="135"/>
+      <c r="M2" s="135"/>
+      <c r="N2" s="135"/>
+      <c r="O2" s="135"/>
+      <c r="P2" s="135"/>
+      <c r="Q2" s="135"/>
+      <c r="R2" s="136"/>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.45">
+      <c r="B3" s="121"/>
+      <c r="C3" s="122"/>
+      <c r="D3" s="126"/>
+      <c r="E3" s="126"/>
+      <c r="F3" s="131" t="s">
+        <v>96</v>
+      </c>
+      <c r="G3" s="132"/>
+      <c r="H3" s="133"/>
+      <c r="I3" s="137"/>
+      <c r="J3" s="138"/>
+      <c r="K3" s="138"/>
+      <c r="L3" s="138"/>
+      <c r="M3" s="138"/>
+      <c r="N3" s="138"/>
+      <c r="O3" s="138"/>
+      <c r="P3" s="138"/>
+      <c r="Q3" s="138"/>
+      <c r="R3" s="139"/>
+    </row>
+    <row r="4" spans="1:20" ht="36.6" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B4" s="123"/>
+      <c r="C4" s="124"/>
+      <c r="D4" s="127"/>
+      <c r="E4" s="127"/>
+      <c r="F4" s="103" t="s">
+        <v>140</v>
+      </c>
+      <c r="G4" s="104" t="s">
+        <v>147</v>
+      </c>
+      <c r="H4" s="105" t="s">
+        <v>57</v>
+      </c>
+      <c r="I4" s="106" t="s">
+        <v>58</v>
+      </c>
+      <c r="J4" s="107" t="s">
+        <v>59</v>
+      </c>
+      <c r="K4" s="107" t="s">
+        <v>60</v>
+      </c>
+      <c r="L4" s="107" t="s">
+        <v>139</v>
+      </c>
+      <c r="M4" s="107" t="s">
+        <v>61</v>
+      </c>
+      <c r="N4" s="107" t="s">
+        <v>62</v>
+      </c>
+      <c r="O4" s="107" t="s">
+        <v>63</v>
+      </c>
+      <c r="P4" s="107" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q4" s="107" t="s">
+        <v>65</v>
+      </c>
+      <c r="R4" s="108" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" ht="20.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B5" s="102" t="s">
+        <v>149</v>
+      </c>
+      <c r="C5" s="100"/>
+      <c r="D5" s="113"/>
+      <c r="E5" s="113"/>
+      <c r="F5" s="114"/>
+      <c r="G5" s="115"/>
+      <c r="H5" s="116"/>
+      <c r="I5" s="117"/>
+      <c r="J5" s="115"/>
+      <c r="K5" s="115"/>
+      <c r="L5" s="115"/>
+      <c r="M5" s="115"/>
+      <c r="N5" s="115"/>
+      <c r="O5" s="115"/>
+      <c r="P5" s="115"/>
+      <c r="Q5" s="115"/>
+      <c r="R5" s="118"/>
+      <c r="T5" s="95"/>
+    </row>
+    <row r="6" spans="1:20" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B6" s="98"/>
+      <c r="C6" s="101"/>
+      <c r="D6" s="109"/>
+      <c r="E6" s="109"/>
+      <c r="F6" s="110"/>
+      <c r="G6" s="111"/>
+      <c r="H6" s="112"/>
+      <c r="I6" s="99"/>
+      <c r="J6" s="96"/>
+      <c r="K6" s="96"/>
+      <c r="L6" s="96"/>
+      <c r="M6" s="96"/>
+      <c r="N6" s="96"/>
+      <c r="O6" s="96"/>
+      <c r="P6" s="96"/>
+      <c r="Q6" s="96"/>
+      <c r="R6" s="97"/>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.45">
+      <c r="I7" s="94"/>
+      <c r="J7" s="94"/>
+      <c r="K7" s="94"/>
+      <c r="L7" s="94"/>
+      <c r="M7" s="94"/>
+      <c r="N7" s="94"/>
+      <c r="O7" s="94"/>
+      <c r="P7" s="94"/>
+      <c r="Q7" s="94"/>
+      <c r="R7" s="94"/>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="B2:C4"/>
+    <mergeCell ref="D2:D4"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="I2:R3"/>
+    <mergeCell ref="F3:H3"/>
+    <mergeCell ref="E2:E4"/>
+  </mergeCells>
+  <phoneticPr fontId="1"/>
+  <conditionalFormatting sqref="I5:R5">
+    <cfRule type="cellIs" dxfId="15" priority="1" operator="lessThanOrEqual">
+      <formula>3.4</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
+      <x14:conditionalFormattings>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="2" id="{ACCDAD0A-AC6D-4186-8B65-90202760F29B}">
+            <x14:iconSet iconSet="3Arrows" custom="1">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num" gte="0">
+                <xm:f>-0.25</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>0.25</xm:f>
+              </x14:cfvo>
+              <x14:cfIcon iconSet="3Arrows" iconId="0"/>
+              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
+              <x14:cfIcon iconSet="3Arrows" iconId="2"/>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>I6:R6</xm:sqref>
+        </x14:conditionalFormatting>
+      </x14:conditionalFormattings>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5C06947-9AD3-4764-A00F-59E09793C545}">
   <sheetPr>
     <tabColor theme="8" tint="0.39997558519241921"/>
@@ -2920,40 +3154,40 @@
   <sheetData>
     <row r="1" spans="2:29" ht="15.6" thickBot="1" x14ac:dyDescent="0.5"/>
     <row r="2" spans="2:29" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B2" s="113" t="s">
+      <c r="B2" s="143" t="s">
         <v>53</v>
       </c>
-      <c r="C2" s="114"/>
-      <c r="D2" s="125" t="s">
+      <c r="C2" s="144"/>
+      <c r="D2" s="152" t="s">
         <v>54</v>
       </c>
-      <c r="E2" s="133" t="s">
+      <c r="E2" s="160" t="s">
         <v>55</v>
       </c>
-      <c r="F2" s="134"/>
-      <c r="G2" s="135"/>
-      <c r="H2" s="127" t="s">
+      <c r="F2" s="161"/>
+      <c r="G2" s="162"/>
+      <c r="H2" s="154" t="s">
         <v>56</v>
       </c>
-      <c r="I2" s="128"/>
-      <c r="J2" s="128"/>
-      <c r="K2" s="128"/>
-      <c r="L2" s="128"/>
-      <c r="M2" s="128"/>
-      <c r="N2" s="128"/>
-      <c r="O2" s="128"/>
-      <c r="P2" s="128"/>
-      <c r="Q2" s="129"/>
+      <c r="I2" s="155"/>
+      <c r="J2" s="155"/>
+      <c r="K2" s="155"/>
+      <c r="L2" s="155"/>
+      <c r="M2" s="155"/>
+      <c r="N2" s="155"/>
+      <c r="O2" s="155"/>
+      <c r="P2" s="155"/>
+      <c r="Q2" s="156"/>
     </row>
     <row r="3" spans="2:29" x14ac:dyDescent="0.45">
-      <c r="B3" s="115"/>
-      <c r="C3" s="116"/>
-      <c r="D3" s="126"/>
-      <c r="E3" s="130" t="s">
+      <c r="B3" s="145"/>
+      <c r="C3" s="146"/>
+      <c r="D3" s="153"/>
+      <c r="E3" s="157" t="s">
         <v>96</v>
       </c>
-      <c r="F3" s="131"/>
-      <c r="G3" s="132"/>
+      <c r="F3" s="158"/>
+      <c r="G3" s="159"/>
       <c r="H3" s="22"/>
       <c r="I3" s="21"/>
       <c r="J3" s="21"/>
@@ -2966,9 +3200,9 @@
       <c r="Q3" s="20"/>
     </row>
     <row r="4" spans="2:29" ht="30.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B4" s="117"/>
-      <c r="C4" s="118"/>
-      <c r="D4" s="126"/>
+      <c r="B4" s="147"/>
+      <c r="C4" s="148"/>
+      <c r="D4" s="153"/>
       <c r="E4" s="85" t="s">
         <v>140</v>
       </c>
@@ -3010,10 +3244,10 @@
       </c>
     </row>
     <row r="5" spans="2:29" x14ac:dyDescent="0.45">
-      <c r="B5" s="122" t="s">
+      <c r="B5" s="149" t="s">
         <v>89</v>
       </c>
-      <c r="C5" s="119" t="s">
+      <c r="C5" s="140" t="s">
         <v>137</v>
       </c>
       <c r="D5" s="33" t="s">
@@ -3067,8 +3301,8 @@
       </c>
     </row>
     <row r="6" spans="2:29" x14ac:dyDescent="0.45">
-      <c r="B6" s="123"/>
-      <c r="C6" s="120"/>
+      <c r="B6" s="150"/>
+      <c r="C6" s="141"/>
       <c r="D6" s="26" t="s">
         <v>102</v>
       </c>
@@ -3121,8 +3355,8 @@
       <c r="AC6" s="19"/>
     </row>
     <row r="7" spans="2:29" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B7" s="123"/>
-      <c r="C7" s="121"/>
+      <c r="B7" s="150"/>
+      <c r="C7" s="142"/>
       <c r="D7" s="83" t="s">
         <v>70</v>
       </c>
@@ -3173,7 +3407,7 @@
       <c r="AC7" s="19"/>
     </row>
     <row r="8" spans="2:29" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B8" s="123"/>
+      <c r="B8" s="150"/>
       <c r="C8" s="36" t="s">
         <v>91</v>
       </c>
@@ -3227,8 +3461,8 @@
       </c>
     </row>
     <row r="9" spans="2:29" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B9" s="123"/>
-      <c r="C9" s="119" t="s">
+      <c r="B9" s="150"/>
+      <c r="C9" s="140" t="s">
         <v>101</v>
       </c>
       <c r="D9" s="33" t="s">
@@ -3279,8 +3513,8 @@
       </c>
     </row>
     <row r="10" spans="2:29" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B10" s="123"/>
-      <c r="C10" s="120"/>
+      <c r="B10" s="150"/>
+      <c r="C10" s="141"/>
       <c r="D10" s="26" t="s">
         <v>102</v>
       </c>
@@ -3331,8 +3565,8 @@
       <c r="AC10" s="19"/>
     </row>
     <row r="11" spans="2:29" ht="15.6" hidden="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B11" s="123"/>
-      <c r="C11" s="121"/>
+      <c r="B11" s="150"/>
+      <c r="C11" s="142"/>
       <c r="D11" s="34" t="s">
         <v>70</v>
       </c>
@@ -3383,7 +3617,7 @@
       <c r="AC11" s="19"/>
     </row>
     <row r="12" spans="2:29" ht="15.6" hidden="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B12" s="123"/>
+      <c r="B12" s="150"/>
       <c r="C12" s="36" t="s">
         <v>91</v>
       </c>
@@ -3437,8 +3671,8 @@
       </c>
     </row>
     <row r="13" spans="2:29" x14ac:dyDescent="0.45">
-      <c r="B13" s="123"/>
-      <c r="C13" s="119" t="s">
+      <c r="B13" s="150"/>
+      <c r="C13" s="140" t="s">
         <v>142</v>
       </c>
       <c r="D13" s="33" t="s">
@@ -3489,8 +3723,8 @@
       </c>
     </row>
     <row r="14" spans="2:29" x14ac:dyDescent="0.45">
-      <c r="B14" s="123"/>
-      <c r="C14" s="120"/>
+      <c r="B14" s="150"/>
+      <c r="C14" s="141"/>
       <c r="D14" s="26" t="s">
         <v>102</v>
       </c>
@@ -3541,8 +3775,8 @@
       <c r="AC14" s="19"/>
     </row>
     <row r="15" spans="2:29" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B15" s="123"/>
-      <c r="C15" s="121"/>
+      <c r="B15" s="150"/>
+      <c r="C15" s="142"/>
       <c r="D15" s="83" t="s">
         <v>70</v>
       </c>
@@ -3593,7 +3827,7 @@
       <c r="AC15" s="19"/>
     </row>
     <row r="16" spans="2:29" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B16" s="124"/>
+      <c r="B16" s="151"/>
       <c r="C16" s="32" t="s">
         <v>91</v>
       </c>
@@ -3659,40 +3893,40 @@
       <c r="Q17" s="12"/>
     </row>
     <row r="18" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B18" s="113" t="s">
+      <c r="B18" s="143" t="s">
         <v>53</v>
       </c>
-      <c r="C18" s="114"/>
-      <c r="D18" s="125" t="s">
+      <c r="C18" s="144"/>
+      <c r="D18" s="152" t="s">
         <v>54</v>
       </c>
-      <c r="E18" s="133" t="s">
+      <c r="E18" s="160" t="s">
         <v>55</v>
       </c>
-      <c r="F18" s="134"/>
-      <c r="G18" s="135"/>
-      <c r="H18" s="139" t="s">
+      <c r="F18" s="161"/>
+      <c r="G18" s="162"/>
+      <c r="H18" s="166" t="s">
         <v>56</v>
       </c>
-      <c r="I18" s="140"/>
-      <c r="J18" s="140"/>
-      <c r="K18" s="140"/>
-      <c r="L18" s="140"/>
-      <c r="M18" s="140"/>
-      <c r="N18" s="140"/>
-      <c r="O18" s="140"/>
-      <c r="P18" s="140"/>
-      <c r="Q18" s="141"/>
+      <c r="I18" s="167"/>
+      <c r="J18" s="167"/>
+      <c r="K18" s="167"/>
+      <c r="L18" s="167"/>
+      <c r="M18" s="167"/>
+      <c r="N18" s="167"/>
+      <c r="O18" s="167"/>
+      <c r="P18" s="167"/>
+      <c r="Q18" s="168"/>
     </row>
     <row r="19" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B19" s="115"/>
-      <c r="C19" s="116"/>
-      <c r="D19" s="126"/>
-      <c r="E19" s="130" t="s">
+      <c r="B19" s="145"/>
+      <c r="C19" s="146"/>
+      <c r="D19" s="153"/>
+      <c r="E19" s="157" t="s">
         <v>96</v>
       </c>
-      <c r="F19" s="131"/>
-      <c r="G19" s="132"/>
+      <c r="F19" s="158"/>
+      <c r="G19" s="159"/>
       <c r="H19" s="67"/>
       <c r="I19" s="68"/>
       <c r="J19" s="68"/>
@@ -3705,9 +3939,9 @@
       <c r="Q19" s="69"/>
     </row>
     <row r="20" spans="2:28" ht="30.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B20" s="117"/>
-      <c r="C20" s="118"/>
-      <c r="D20" s="126"/>
+      <c r="B20" s="147"/>
+      <c r="C20" s="148"/>
+      <c r="D20" s="153"/>
       <c r="E20" s="85" t="s">
         <v>140</v>
       </c>
@@ -3749,10 +3983,10 @@
       </c>
     </row>
     <row r="21" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B21" s="122" t="s">
+      <c r="B21" s="149" t="s">
         <v>100</v>
       </c>
-      <c r="C21" s="119" t="s">
+      <c r="C21" s="140" t="s">
         <v>99</v>
       </c>
       <c r="D21" s="33" t="s">
@@ -3812,8 +4046,8 @@
       </c>
     </row>
     <row r="22" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B22" s="123"/>
-      <c r="C22" s="120"/>
+      <c r="B22" s="150"/>
+      <c r="C22" s="141"/>
       <c r="D22" s="26" t="s">
         <v>102</v>
       </c>
@@ -3867,8 +4101,8 @@
       <c r="AB22" s="19"/>
     </row>
     <row r="23" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B23" s="123"/>
-      <c r="C23" s="121"/>
+      <c r="B23" s="150"/>
+      <c r="C23" s="142"/>
       <c r="D23" s="83" t="s">
         <v>70</v>
       </c>
@@ -3922,7 +4156,7 @@
       <c r="AB23" s="19"/>
     </row>
     <row r="24" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B24" s="123"/>
+      <c r="B24" s="150"/>
       <c r="C24" s="36" t="s">
         <v>91</v>
       </c>
@@ -3978,8 +4212,8 @@
       </c>
     </row>
     <row r="25" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B25" s="123"/>
-      <c r="C25" s="119" t="s">
+      <c r="B25" s="150"/>
+      <c r="C25" s="140" t="s">
         <v>98</v>
       </c>
       <c r="D25" s="33" t="s">
@@ -4039,8 +4273,8 @@
       </c>
     </row>
     <row r="26" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B26" s="123"/>
-      <c r="C26" s="120"/>
+      <c r="B26" s="150"/>
+      <c r="C26" s="141"/>
       <c r="D26" s="26" t="s">
         <v>102</v>
       </c>
@@ -4094,8 +4328,8 @@
       <c r="AB26" s="19"/>
     </row>
     <row r="27" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B27" s="123"/>
-      <c r="C27" s="121"/>
+      <c r="B27" s="150"/>
+      <c r="C27" s="142"/>
       <c r="D27" s="83" t="s">
         <v>70</v>
       </c>
@@ -4149,7 +4383,7 @@
       <c r="AB27" s="19"/>
     </row>
     <row r="28" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B28" s="123"/>
+      <c r="B28" s="150"/>
       <c r="C28" s="36" t="s">
         <v>91</v>
       </c>
@@ -4205,8 +4439,8 @@
       </c>
     </row>
     <row r="29" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B29" s="123"/>
-      <c r="C29" s="119" t="s">
+      <c r="B29" s="150"/>
+      <c r="C29" s="140" t="s">
         <v>97</v>
       </c>
       <c r="D29" s="33" t="s">
@@ -4266,8 +4500,8 @@
       </c>
     </row>
     <row r="30" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B30" s="123"/>
-      <c r="C30" s="120"/>
+      <c r="B30" s="150"/>
+      <c r="C30" s="141"/>
       <c r="D30" s="26" t="s">
         <v>102</v>
       </c>
@@ -4321,8 +4555,8 @@
       <c r="AB30" s="19"/>
     </row>
     <row r="31" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B31" s="123"/>
-      <c r="C31" s="121"/>
+      <c r="B31" s="150"/>
+      <c r="C31" s="142"/>
       <c r="D31" s="83" t="s">
         <v>70</v>
       </c>
@@ -4376,7 +4610,7 @@
       <c r="AB31" s="19"/>
     </row>
     <row r="32" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B32" s="124"/>
+      <c r="B32" s="151"/>
       <c r="C32" s="32" t="s">
         <v>91</v>
       </c>
@@ -4444,40 +4678,40 @@
       <c r="Q33" s="12"/>
     </row>
     <row r="34" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B34" s="113" t="s">
+      <c r="B34" s="143" t="s">
         <v>53</v>
       </c>
-      <c r="C34" s="114"/>
-      <c r="D34" s="125" t="s">
+      <c r="C34" s="144"/>
+      <c r="D34" s="152" t="s">
         <v>54</v>
       </c>
-      <c r="E34" s="133" t="s">
+      <c r="E34" s="160" t="s">
         <v>55</v>
       </c>
-      <c r="F34" s="134"/>
-      <c r="G34" s="135"/>
-      <c r="H34" s="139" t="s">
+      <c r="F34" s="161"/>
+      <c r="G34" s="162"/>
+      <c r="H34" s="166" t="s">
         <v>56</v>
       </c>
-      <c r="I34" s="140"/>
-      <c r="J34" s="140"/>
-      <c r="K34" s="140"/>
-      <c r="L34" s="140"/>
-      <c r="M34" s="140"/>
-      <c r="N34" s="140"/>
-      <c r="O34" s="140"/>
-      <c r="P34" s="140"/>
-      <c r="Q34" s="141"/>
+      <c r="I34" s="167"/>
+      <c r="J34" s="167"/>
+      <c r="K34" s="167"/>
+      <c r="L34" s="167"/>
+      <c r="M34" s="167"/>
+      <c r="N34" s="167"/>
+      <c r="O34" s="167"/>
+      <c r="P34" s="167"/>
+      <c r="Q34" s="168"/>
     </row>
     <row r="35" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B35" s="115"/>
-      <c r="C35" s="116"/>
-      <c r="D35" s="126"/>
-      <c r="E35" s="130" t="s">
+      <c r="B35" s="145"/>
+      <c r="C35" s="146"/>
+      <c r="D35" s="153"/>
+      <c r="E35" s="157" t="s">
         <v>96</v>
       </c>
-      <c r="F35" s="131"/>
-      <c r="G35" s="132"/>
+      <c r="F35" s="158"/>
+      <c r="G35" s="159"/>
       <c r="H35" s="67"/>
       <c r="I35" s="68"/>
       <c r="J35" s="68"/>
@@ -4490,9 +4724,9 @@
       <c r="Q35" s="69"/>
     </row>
     <row r="36" spans="2:28" ht="30.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B36" s="117"/>
-      <c r="C36" s="118"/>
-      <c r="D36" s="126"/>
+      <c r="B36" s="147"/>
+      <c r="C36" s="148"/>
+      <c r="D36" s="153"/>
       <c r="E36" s="85" t="s">
         <v>140</v>
       </c>
@@ -4534,10 +4768,10 @@
       </c>
     </row>
     <row r="37" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B37" s="122" t="s">
+      <c r="B37" s="149" t="s">
         <v>95</v>
       </c>
-      <c r="C37" s="119" t="s">
+      <c r="C37" s="140" t="s">
         <v>94</v>
       </c>
       <c r="D37" s="33" t="s">
@@ -4597,8 +4831,8 @@
       </c>
     </row>
     <row r="38" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B38" s="123"/>
-      <c r="C38" s="120"/>
+      <c r="B38" s="150"/>
+      <c r="C38" s="141"/>
       <c r="D38" s="26" t="s">
         <v>102</v>
       </c>
@@ -4652,8 +4886,8 @@
       <c r="AB38" s="19"/>
     </row>
     <row r="39" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B39" s="123"/>
-      <c r="C39" s="121"/>
+      <c r="B39" s="150"/>
+      <c r="C39" s="142"/>
       <c r="D39" s="83" t="s">
         <v>70</v>
       </c>
@@ -4707,7 +4941,7 @@
       <c r="AB39" s="19"/>
     </row>
     <row r="40" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B40" s="123"/>
+      <c r="B40" s="150"/>
       <c r="C40" s="36" t="s">
         <v>91</v>
       </c>
@@ -4763,8 +4997,8 @@
       </c>
     </row>
     <row r="41" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B41" s="123"/>
-      <c r="C41" s="119" t="s">
+      <c r="B41" s="150"/>
+      <c r="C41" s="140" t="s">
         <v>79</v>
       </c>
       <c r="D41" s="33" t="s">
@@ -4824,8 +5058,8 @@
       </c>
     </row>
     <row r="42" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B42" s="123"/>
-      <c r="C42" s="120"/>
+      <c r="B42" s="150"/>
+      <c r="C42" s="141"/>
       <c r="D42" s="26" t="s">
         <v>102</v>
       </c>
@@ -4879,8 +5113,8 @@
       <c r="AB42" s="19"/>
     </row>
     <row r="43" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B43" s="123"/>
-      <c r="C43" s="121"/>
+      <c r="B43" s="150"/>
+      <c r="C43" s="142"/>
       <c r="D43" s="83" t="s">
         <v>70</v>
       </c>
@@ -4934,7 +5168,7 @@
       <c r="AB43" s="19"/>
     </row>
     <row r="44" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B44" s="123"/>
+      <c r="B44" s="150"/>
       <c r="C44" s="36" t="s">
         <v>91</v>
       </c>
@@ -4990,8 +5224,8 @@
       </c>
     </row>
     <row r="45" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B45" s="123"/>
-      <c r="C45" s="119" t="s">
+      <c r="B45" s="150"/>
+      <c r="C45" s="140" t="s">
         <v>93</v>
       </c>
       <c r="D45" s="33" t="s">
@@ -5051,8 +5285,8 @@
       </c>
     </row>
     <row r="46" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B46" s="123"/>
-      <c r="C46" s="120"/>
+      <c r="B46" s="150"/>
+      <c r="C46" s="141"/>
       <c r="D46" s="26" t="s">
         <v>102</v>
       </c>
@@ -5106,8 +5340,8 @@
       <c r="AB46" s="19"/>
     </row>
     <row r="47" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B47" s="123"/>
-      <c r="C47" s="121"/>
+      <c r="B47" s="150"/>
+      <c r="C47" s="142"/>
       <c r="D47" s="83" t="s">
         <v>70</v>
       </c>
@@ -5161,7 +5395,7 @@
       <c r="AB47" s="19"/>
     </row>
     <row r="48" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B48" s="123"/>
+      <c r="B48" s="150"/>
       <c r="C48" s="36" t="s">
         <v>91</v>
       </c>
@@ -5217,14 +5451,14 @@
       </c>
     </row>
     <row r="49" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B49" s="123"/>
-      <c r="C49" s="119" t="s">
+      <c r="B49" s="150"/>
+      <c r="C49" s="140" t="s">
         <v>92</v>
       </c>
       <c r="D49" s="33" t="s">
         <v>143</v>
       </c>
-      <c r="E49" s="136"/>
+      <c r="E49" s="163"/>
       <c r="F49" s="87"/>
       <c r="G49" s="31"/>
       <c r="H49" s="64" t="e">
@@ -5269,12 +5503,12 @@
       </c>
     </row>
     <row r="50" spans="2:28" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B50" s="123"/>
-      <c r="C50" s="120"/>
+      <c r="B50" s="150"/>
+      <c r="C50" s="141"/>
       <c r="D50" s="26" t="s">
         <v>102</v>
       </c>
-      <c r="E50" s="137"/>
+      <c r="E50" s="164"/>
       <c r="F50" s="88"/>
       <c r="G50" s="28"/>
       <c r="H50" s="73">
@@ -5320,12 +5554,12 @@
       <c r="AB50" s="19"/>
     </row>
     <row r="51" spans="2:28" ht="18.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B51" s="123"/>
-      <c r="C51" s="121"/>
+      <c r="B51" s="150"/>
+      <c r="C51" s="142"/>
       <c r="D51" s="83" t="s">
         <v>70</v>
       </c>
-      <c r="E51" s="138"/>
+      <c r="E51" s="165"/>
       <c r="F51" s="89"/>
       <c r="G51" s="54"/>
       <c r="H51" s="75">
@@ -5371,7 +5605,7 @@
       <c r="AB51" s="19"/>
     </row>
     <row r="52" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B52" s="124"/>
+      <c r="B52" s="151"/>
       <c r="C52" s="32" t="s">
         <v>91</v>
       </c>
@@ -5823,12 +6057,16 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="C41:C43"/>
-    <mergeCell ref="C45:C47"/>
-    <mergeCell ref="C49:C51"/>
-    <mergeCell ref="B34:C36"/>
-    <mergeCell ref="B37:B52"/>
-    <mergeCell ref="C37:C39"/>
+    <mergeCell ref="B2:C4"/>
+    <mergeCell ref="C9:C11"/>
+    <mergeCell ref="C13:C15"/>
+    <mergeCell ref="C21:C23"/>
+    <mergeCell ref="B18:C20"/>
+    <mergeCell ref="B5:B16"/>
+    <mergeCell ref="B21:B32"/>
+    <mergeCell ref="C5:C7"/>
+    <mergeCell ref="C29:C31"/>
+    <mergeCell ref="C25:C27"/>
     <mergeCell ref="D2:D4"/>
     <mergeCell ref="H2:Q2"/>
     <mergeCell ref="E3:G3"/>
@@ -5842,16 +6080,12 @@
     <mergeCell ref="D18:D20"/>
     <mergeCell ref="E18:G18"/>
     <mergeCell ref="E19:G19"/>
-    <mergeCell ref="B2:C4"/>
-    <mergeCell ref="C9:C11"/>
-    <mergeCell ref="C13:C15"/>
-    <mergeCell ref="C21:C23"/>
-    <mergeCell ref="B18:C20"/>
-    <mergeCell ref="B5:B16"/>
-    <mergeCell ref="B21:B32"/>
-    <mergeCell ref="C5:C7"/>
-    <mergeCell ref="C29:C31"/>
-    <mergeCell ref="C25:C27"/>
+    <mergeCell ref="C41:C43"/>
+    <mergeCell ref="C45:C47"/>
+    <mergeCell ref="C49:C51"/>
+    <mergeCell ref="B34:C36"/>
+    <mergeCell ref="B37:B52"/>
+    <mergeCell ref="C37:C39"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <conditionalFormatting sqref="H5:Q7">
@@ -5959,7 +6193,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <tabColor theme="4" tint="0.39997558519241921"/>

--- a/tool/track-aggregator/template/年度比較結果.xlsx
+++ b/tool/track-aggregator/template/年度比較結果.xlsx
@@ -8,19 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ishid\Desktop\project_management\tool\track-aggregator\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E3DDCFC-AB7E-411F-8E71-20B89197337C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E61876E-413C-4206-8206-2E069F9A715A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="760" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="経年比較" sheetId="31" r:id="rId1"/>
     <sheet name="経年比較-会社別" sheetId="32" r:id="rId2"/>
-    <sheet name="経年比較（前年同じFMT）" sheetId="22" state="hidden" r:id="rId3"/>
-    <sheet name="ビジネス基礎（Day5)" sheetId="13" state="hidden" r:id="rId4"/>
+    <sheet name="経年比較-ランク別" sheetId="33" r:id="rId3"/>
+    <sheet name="経年比較（前年同じFMT）" sheetId="22" state="hidden" r:id="rId4"/>
+    <sheet name="ビジネス基礎（Day5)" sheetId="13" state="hidden" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">経年比較!$B$2:$Q$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'経年比較（前年同じFMT）'!$B$2:$Q$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'経年比較（前年同じFMT）'!$B$2:$Q$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'経年比較-ランク別'!$B$2:$R$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'経年比較-会社別'!$B$2:$R$6</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -33,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="152">
   <si>
     <t>目的達成</t>
     <rPh sb="0" eb="2">
@@ -879,6 +881,10 @@
     <rPh sb="0" eb="3">
       <t>カイシャメイ</t>
     </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>ランク</t>
     <phoneticPr fontId="3"/>
   </si>
 </sst>
@@ -1752,7 +1758,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="169">
+  <cellXfs count="171">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2053,12 +2059,6 @@
     <xf numFmtId="179" fontId="12" fillId="6" borderId="43" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="7" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
@@ -2259,6 +2259,18 @@
     </xf>
     <xf numFmtId="179" fontId="5" fillId="8" borderId="20" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="15" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -2267,7 +2279,7 @@
     <cellStyle name="標準" xfId="0" builtinId="0"/>
     <cellStyle name="標準 2" xfId="2" xr:uid="{35DECEAB-A874-4A31-B6F5-75B712B64A43}"/>
   </cellStyles>
-  <dxfs count="17">
+  <dxfs count="18">
     <dxf>
       <font>
         <color rgb="FFFF0000"/>
@@ -2389,6 +2401,16 @@
       <font>
         <color rgb="FFFF0000"/>
       </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -2719,7 +2741,7 @@
   <cols>
     <col min="1" max="1" width="2.59765625" style="93" customWidth="1"/>
     <col min="2" max="2" width="2.796875" style="93" customWidth="1"/>
-    <col min="3" max="3" width="25.19921875" style="93" customWidth="1"/>
+    <col min="3" max="3" width="30.69921875" style="93" customWidth="1"/>
     <col min="4" max="4" width="10.296875" style="93" customWidth="1"/>
     <col min="5" max="6" width="10.69921875" style="94" customWidth="1"/>
     <col min="7" max="7" width="10.69921875" style="93" customWidth="1"/>
@@ -2734,123 +2756,123 @@
       </c>
     </row>
     <row r="2" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B2" s="119" t="s">
+      <c r="B2" s="117" t="s">
         <v>53</v>
       </c>
-      <c r="C2" s="120"/>
-      <c r="D2" s="125" t="s">
+      <c r="C2" s="118"/>
+      <c r="D2" s="123" t="s">
         <v>54</v>
       </c>
-      <c r="E2" s="128" t="s">
+      <c r="E2" s="126" t="s">
         <v>55</v>
       </c>
-      <c r="F2" s="129"/>
-      <c r="G2" s="130"/>
-      <c r="H2" s="134" t="s">
+      <c r="F2" s="127"/>
+      <c r="G2" s="128"/>
+      <c r="H2" s="132" t="s">
         <v>56</v>
       </c>
-      <c r="I2" s="135"/>
-      <c r="J2" s="135"/>
-      <c r="K2" s="135"/>
-      <c r="L2" s="135"/>
-      <c r="M2" s="135"/>
-      <c r="N2" s="135"/>
-      <c r="O2" s="135"/>
-      <c r="P2" s="135"/>
-      <c r="Q2" s="136"/>
+      <c r="I2" s="133"/>
+      <c r="J2" s="133"/>
+      <c r="K2" s="133"/>
+      <c r="L2" s="133"/>
+      <c r="M2" s="133"/>
+      <c r="N2" s="133"/>
+      <c r="O2" s="133"/>
+      <c r="P2" s="133"/>
+      <c r="Q2" s="134"/>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.45">
-      <c r="B3" s="121"/>
-      <c r="C3" s="122"/>
-      <c r="D3" s="126"/>
-      <c r="E3" s="131" t="s">
+      <c r="B3" s="119"/>
+      <c r="C3" s="120"/>
+      <c r="D3" s="124"/>
+      <c r="E3" s="129" t="s">
         <v>96</v>
       </c>
-      <c r="F3" s="132"/>
-      <c r="G3" s="133"/>
-      <c r="H3" s="137"/>
-      <c r="I3" s="138"/>
-      <c r="J3" s="138"/>
-      <c r="K3" s="138"/>
-      <c r="L3" s="138"/>
-      <c r="M3" s="138"/>
-      <c r="N3" s="138"/>
-      <c r="O3" s="138"/>
-      <c r="P3" s="138"/>
-      <c r="Q3" s="139"/>
+      <c r="F3" s="130"/>
+      <c r="G3" s="131"/>
+      <c r="H3" s="135"/>
+      <c r="I3" s="136"/>
+      <c r="J3" s="136"/>
+      <c r="K3" s="136"/>
+      <c r="L3" s="136"/>
+      <c r="M3" s="136"/>
+      <c r="N3" s="136"/>
+      <c r="O3" s="136"/>
+      <c r="P3" s="136"/>
+      <c r="Q3" s="137"/>
     </row>
     <row r="4" spans="1:19" ht="36.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B4" s="123"/>
-      <c r="C4" s="124"/>
-      <c r="D4" s="127"/>
-      <c r="E4" s="103" t="s">
+      <c r="B4" s="121"/>
+      <c r="C4" s="122"/>
+      <c r="D4" s="125"/>
+      <c r="E4" s="101" t="s">
         <v>140</v>
       </c>
-      <c r="F4" s="104" t="s">
+      <c r="F4" s="102" t="s">
         <v>147</v>
       </c>
-      <c r="G4" s="105" t="s">
+      <c r="G4" s="103" t="s">
         <v>57</v>
       </c>
-      <c r="H4" s="106" t="s">
+      <c r="H4" s="104" t="s">
         <v>58</v>
       </c>
-      <c r="I4" s="107" t="s">
+      <c r="I4" s="105" t="s">
         <v>59</v>
       </c>
-      <c r="J4" s="107" t="s">
+      <c r="J4" s="105" t="s">
         <v>60</v>
       </c>
-      <c r="K4" s="107" t="s">
+      <c r="K4" s="105" t="s">
         <v>139</v>
       </c>
-      <c r="L4" s="107" t="s">
+      <c r="L4" s="105" t="s">
         <v>61</v>
       </c>
-      <c r="M4" s="107" t="s">
+      <c r="M4" s="105" t="s">
         <v>62</v>
       </c>
-      <c r="N4" s="107" t="s">
+      <c r="N4" s="105" t="s">
         <v>63</v>
       </c>
-      <c r="O4" s="107" t="s">
+      <c r="O4" s="105" t="s">
         <v>64</v>
       </c>
-      <c r="P4" s="107" t="s">
+      <c r="P4" s="105" t="s">
         <v>65</v>
       </c>
-      <c r="Q4" s="108" t="s">
+      <c r="Q4" s="106" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="20.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B5" s="102" t="s">
+      <c r="B5" s="100" t="s">
         <v>149</v>
       </c>
-      <c r="C5" s="100"/>
-      <c r="D5" s="113"/>
-      <c r="E5" s="114"/>
-      <c r="F5" s="115"/>
-      <c r="G5" s="116"/>
-      <c r="H5" s="117"/>
-      <c r="I5" s="115"/>
-      <c r="J5" s="115"/>
-      <c r="K5" s="115"/>
-      <c r="L5" s="115"/>
-      <c r="M5" s="115"/>
-      <c r="N5" s="115"/>
-      <c r="O5" s="115"/>
-      <c r="P5" s="115"/>
-      <c r="Q5" s="118"/>
+      <c r="C5" s="169"/>
+      <c r="D5" s="111"/>
+      <c r="E5" s="112"/>
+      <c r="F5" s="113"/>
+      <c r="G5" s="114"/>
+      <c r="H5" s="115"/>
+      <c r="I5" s="113"/>
+      <c r="J5" s="113"/>
+      <c r="K5" s="113"/>
+      <c r="L5" s="113"/>
+      <c r="M5" s="113"/>
+      <c r="N5" s="113"/>
+      <c r="O5" s="113"/>
+      <c r="P5" s="113"/>
+      <c r="Q5" s="116"/>
       <c r="S5" s="95"/>
     </row>
     <row r="6" spans="1:19" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B6" s="98"/>
-      <c r="C6" s="101"/>
-      <c r="D6" s="109"/>
-      <c r="E6" s="110"/>
-      <c r="F6" s="111"/>
-      <c r="G6" s="112"/>
+      <c r="C6" s="170"/>
+      <c r="D6" s="107"/>
+      <c r="E6" s="108"/>
+      <c r="F6" s="109"/>
+      <c r="G6" s="110"/>
       <c r="H6" s="99"/>
       <c r="I6" s="96"/>
       <c r="J6" s="96"/>
@@ -2884,7 +2906,7 @@
   </mergeCells>
   <phoneticPr fontId="1"/>
   <conditionalFormatting sqref="H5:Q5">
-    <cfRule type="cellIs" dxfId="16" priority="1" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="17" priority="1" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2925,9 +2947,9 @@
   <cols>
     <col min="1" max="1" width="2.59765625" style="93" customWidth="1"/>
     <col min="2" max="2" width="2.796875" style="93" customWidth="1"/>
-    <col min="3" max="3" width="25.19921875" style="93" customWidth="1"/>
-    <col min="4" max="4" width="10.296875" style="93" customWidth="1"/>
-    <col min="5" max="5" width="40.69921875" style="93" customWidth="1"/>
+    <col min="3" max="3" width="30.69921875" style="93" customWidth="1"/>
+    <col min="4" max="4" width="40.69921875" style="93" customWidth="1"/>
+    <col min="5" max="5" width="10.296875" style="93" customWidth="1"/>
     <col min="6" max="7" width="10.69921875" style="94" customWidth="1"/>
     <col min="8" max="8" width="10.69921875" style="93" customWidth="1"/>
     <col min="9" max="9" width="14.19921875" style="93" bestFit="1" customWidth="1"/>
@@ -2941,130 +2963,130 @@
       </c>
     </row>
     <row r="2" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B2" s="119" t="s">
+      <c r="B2" s="117" t="s">
         <v>53</v>
       </c>
-      <c r="C2" s="120"/>
-      <c r="D2" s="125" t="s">
+      <c r="C2" s="118"/>
+      <c r="D2" s="123" t="s">
+        <v>150</v>
+      </c>
+      <c r="E2" s="123" t="s">
         <v>54</v>
       </c>
-      <c r="E2" s="125" t="s">
-        <v>150</v>
-      </c>
-      <c r="F2" s="128" t="s">
+      <c r="F2" s="126" t="s">
         <v>55</v>
       </c>
-      <c r="G2" s="129"/>
-      <c r="H2" s="130"/>
-      <c r="I2" s="134" t="s">
+      <c r="G2" s="127"/>
+      <c r="H2" s="128"/>
+      <c r="I2" s="132" t="s">
         <v>56</v>
       </c>
-      <c r="J2" s="135"/>
-      <c r="K2" s="135"/>
-      <c r="L2" s="135"/>
-      <c r="M2" s="135"/>
-      <c r="N2" s="135"/>
-      <c r="O2" s="135"/>
-      <c r="P2" s="135"/>
-      <c r="Q2" s="135"/>
-      <c r="R2" s="136"/>
+      <c r="J2" s="133"/>
+      <c r="K2" s="133"/>
+      <c r="L2" s="133"/>
+      <c r="M2" s="133"/>
+      <c r="N2" s="133"/>
+      <c r="O2" s="133"/>
+      <c r="P2" s="133"/>
+      <c r="Q2" s="133"/>
+      <c r="R2" s="134"/>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.45">
-      <c r="B3" s="121"/>
-      <c r="C3" s="122"/>
-      <c r="D3" s="126"/>
-      <c r="E3" s="126"/>
-      <c r="F3" s="131" t="s">
+      <c r="B3" s="119"/>
+      <c r="C3" s="120"/>
+      <c r="D3" s="124"/>
+      <c r="E3" s="124"/>
+      <c r="F3" s="129" t="s">
         <v>96</v>
       </c>
-      <c r="G3" s="132"/>
-      <c r="H3" s="133"/>
-      <c r="I3" s="137"/>
-      <c r="J3" s="138"/>
-      <c r="K3" s="138"/>
-      <c r="L3" s="138"/>
-      <c r="M3" s="138"/>
-      <c r="N3" s="138"/>
-      <c r="O3" s="138"/>
-      <c r="P3" s="138"/>
-      <c r="Q3" s="138"/>
-      <c r="R3" s="139"/>
+      <c r="G3" s="130"/>
+      <c r="H3" s="131"/>
+      <c r="I3" s="135"/>
+      <c r="J3" s="136"/>
+      <c r="K3" s="136"/>
+      <c r="L3" s="136"/>
+      <c r="M3" s="136"/>
+      <c r="N3" s="136"/>
+      <c r="O3" s="136"/>
+      <c r="P3" s="136"/>
+      <c r="Q3" s="136"/>
+      <c r="R3" s="137"/>
     </row>
     <row r="4" spans="1:20" ht="36.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B4" s="123"/>
-      <c r="C4" s="124"/>
-      <c r="D4" s="127"/>
-      <c r="E4" s="127"/>
-      <c r="F4" s="103" t="s">
+      <c r="B4" s="121"/>
+      <c r="C4" s="122"/>
+      <c r="D4" s="125"/>
+      <c r="E4" s="125"/>
+      <c r="F4" s="101" t="s">
         <v>140</v>
       </c>
-      <c r="G4" s="104" t="s">
+      <c r="G4" s="102" t="s">
         <v>147</v>
       </c>
-      <c r="H4" s="105" t="s">
+      <c r="H4" s="103" t="s">
         <v>57</v>
       </c>
-      <c r="I4" s="106" t="s">
+      <c r="I4" s="104" t="s">
         <v>58</v>
       </c>
-      <c r="J4" s="107" t="s">
+      <c r="J4" s="105" t="s">
         <v>59</v>
       </c>
-      <c r="K4" s="107" t="s">
+      <c r="K4" s="105" t="s">
         <v>60</v>
       </c>
-      <c r="L4" s="107" t="s">
+      <c r="L4" s="105" t="s">
         <v>139</v>
       </c>
-      <c r="M4" s="107" t="s">
+      <c r="M4" s="105" t="s">
         <v>61</v>
       </c>
-      <c r="N4" s="107" t="s">
+      <c r="N4" s="105" t="s">
         <v>62</v>
       </c>
-      <c r="O4" s="107" t="s">
+      <c r="O4" s="105" t="s">
         <v>63</v>
       </c>
-      <c r="P4" s="107" t="s">
+      <c r="P4" s="105" t="s">
         <v>64</v>
       </c>
-      <c r="Q4" s="107" t="s">
+      <c r="Q4" s="105" t="s">
         <v>65</v>
       </c>
-      <c r="R4" s="108" t="s">
+      <c r="R4" s="106" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="5" spans="1:20" ht="20.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B5" s="102" t="s">
+      <c r="B5" s="100" t="s">
         <v>149</v>
       </c>
-      <c r="C5" s="100"/>
-      <c r="D5" s="113"/>
-      <c r="E5" s="113"/>
-      <c r="F5" s="114"/>
-      <c r="G5" s="115"/>
-      <c r="H5" s="116"/>
-      <c r="I5" s="117"/>
-      <c r="J5" s="115"/>
-      <c r="K5" s="115"/>
-      <c r="L5" s="115"/>
-      <c r="M5" s="115"/>
-      <c r="N5" s="115"/>
-      <c r="O5" s="115"/>
-      <c r="P5" s="115"/>
-      <c r="Q5" s="115"/>
-      <c r="R5" s="118"/>
+      <c r="C5" s="169"/>
+      <c r="D5" s="167"/>
+      <c r="E5" s="111"/>
+      <c r="F5" s="112"/>
+      <c r="G5" s="113"/>
+      <c r="H5" s="114"/>
+      <c r="I5" s="115"/>
+      <c r="J5" s="113"/>
+      <c r="K5" s="113"/>
+      <c r="L5" s="113"/>
+      <c r="M5" s="113"/>
+      <c r="N5" s="113"/>
+      <c r="O5" s="113"/>
+      <c r="P5" s="113"/>
+      <c r="Q5" s="113"/>
+      <c r="R5" s="116"/>
       <c r="T5" s="95"/>
     </row>
     <row r="6" spans="1:20" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B6" s="98"/>
-      <c r="C6" s="101"/>
-      <c r="D6" s="109"/>
-      <c r="E6" s="109"/>
-      <c r="F6" s="110"/>
-      <c r="G6" s="111"/>
-      <c r="H6" s="112"/>
+      <c r="C6" s="170"/>
+      <c r="D6" s="168"/>
+      <c r="E6" s="107"/>
+      <c r="F6" s="108"/>
+      <c r="G6" s="109"/>
+      <c r="H6" s="110"/>
       <c r="I6" s="99"/>
       <c r="J6" s="96"/>
       <c r="K6" s="96"/>
@@ -3091,15 +3113,15 @@
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="B2:C4"/>
-    <mergeCell ref="D2:D4"/>
+    <mergeCell ref="E2:E4"/>
     <mergeCell ref="F2:H2"/>
     <mergeCell ref="I2:R3"/>
     <mergeCell ref="F3:H3"/>
-    <mergeCell ref="E2:E4"/>
+    <mergeCell ref="D2:D4"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <conditionalFormatting sqref="I5:R5">
-    <cfRule type="cellIs" dxfId="15" priority="1" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="16" priority="1" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3134,6 +3156,221 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D0D5B12-79D9-42EC-8039-D2A663034F34}">
+  <dimension ref="A1:T7"/>
+  <sheetFormatPr defaultColWidth="8.19921875" defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="2.59765625" style="93" customWidth="1"/>
+    <col min="2" max="2" width="2.796875" style="93" customWidth="1"/>
+    <col min="3" max="3" width="30.69921875" style="93" customWidth="1"/>
+    <col min="4" max="4" width="13.3984375" style="93" customWidth="1"/>
+    <col min="5" max="5" width="10.296875" style="93" customWidth="1"/>
+    <col min="6" max="7" width="10.69921875" style="94" customWidth="1"/>
+    <col min="8" max="8" width="10.69921875" style="93" customWidth="1"/>
+    <col min="9" max="9" width="14.19921875" style="93" bestFit="1" customWidth="1"/>
+    <col min="10" max="18" width="9.5" style="93" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="8.19921875" style="93"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:20" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A1" s="93" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B2" s="117" t="s">
+        <v>53</v>
+      </c>
+      <c r="C2" s="118"/>
+      <c r="D2" s="123" t="s">
+        <v>151</v>
+      </c>
+      <c r="E2" s="123" t="s">
+        <v>54</v>
+      </c>
+      <c r="F2" s="126" t="s">
+        <v>55</v>
+      </c>
+      <c r="G2" s="127"/>
+      <c r="H2" s="128"/>
+      <c r="I2" s="132" t="s">
+        <v>56</v>
+      </c>
+      <c r="J2" s="133"/>
+      <c r="K2" s="133"/>
+      <c r="L2" s="133"/>
+      <c r="M2" s="133"/>
+      <c r="N2" s="133"/>
+      <c r="O2" s="133"/>
+      <c r="P2" s="133"/>
+      <c r="Q2" s="133"/>
+      <c r="R2" s="134"/>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.45">
+      <c r="B3" s="119"/>
+      <c r="C3" s="120"/>
+      <c r="D3" s="124"/>
+      <c r="E3" s="124"/>
+      <c r="F3" s="129" t="s">
+        <v>96</v>
+      </c>
+      <c r="G3" s="130"/>
+      <c r="H3" s="131"/>
+      <c r="I3" s="135"/>
+      <c r="J3" s="136"/>
+      <c r="K3" s="136"/>
+      <c r="L3" s="136"/>
+      <c r="M3" s="136"/>
+      <c r="N3" s="136"/>
+      <c r="O3" s="136"/>
+      <c r="P3" s="136"/>
+      <c r="Q3" s="136"/>
+      <c r="R3" s="137"/>
+    </row>
+    <row r="4" spans="1:20" ht="36.6" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B4" s="121"/>
+      <c r="C4" s="122"/>
+      <c r="D4" s="125"/>
+      <c r="E4" s="125"/>
+      <c r="F4" s="101" t="s">
+        <v>140</v>
+      </c>
+      <c r="G4" s="102" t="s">
+        <v>147</v>
+      </c>
+      <c r="H4" s="103" t="s">
+        <v>57</v>
+      </c>
+      <c r="I4" s="104" t="s">
+        <v>58</v>
+      </c>
+      <c r="J4" s="105" t="s">
+        <v>59</v>
+      </c>
+      <c r="K4" s="105" t="s">
+        <v>60</v>
+      </c>
+      <c r="L4" s="105" t="s">
+        <v>139</v>
+      </c>
+      <c r="M4" s="105" t="s">
+        <v>61</v>
+      </c>
+      <c r="N4" s="105" t="s">
+        <v>62</v>
+      </c>
+      <c r="O4" s="105" t="s">
+        <v>63</v>
+      </c>
+      <c r="P4" s="105" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q4" s="105" t="s">
+        <v>65</v>
+      </c>
+      <c r="R4" s="106" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" ht="20.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B5" s="100" t="s">
+        <v>149</v>
+      </c>
+      <c r="C5" s="169"/>
+      <c r="D5" s="167"/>
+      <c r="E5" s="111"/>
+      <c r="F5" s="112"/>
+      <c r="G5" s="113"/>
+      <c r="H5" s="114"/>
+      <c r="I5" s="115"/>
+      <c r="J5" s="113"/>
+      <c r="K5" s="113"/>
+      <c r="L5" s="113"/>
+      <c r="M5" s="113"/>
+      <c r="N5" s="113"/>
+      <c r="O5" s="113"/>
+      <c r="P5" s="113"/>
+      <c r="Q5" s="113"/>
+      <c r="R5" s="116"/>
+      <c r="T5" s="95"/>
+    </row>
+    <row r="6" spans="1:20" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B6" s="98"/>
+      <c r="C6" s="170"/>
+      <c r="D6" s="168"/>
+      <c r="E6" s="107"/>
+      <c r="F6" s="108"/>
+      <c r="G6" s="109"/>
+      <c r="H6" s="110"/>
+      <c r="I6" s="99"/>
+      <c r="J6" s="96"/>
+      <c r="K6" s="96"/>
+      <c r="L6" s="96"/>
+      <c r="M6" s="96"/>
+      <c r="N6" s="96"/>
+      <c r="O6" s="96"/>
+      <c r="P6" s="96"/>
+      <c r="Q6" s="96"/>
+      <c r="R6" s="97"/>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.45">
+      <c r="I7" s="94"/>
+      <c r="J7" s="94"/>
+      <c r="K7" s="94"/>
+      <c r="L7" s="94"/>
+      <c r="M7" s="94"/>
+      <c r="N7" s="94"/>
+      <c r="O7" s="94"/>
+      <c r="P7" s="94"/>
+      <c r="Q7" s="94"/>
+      <c r="R7" s="94"/>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="B2:C4"/>
+    <mergeCell ref="E2:E4"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="I2:R3"/>
+    <mergeCell ref="F3:H3"/>
+    <mergeCell ref="D2:D4"/>
+  </mergeCells>
+  <phoneticPr fontId="1"/>
+  <conditionalFormatting sqref="I5:R5">
+    <cfRule type="cellIs" dxfId="15" priority="1" operator="lessThanOrEqual">
+      <formula>3.4</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
+      <x14:conditionalFormattings>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="2" id="{E3CFEB59-5C73-49AB-BE2A-0F88EC39808A}">
+            <x14:iconSet iconSet="3Arrows" custom="1">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num" gte="0">
+                <xm:f>-0.25</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>0.25</xm:f>
+              </x14:cfvo>
+              <x14:cfIcon iconSet="3Arrows" iconId="0"/>
+              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
+              <x14:cfIcon iconSet="3Arrows" iconId="2"/>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>I6:R6</xm:sqref>
+        </x14:conditionalFormatting>
+      </x14:conditionalFormattings>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5C06947-9AD3-4764-A00F-59E09793C545}">
   <sheetPr>
     <tabColor theme="8" tint="0.39997558519241921"/>
@@ -3154,40 +3391,40 @@
   <sheetData>
     <row r="1" spans="2:29" ht="15.6" thickBot="1" x14ac:dyDescent="0.5"/>
     <row r="2" spans="2:29" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B2" s="143" t="s">
+      <c r="B2" s="141" t="s">
         <v>53</v>
       </c>
-      <c r="C2" s="144"/>
-      <c r="D2" s="152" t="s">
+      <c r="C2" s="142"/>
+      <c r="D2" s="150" t="s">
         <v>54</v>
       </c>
-      <c r="E2" s="160" t="s">
+      <c r="E2" s="158" t="s">
         <v>55</v>
       </c>
-      <c r="F2" s="161"/>
-      <c r="G2" s="162"/>
-      <c r="H2" s="154" t="s">
+      <c r="F2" s="159"/>
+      <c r="G2" s="160"/>
+      <c r="H2" s="152" t="s">
         <v>56</v>
       </c>
-      <c r="I2" s="155"/>
-      <c r="J2" s="155"/>
-      <c r="K2" s="155"/>
-      <c r="L2" s="155"/>
-      <c r="M2" s="155"/>
-      <c r="N2" s="155"/>
-      <c r="O2" s="155"/>
-      <c r="P2" s="155"/>
-      <c r="Q2" s="156"/>
+      <c r="I2" s="153"/>
+      <c r="J2" s="153"/>
+      <c r="K2" s="153"/>
+      <c r="L2" s="153"/>
+      <c r="M2" s="153"/>
+      <c r="N2" s="153"/>
+      <c r="O2" s="153"/>
+      <c r="P2" s="153"/>
+      <c r="Q2" s="154"/>
     </row>
     <row r="3" spans="2:29" x14ac:dyDescent="0.45">
-      <c r="B3" s="145"/>
-      <c r="C3" s="146"/>
-      <c r="D3" s="153"/>
-      <c r="E3" s="157" t="s">
+      <c r="B3" s="143"/>
+      <c r="C3" s="144"/>
+      <c r="D3" s="151"/>
+      <c r="E3" s="155" t="s">
         <v>96</v>
       </c>
-      <c r="F3" s="158"/>
-      <c r="G3" s="159"/>
+      <c r="F3" s="156"/>
+      <c r="G3" s="157"/>
       <c r="H3" s="22"/>
       <c r="I3" s="21"/>
       <c r="J3" s="21"/>
@@ -3200,9 +3437,9 @@
       <c r="Q3" s="20"/>
     </row>
     <row r="4" spans="2:29" ht="30.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B4" s="147"/>
-      <c r="C4" s="148"/>
-      <c r="D4" s="153"/>
+      <c r="B4" s="145"/>
+      <c r="C4" s="146"/>
+      <c r="D4" s="151"/>
       <c r="E4" s="85" t="s">
         <v>140</v>
       </c>
@@ -3244,10 +3481,10 @@
       </c>
     </row>
     <row r="5" spans="2:29" x14ac:dyDescent="0.45">
-      <c r="B5" s="149" t="s">
+      <c r="B5" s="147" t="s">
         <v>89</v>
       </c>
-      <c r="C5" s="140" t="s">
+      <c r="C5" s="138" t="s">
         <v>137</v>
       </c>
       <c r="D5" s="33" t="s">
@@ -3301,8 +3538,8 @@
       </c>
     </row>
     <row r="6" spans="2:29" x14ac:dyDescent="0.45">
-      <c r="B6" s="150"/>
-      <c r="C6" s="141"/>
+      <c r="B6" s="148"/>
+      <c r="C6" s="139"/>
       <c r="D6" s="26" t="s">
         <v>102</v>
       </c>
@@ -3355,8 +3592,8 @@
       <c r="AC6" s="19"/>
     </row>
     <row r="7" spans="2:29" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B7" s="150"/>
-      <c r="C7" s="142"/>
+      <c r="B7" s="148"/>
+      <c r="C7" s="140"/>
       <c r="D7" s="83" t="s">
         <v>70</v>
       </c>
@@ -3407,7 +3644,7 @@
       <c r="AC7" s="19"/>
     </row>
     <row r="8" spans="2:29" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B8" s="150"/>
+      <c r="B8" s="148"/>
       <c r="C8" s="36" t="s">
         <v>91</v>
       </c>
@@ -3461,8 +3698,8 @@
       </c>
     </row>
     <row r="9" spans="2:29" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B9" s="150"/>
-      <c r="C9" s="140" t="s">
+      <c r="B9" s="148"/>
+      <c r="C9" s="138" t="s">
         <v>101</v>
       </c>
       <c r="D9" s="33" t="s">
@@ -3513,8 +3750,8 @@
       </c>
     </row>
     <row r="10" spans="2:29" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B10" s="150"/>
-      <c r="C10" s="141"/>
+      <c r="B10" s="148"/>
+      <c r="C10" s="139"/>
       <c r="D10" s="26" t="s">
         <v>102</v>
       </c>
@@ -3565,8 +3802,8 @@
       <c r="AC10" s="19"/>
     </row>
     <row r="11" spans="2:29" ht="15.6" hidden="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B11" s="150"/>
-      <c r="C11" s="142"/>
+      <c r="B11" s="148"/>
+      <c r="C11" s="140"/>
       <c r="D11" s="34" t="s">
         <v>70</v>
       </c>
@@ -3617,7 +3854,7 @@
       <c r="AC11" s="19"/>
     </row>
     <row r="12" spans="2:29" ht="15.6" hidden="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B12" s="150"/>
+      <c r="B12" s="148"/>
       <c r="C12" s="36" t="s">
         <v>91</v>
       </c>
@@ -3671,8 +3908,8 @@
       </c>
     </row>
     <row r="13" spans="2:29" x14ac:dyDescent="0.45">
-      <c r="B13" s="150"/>
-      <c r="C13" s="140" t="s">
+      <c r="B13" s="148"/>
+      <c r="C13" s="138" t="s">
         <v>142</v>
       </c>
       <c r="D13" s="33" t="s">
@@ -3723,8 +3960,8 @@
       </c>
     </row>
     <row r="14" spans="2:29" x14ac:dyDescent="0.45">
-      <c r="B14" s="150"/>
-      <c r="C14" s="141"/>
+      <c r="B14" s="148"/>
+      <c r="C14" s="139"/>
       <c r="D14" s="26" t="s">
         <v>102</v>
       </c>
@@ -3775,8 +4012,8 @@
       <c r="AC14" s="19"/>
     </row>
     <row r="15" spans="2:29" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B15" s="150"/>
-      <c r="C15" s="142"/>
+      <c r="B15" s="148"/>
+      <c r="C15" s="140"/>
       <c r="D15" s="83" t="s">
         <v>70</v>
       </c>
@@ -3827,7 +4064,7 @@
       <c r="AC15" s="19"/>
     </row>
     <row r="16" spans="2:29" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B16" s="151"/>
+      <c r="B16" s="149"/>
       <c r="C16" s="32" t="s">
         <v>91</v>
       </c>
@@ -3893,40 +4130,40 @@
       <c r="Q17" s="12"/>
     </row>
     <row r="18" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B18" s="143" t="s">
+      <c r="B18" s="141" t="s">
         <v>53</v>
       </c>
-      <c r="C18" s="144"/>
-      <c r="D18" s="152" t="s">
+      <c r="C18" s="142"/>
+      <c r="D18" s="150" t="s">
         <v>54</v>
       </c>
-      <c r="E18" s="160" t="s">
+      <c r="E18" s="158" t="s">
         <v>55</v>
       </c>
-      <c r="F18" s="161"/>
-      <c r="G18" s="162"/>
-      <c r="H18" s="166" t="s">
+      <c r="F18" s="159"/>
+      <c r="G18" s="160"/>
+      <c r="H18" s="164" t="s">
         <v>56</v>
       </c>
-      <c r="I18" s="167"/>
-      <c r="J18" s="167"/>
-      <c r="K18" s="167"/>
-      <c r="L18" s="167"/>
-      <c r="M18" s="167"/>
-      <c r="N18" s="167"/>
-      <c r="O18" s="167"/>
-      <c r="P18" s="167"/>
-      <c r="Q18" s="168"/>
+      <c r="I18" s="165"/>
+      <c r="J18" s="165"/>
+      <c r="K18" s="165"/>
+      <c r="L18" s="165"/>
+      <c r="M18" s="165"/>
+      <c r="N18" s="165"/>
+      <c r="O18" s="165"/>
+      <c r="P18" s="165"/>
+      <c r="Q18" s="166"/>
     </row>
     <row r="19" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B19" s="145"/>
-      <c r="C19" s="146"/>
-      <c r="D19" s="153"/>
-      <c r="E19" s="157" t="s">
+      <c r="B19" s="143"/>
+      <c r="C19" s="144"/>
+      <c r="D19" s="151"/>
+      <c r="E19" s="155" t="s">
         <v>96</v>
       </c>
-      <c r="F19" s="158"/>
-      <c r="G19" s="159"/>
+      <c r="F19" s="156"/>
+      <c r="G19" s="157"/>
       <c r="H19" s="67"/>
       <c r="I19" s="68"/>
       <c r="J19" s="68"/>
@@ -3939,9 +4176,9 @@
       <c r="Q19" s="69"/>
     </row>
     <row r="20" spans="2:28" ht="30.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B20" s="147"/>
-      <c r="C20" s="148"/>
-      <c r="D20" s="153"/>
+      <c r="B20" s="145"/>
+      <c r="C20" s="146"/>
+      <c r="D20" s="151"/>
       <c r="E20" s="85" t="s">
         <v>140</v>
       </c>
@@ -3983,10 +4220,10 @@
       </c>
     </row>
     <row r="21" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B21" s="149" t="s">
+      <c r="B21" s="147" t="s">
         <v>100</v>
       </c>
-      <c r="C21" s="140" t="s">
+      <c r="C21" s="138" t="s">
         <v>99</v>
       </c>
       <c r="D21" s="33" t="s">
@@ -4046,8 +4283,8 @@
       </c>
     </row>
     <row r="22" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B22" s="150"/>
-      <c r="C22" s="141"/>
+      <c r="B22" s="148"/>
+      <c r="C22" s="139"/>
       <c r="D22" s="26" t="s">
         <v>102</v>
       </c>
@@ -4101,8 +4338,8 @@
       <c r="AB22" s="19"/>
     </row>
     <row r="23" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B23" s="150"/>
-      <c r="C23" s="142"/>
+      <c r="B23" s="148"/>
+      <c r="C23" s="140"/>
       <c r="D23" s="83" t="s">
         <v>70</v>
       </c>
@@ -4156,7 +4393,7 @@
       <c r="AB23" s="19"/>
     </row>
     <row r="24" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B24" s="150"/>
+      <c r="B24" s="148"/>
       <c r="C24" s="36" t="s">
         <v>91</v>
       </c>
@@ -4212,8 +4449,8 @@
       </c>
     </row>
     <row r="25" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B25" s="150"/>
-      <c r="C25" s="140" t="s">
+      <c r="B25" s="148"/>
+      <c r="C25" s="138" t="s">
         <v>98</v>
       </c>
       <c r="D25" s="33" t="s">
@@ -4273,8 +4510,8 @@
       </c>
     </row>
     <row r="26" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B26" s="150"/>
-      <c r="C26" s="141"/>
+      <c r="B26" s="148"/>
+      <c r="C26" s="139"/>
       <c r="D26" s="26" t="s">
         <v>102</v>
       </c>
@@ -4328,8 +4565,8 @@
       <c r="AB26" s="19"/>
     </row>
     <row r="27" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B27" s="150"/>
-      <c r="C27" s="142"/>
+      <c r="B27" s="148"/>
+      <c r="C27" s="140"/>
       <c r="D27" s="83" t="s">
         <v>70</v>
       </c>
@@ -4383,7 +4620,7 @@
       <c r="AB27" s="19"/>
     </row>
     <row r="28" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B28" s="150"/>
+      <c r="B28" s="148"/>
       <c r="C28" s="36" t="s">
         <v>91</v>
       </c>
@@ -4439,8 +4676,8 @@
       </c>
     </row>
     <row r="29" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B29" s="150"/>
-      <c r="C29" s="140" t="s">
+      <c r="B29" s="148"/>
+      <c r="C29" s="138" t="s">
         <v>97</v>
       </c>
       <c r="D29" s="33" t="s">
@@ -4500,8 +4737,8 @@
       </c>
     </row>
     <row r="30" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B30" s="150"/>
-      <c r="C30" s="141"/>
+      <c r="B30" s="148"/>
+      <c r="C30" s="139"/>
       <c r="D30" s="26" t="s">
         <v>102</v>
       </c>
@@ -4555,8 +4792,8 @@
       <c r="AB30" s="19"/>
     </row>
     <row r="31" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B31" s="150"/>
-      <c r="C31" s="142"/>
+      <c r="B31" s="148"/>
+      <c r="C31" s="140"/>
       <c r="D31" s="83" t="s">
         <v>70</v>
       </c>
@@ -4610,7 +4847,7 @@
       <c r="AB31" s="19"/>
     </row>
     <row r="32" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B32" s="151"/>
+      <c r="B32" s="149"/>
       <c r="C32" s="32" t="s">
         <v>91</v>
       </c>
@@ -4678,40 +4915,40 @@
       <c r="Q33" s="12"/>
     </row>
     <row r="34" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B34" s="143" t="s">
+      <c r="B34" s="141" t="s">
         <v>53</v>
       </c>
-      <c r="C34" s="144"/>
-      <c r="D34" s="152" t="s">
+      <c r="C34" s="142"/>
+      <c r="D34" s="150" t="s">
         <v>54</v>
       </c>
-      <c r="E34" s="160" t="s">
+      <c r="E34" s="158" t="s">
         <v>55</v>
       </c>
-      <c r="F34" s="161"/>
-      <c r="G34" s="162"/>
-      <c r="H34" s="166" t="s">
+      <c r="F34" s="159"/>
+      <c r="G34" s="160"/>
+      <c r="H34" s="164" t="s">
         <v>56</v>
       </c>
-      <c r="I34" s="167"/>
-      <c r="J34" s="167"/>
-      <c r="K34" s="167"/>
-      <c r="L34" s="167"/>
-      <c r="M34" s="167"/>
-      <c r="N34" s="167"/>
-      <c r="O34" s="167"/>
-      <c r="P34" s="167"/>
-      <c r="Q34" s="168"/>
+      <c r="I34" s="165"/>
+      <c r="J34" s="165"/>
+      <c r="K34" s="165"/>
+      <c r="L34" s="165"/>
+      <c r="M34" s="165"/>
+      <c r="N34" s="165"/>
+      <c r="O34" s="165"/>
+      <c r="P34" s="165"/>
+      <c r="Q34" s="166"/>
     </row>
     <row r="35" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B35" s="145"/>
-      <c r="C35" s="146"/>
-      <c r="D35" s="153"/>
-      <c r="E35" s="157" t="s">
+      <c r="B35" s="143"/>
+      <c r="C35" s="144"/>
+      <c r="D35" s="151"/>
+      <c r="E35" s="155" t="s">
         <v>96</v>
       </c>
-      <c r="F35" s="158"/>
-      <c r="G35" s="159"/>
+      <c r="F35" s="156"/>
+      <c r="G35" s="157"/>
       <c r="H35" s="67"/>
       <c r="I35" s="68"/>
       <c r="J35" s="68"/>
@@ -4724,9 +4961,9 @@
       <c r="Q35" s="69"/>
     </row>
     <row r="36" spans="2:28" ht="30.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B36" s="147"/>
-      <c r="C36" s="148"/>
-      <c r="D36" s="153"/>
+      <c r="B36" s="145"/>
+      <c r="C36" s="146"/>
+      <c r="D36" s="151"/>
       <c r="E36" s="85" t="s">
         <v>140</v>
       </c>
@@ -4768,10 +5005,10 @@
       </c>
     </row>
     <row r="37" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B37" s="149" t="s">
+      <c r="B37" s="147" t="s">
         <v>95</v>
       </c>
-      <c r="C37" s="140" t="s">
+      <c r="C37" s="138" t="s">
         <v>94</v>
       </c>
       <c r="D37" s="33" t="s">
@@ -4831,8 +5068,8 @@
       </c>
     </row>
     <row r="38" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B38" s="150"/>
-      <c r="C38" s="141"/>
+      <c r="B38" s="148"/>
+      <c r="C38" s="139"/>
       <c r="D38" s="26" t="s">
         <v>102</v>
       </c>
@@ -4886,8 +5123,8 @@
       <c r="AB38" s="19"/>
     </row>
     <row r="39" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B39" s="150"/>
-      <c r="C39" s="142"/>
+      <c r="B39" s="148"/>
+      <c r="C39" s="140"/>
       <c r="D39" s="83" t="s">
         <v>70</v>
       </c>
@@ -4941,7 +5178,7 @@
       <c r="AB39" s="19"/>
     </row>
     <row r="40" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B40" s="150"/>
+      <c r="B40" s="148"/>
       <c r="C40" s="36" t="s">
         <v>91</v>
       </c>
@@ -4997,8 +5234,8 @@
       </c>
     </row>
     <row r="41" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B41" s="150"/>
-      <c r="C41" s="140" t="s">
+      <c r="B41" s="148"/>
+      <c r="C41" s="138" t="s">
         <v>79</v>
       </c>
       <c r="D41" s="33" t="s">
@@ -5058,8 +5295,8 @@
       </c>
     </row>
     <row r="42" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B42" s="150"/>
-      <c r="C42" s="141"/>
+      <c r="B42" s="148"/>
+      <c r="C42" s="139"/>
       <c r="D42" s="26" t="s">
         <v>102</v>
       </c>
@@ -5113,8 +5350,8 @@
       <c r="AB42" s="19"/>
     </row>
     <row r="43" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B43" s="150"/>
-      <c r="C43" s="142"/>
+      <c r="B43" s="148"/>
+      <c r="C43" s="140"/>
       <c r="D43" s="83" t="s">
         <v>70</v>
       </c>
@@ -5168,7 +5405,7 @@
       <c r="AB43" s="19"/>
     </row>
     <row r="44" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B44" s="150"/>
+      <c r="B44" s="148"/>
       <c r="C44" s="36" t="s">
         <v>91</v>
       </c>
@@ -5224,8 +5461,8 @@
       </c>
     </row>
     <row r="45" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B45" s="150"/>
-      <c r="C45" s="140" t="s">
+      <c r="B45" s="148"/>
+      <c r="C45" s="138" t="s">
         <v>93</v>
       </c>
       <c r="D45" s="33" t="s">
@@ -5285,8 +5522,8 @@
       </c>
     </row>
     <row r="46" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B46" s="150"/>
-      <c r="C46" s="141"/>
+      <c r="B46" s="148"/>
+      <c r="C46" s="139"/>
       <c r="D46" s="26" t="s">
         <v>102</v>
       </c>
@@ -5340,8 +5577,8 @@
       <c r="AB46" s="19"/>
     </row>
     <row r="47" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B47" s="150"/>
-      <c r="C47" s="142"/>
+      <c r="B47" s="148"/>
+      <c r="C47" s="140"/>
       <c r="D47" s="83" t="s">
         <v>70</v>
       </c>
@@ -5395,7 +5632,7 @@
       <c r="AB47" s="19"/>
     </row>
     <row r="48" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B48" s="150"/>
+      <c r="B48" s="148"/>
       <c r="C48" s="36" t="s">
         <v>91</v>
       </c>
@@ -5451,14 +5688,14 @@
       </c>
     </row>
     <row r="49" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B49" s="150"/>
-      <c r="C49" s="140" t="s">
+      <c r="B49" s="148"/>
+      <c r="C49" s="138" t="s">
         <v>92</v>
       </c>
       <c r="D49" s="33" t="s">
         <v>143</v>
       </c>
-      <c r="E49" s="163"/>
+      <c r="E49" s="161"/>
       <c r="F49" s="87"/>
       <c r="G49" s="31"/>
       <c r="H49" s="64" t="e">
@@ -5503,12 +5740,12 @@
       </c>
     </row>
     <row r="50" spans="2:28" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B50" s="150"/>
-      <c r="C50" s="141"/>
+      <c r="B50" s="148"/>
+      <c r="C50" s="139"/>
       <c r="D50" s="26" t="s">
         <v>102</v>
       </c>
-      <c r="E50" s="164"/>
+      <c r="E50" s="162"/>
       <c r="F50" s="88"/>
       <c r="G50" s="28"/>
       <c r="H50" s="73">
@@ -5554,12 +5791,12 @@
       <c r="AB50" s="19"/>
     </row>
     <row r="51" spans="2:28" ht="18.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B51" s="150"/>
-      <c r="C51" s="142"/>
+      <c r="B51" s="148"/>
+      <c r="C51" s="140"/>
       <c r="D51" s="83" t="s">
         <v>70</v>
       </c>
-      <c r="E51" s="165"/>
+      <c r="E51" s="163"/>
       <c r="F51" s="89"/>
       <c r="G51" s="54"/>
       <c r="H51" s="75">
@@ -5605,7 +5842,7 @@
       <c r="AB51" s="19"/>
     </row>
     <row r="52" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B52" s="151"/>
+      <c r="B52" s="149"/>
       <c r="C52" s="32" t="s">
         <v>91</v>
       </c>
@@ -6193,7 +6430,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <tabColor theme="4" tint="0.39997558519241921"/>

--- a/tool/track-aggregator/template/年度比較結果.xlsx
+++ b/tool/track-aggregator/template/年度比較結果.xlsx
@@ -8,20 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ishid\Desktop\project_management\tool\track-aggregator\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E61876E-413C-4206-8206-2E069F9A715A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B70F2EC-B76F-4FFB-9F18-86FA2EEF6F2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="760" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="経年比較" sheetId="31" r:id="rId1"/>
     <sheet name="経年比較-会社別" sheetId="32" r:id="rId2"/>
     <sheet name="経年比較-ランク別" sheetId="33" r:id="rId3"/>
-    <sheet name="経年比較（前年同じFMT）" sheetId="22" state="hidden" r:id="rId4"/>
-    <sheet name="ビジネス基礎（Day5)" sheetId="13" state="hidden" r:id="rId5"/>
+    <sheet name="経年比較-クラス別" sheetId="34" r:id="rId4"/>
+    <sheet name="経年比較（前年同じFMT）" sheetId="22" state="hidden" r:id="rId5"/>
+    <sheet name="ビジネス基礎（Day5)" sheetId="13" state="hidden" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">経年比較!$B$2:$Q$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'経年比較（前年同じFMT）'!$B$2:$Q$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'経年比較（前年同じFMT）'!$B$2:$Q$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'経年比較-クラス別'!$B$2:$R$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'経年比較-ランク別'!$B$2:$R$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'経年比較-会社別'!$B$2:$R$6</definedName>
   </definedNames>
@@ -35,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="153">
   <si>
     <t>目的達成</t>
     <rPh sb="0" eb="2">
@@ -885,6 +887,10 @@
   </si>
   <si>
     <t>ランク</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>クラス</t>
     <phoneticPr fontId="3"/>
   </si>
 </sst>
@@ -2110,6 +2116,18 @@
     <xf numFmtId="179" fontId="11" fillId="0" borderId="42" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="15" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="7" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2173,6 +2191,24 @@
     <xf numFmtId="0" fontId="10" fillId="8" borderId="54" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="16" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="27" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2182,24 +2218,6 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="32" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="16" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="15" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
@@ -2259,18 +2277,6 @@
     </xf>
     <xf numFmtId="179" fontId="5" fillId="8" borderId="20" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="15" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -2279,7 +2285,17 @@
     <cellStyle name="標準" xfId="0" builtinId="0"/>
     <cellStyle name="標準 2" xfId="2" xr:uid="{35DECEAB-A874-4A31-B6F5-75B712B64A43}"/>
   </cellStyles>
-  <dxfs count="18">
+  <dxfs count="19">
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FFFF0000"/>
@@ -2756,55 +2772,55 @@
       </c>
     </row>
     <row r="2" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B2" s="117" t="s">
+      <c r="B2" s="121" t="s">
         <v>53</v>
       </c>
-      <c r="C2" s="118"/>
-      <c r="D2" s="123" t="s">
+      <c r="C2" s="122"/>
+      <c r="D2" s="127" t="s">
         <v>54</v>
       </c>
-      <c r="E2" s="126" t="s">
+      <c r="E2" s="130" t="s">
         <v>55</v>
       </c>
-      <c r="F2" s="127"/>
-      <c r="G2" s="128"/>
-      <c r="H2" s="132" t="s">
+      <c r="F2" s="131"/>
+      <c r="G2" s="132"/>
+      <c r="H2" s="136" t="s">
         <v>56</v>
       </c>
-      <c r="I2" s="133"/>
-      <c r="J2" s="133"/>
-      <c r="K2" s="133"/>
-      <c r="L2" s="133"/>
-      <c r="M2" s="133"/>
-      <c r="N2" s="133"/>
-      <c r="O2" s="133"/>
-      <c r="P2" s="133"/>
-      <c r="Q2" s="134"/>
+      <c r="I2" s="137"/>
+      <c r="J2" s="137"/>
+      <c r="K2" s="137"/>
+      <c r="L2" s="137"/>
+      <c r="M2" s="137"/>
+      <c r="N2" s="137"/>
+      <c r="O2" s="137"/>
+      <c r="P2" s="137"/>
+      <c r="Q2" s="138"/>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.45">
-      <c r="B3" s="119"/>
-      <c r="C3" s="120"/>
-      <c r="D3" s="124"/>
-      <c r="E3" s="129" t="s">
+      <c r="B3" s="123"/>
+      <c r="C3" s="124"/>
+      <c r="D3" s="128"/>
+      <c r="E3" s="133" t="s">
         <v>96</v>
       </c>
-      <c r="F3" s="130"/>
-      <c r="G3" s="131"/>
-      <c r="H3" s="135"/>
-      <c r="I3" s="136"/>
-      <c r="J3" s="136"/>
-      <c r="K3" s="136"/>
-      <c r="L3" s="136"/>
-      <c r="M3" s="136"/>
-      <c r="N3" s="136"/>
-      <c r="O3" s="136"/>
-      <c r="P3" s="136"/>
-      <c r="Q3" s="137"/>
+      <c r="F3" s="134"/>
+      <c r="G3" s="135"/>
+      <c r="H3" s="139"/>
+      <c r="I3" s="140"/>
+      <c r="J3" s="140"/>
+      <c r="K3" s="140"/>
+      <c r="L3" s="140"/>
+      <c r="M3" s="140"/>
+      <c r="N3" s="140"/>
+      <c r="O3" s="140"/>
+      <c r="P3" s="140"/>
+      <c r="Q3" s="141"/>
     </row>
     <row r="4" spans="1:19" ht="36.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B4" s="121"/>
-      <c r="C4" s="122"/>
-      <c r="D4" s="125"/>
+      <c r="B4" s="125"/>
+      <c r="C4" s="126"/>
+      <c r="D4" s="129"/>
       <c r="E4" s="101" t="s">
         <v>140</v>
       </c>
@@ -2849,7 +2865,7 @@
       <c r="B5" s="100" t="s">
         <v>149</v>
       </c>
-      <c r="C5" s="169"/>
+      <c r="C5" s="119"/>
       <c r="D5" s="111"/>
       <c r="E5" s="112"/>
       <c r="F5" s="113"/>
@@ -2868,7 +2884,7 @@
     </row>
     <row r="6" spans="1:19" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B6" s="98"/>
-      <c r="C6" s="170"/>
+      <c r="C6" s="120"/>
       <c r="D6" s="107"/>
       <c r="E6" s="108"/>
       <c r="F6" s="109"/>
@@ -2906,7 +2922,7 @@
   </mergeCells>
   <phoneticPr fontId="1"/>
   <conditionalFormatting sqref="H5:Q5">
-    <cfRule type="cellIs" dxfId="17" priority="1" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="18" priority="1" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2963,60 +2979,60 @@
       </c>
     </row>
     <row r="2" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B2" s="117" t="s">
+      <c r="B2" s="121" t="s">
         <v>53</v>
       </c>
-      <c r="C2" s="118"/>
-      <c r="D2" s="123" t="s">
+      <c r="C2" s="122"/>
+      <c r="D2" s="127" t="s">
         <v>150</v>
       </c>
-      <c r="E2" s="123" t="s">
+      <c r="E2" s="127" t="s">
         <v>54</v>
       </c>
-      <c r="F2" s="126" t="s">
+      <c r="F2" s="130" t="s">
         <v>55</v>
       </c>
-      <c r="G2" s="127"/>
-      <c r="H2" s="128"/>
-      <c r="I2" s="132" t="s">
+      <c r="G2" s="131"/>
+      <c r="H2" s="132"/>
+      <c r="I2" s="136" t="s">
         <v>56</v>
       </c>
-      <c r="J2" s="133"/>
-      <c r="K2" s="133"/>
-      <c r="L2" s="133"/>
-      <c r="M2" s="133"/>
-      <c r="N2" s="133"/>
-      <c r="O2" s="133"/>
-      <c r="P2" s="133"/>
-      <c r="Q2" s="133"/>
-      <c r="R2" s="134"/>
+      <c r="J2" s="137"/>
+      <c r="K2" s="137"/>
+      <c r="L2" s="137"/>
+      <c r="M2" s="137"/>
+      <c r="N2" s="137"/>
+      <c r="O2" s="137"/>
+      <c r="P2" s="137"/>
+      <c r="Q2" s="137"/>
+      <c r="R2" s="138"/>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.45">
-      <c r="B3" s="119"/>
-      <c r="C3" s="120"/>
-      <c r="D3" s="124"/>
-      <c r="E3" s="124"/>
-      <c r="F3" s="129" t="s">
+      <c r="B3" s="123"/>
+      <c r="C3" s="124"/>
+      <c r="D3" s="128"/>
+      <c r="E3" s="128"/>
+      <c r="F3" s="133" t="s">
         <v>96</v>
       </c>
-      <c r="G3" s="130"/>
-      <c r="H3" s="131"/>
-      <c r="I3" s="135"/>
-      <c r="J3" s="136"/>
-      <c r="K3" s="136"/>
-      <c r="L3" s="136"/>
-      <c r="M3" s="136"/>
-      <c r="N3" s="136"/>
-      <c r="O3" s="136"/>
-      <c r="P3" s="136"/>
-      <c r="Q3" s="136"/>
-      <c r="R3" s="137"/>
+      <c r="G3" s="134"/>
+      <c r="H3" s="135"/>
+      <c r="I3" s="139"/>
+      <c r="J3" s="140"/>
+      <c r="K3" s="140"/>
+      <c r="L3" s="140"/>
+      <c r="M3" s="140"/>
+      <c r="N3" s="140"/>
+      <c r="O3" s="140"/>
+      <c r="P3" s="140"/>
+      <c r="Q3" s="140"/>
+      <c r="R3" s="141"/>
     </row>
     <row r="4" spans="1:20" ht="36.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B4" s="121"/>
-      <c r="C4" s="122"/>
-      <c r="D4" s="125"/>
-      <c r="E4" s="125"/>
+      <c r="B4" s="125"/>
+      <c r="C4" s="126"/>
+      <c r="D4" s="129"/>
+      <c r="E4" s="129"/>
       <c r="F4" s="101" t="s">
         <v>140</v>
       </c>
@@ -3061,8 +3077,8 @@
       <c r="B5" s="100" t="s">
         <v>149</v>
       </c>
-      <c r="C5" s="169"/>
-      <c r="D5" s="167"/>
+      <c r="C5" s="119"/>
+      <c r="D5" s="117"/>
       <c r="E5" s="111"/>
       <c r="F5" s="112"/>
       <c r="G5" s="113"/>
@@ -3081,8 +3097,8 @@
     </row>
     <row r="6" spans="1:20" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B6" s="98"/>
-      <c r="C6" s="170"/>
-      <c r="D6" s="168"/>
+      <c r="C6" s="120"/>
+      <c r="D6" s="118"/>
       <c r="E6" s="107"/>
       <c r="F6" s="108"/>
       <c r="G6" s="109"/>
@@ -3121,7 +3137,7 @@
   </mergeCells>
   <phoneticPr fontId="1"/>
   <conditionalFormatting sqref="I5:R5">
-    <cfRule type="cellIs" dxfId="16" priority="1" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="17" priority="1" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3178,60 +3194,60 @@
       </c>
     </row>
     <row r="2" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B2" s="117" t="s">
+      <c r="B2" s="121" t="s">
         <v>53</v>
       </c>
-      <c r="C2" s="118"/>
-      <c r="D2" s="123" t="s">
+      <c r="C2" s="122"/>
+      <c r="D2" s="127" t="s">
         <v>151</v>
       </c>
-      <c r="E2" s="123" t="s">
+      <c r="E2" s="127" t="s">
         <v>54</v>
       </c>
-      <c r="F2" s="126" t="s">
+      <c r="F2" s="130" t="s">
         <v>55</v>
       </c>
-      <c r="G2" s="127"/>
-      <c r="H2" s="128"/>
-      <c r="I2" s="132" t="s">
+      <c r="G2" s="131"/>
+      <c r="H2" s="132"/>
+      <c r="I2" s="136" t="s">
         <v>56</v>
       </c>
-      <c r="J2" s="133"/>
-      <c r="K2" s="133"/>
-      <c r="L2" s="133"/>
-      <c r="M2" s="133"/>
-      <c r="N2" s="133"/>
-      <c r="O2" s="133"/>
-      <c r="P2" s="133"/>
-      <c r="Q2" s="133"/>
-      <c r="R2" s="134"/>
+      <c r="J2" s="137"/>
+      <c r="K2" s="137"/>
+      <c r="L2" s="137"/>
+      <c r="M2" s="137"/>
+      <c r="N2" s="137"/>
+      <c r="O2" s="137"/>
+      <c r="P2" s="137"/>
+      <c r="Q2" s="137"/>
+      <c r="R2" s="138"/>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.45">
-      <c r="B3" s="119"/>
-      <c r="C3" s="120"/>
-      <c r="D3" s="124"/>
-      <c r="E3" s="124"/>
-      <c r="F3" s="129" t="s">
+      <c r="B3" s="123"/>
+      <c r="C3" s="124"/>
+      <c r="D3" s="128"/>
+      <c r="E3" s="128"/>
+      <c r="F3" s="133" t="s">
         <v>96</v>
       </c>
-      <c r="G3" s="130"/>
-      <c r="H3" s="131"/>
-      <c r="I3" s="135"/>
-      <c r="J3" s="136"/>
-      <c r="K3" s="136"/>
-      <c r="L3" s="136"/>
-      <c r="M3" s="136"/>
-      <c r="N3" s="136"/>
-      <c r="O3" s="136"/>
-      <c r="P3" s="136"/>
-      <c r="Q3" s="136"/>
-      <c r="R3" s="137"/>
+      <c r="G3" s="134"/>
+      <c r="H3" s="135"/>
+      <c r="I3" s="139"/>
+      <c r="J3" s="140"/>
+      <c r="K3" s="140"/>
+      <c r="L3" s="140"/>
+      <c r="M3" s="140"/>
+      <c r="N3" s="140"/>
+      <c r="O3" s="140"/>
+      <c r="P3" s="140"/>
+      <c r="Q3" s="140"/>
+      <c r="R3" s="141"/>
     </row>
     <row r="4" spans="1:20" ht="36.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B4" s="121"/>
-      <c r="C4" s="122"/>
-      <c r="D4" s="125"/>
-      <c r="E4" s="125"/>
+      <c r="B4" s="125"/>
+      <c r="C4" s="126"/>
+      <c r="D4" s="129"/>
+      <c r="E4" s="129"/>
       <c r="F4" s="101" t="s">
         <v>140</v>
       </c>
@@ -3276,8 +3292,8 @@
       <c r="B5" s="100" t="s">
         <v>149</v>
       </c>
-      <c r="C5" s="169"/>
-      <c r="D5" s="167"/>
+      <c r="C5" s="119"/>
+      <c r="D5" s="117"/>
       <c r="E5" s="111"/>
       <c r="F5" s="112"/>
       <c r="G5" s="113"/>
@@ -3296,8 +3312,8 @@
     </row>
     <row r="6" spans="1:20" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B6" s="98"/>
-      <c r="C6" s="170"/>
-      <c r="D6" s="168"/>
+      <c r="C6" s="120"/>
+      <c r="D6" s="118"/>
       <c r="E6" s="107"/>
       <c r="F6" s="108"/>
       <c r="G6" s="109"/>
@@ -3336,7 +3352,7 @@
   </mergeCells>
   <phoneticPr fontId="1"/>
   <conditionalFormatting sqref="I5:R5">
-    <cfRule type="cellIs" dxfId="15" priority="1" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="16" priority="1" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3371,6 +3387,221 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26F3C566-D88E-4FE9-88CC-F9B5102F0878}">
+  <dimension ref="A1:T7"/>
+  <sheetFormatPr defaultColWidth="8.19921875" defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="2.59765625" style="93" customWidth="1"/>
+    <col min="2" max="2" width="2.796875" style="93" customWidth="1"/>
+    <col min="3" max="3" width="30.69921875" style="93" customWidth="1"/>
+    <col min="4" max="4" width="13.3984375" style="93" customWidth="1"/>
+    <col min="5" max="5" width="10.296875" style="93" customWidth="1"/>
+    <col min="6" max="7" width="10.69921875" style="94" customWidth="1"/>
+    <col min="8" max="8" width="10.69921875" style="93" customWidth="1"/>
+    <col min="9" max="9" width="14.19921875" style="93" bestFit="1" customWidth="1"/>
+    <col min="10" max="18" width="9.5" style="93" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="8.19921875" style="93"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:20" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A1" s="93" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B2" s="121" t="s">
+        <v>53</v>
+      </c>
+      <c r="C2" s="122"/>
+      <c r="D2" s="127" t="s">
+        <v>152</v>
+      </c>
+      <c r="E2" s="127" t="s">
+        <v>54</v>
+      </c>
+      <c r="F2" s="130" t="s">
+        <v>55</v>
+      </c>
+      <c r="G2" s="131"/>
+      <c r="H2" s="132"/>
+      <c r="I2" s="136" t="s">
+        <v>56</v>
+      </c>
+      <c r="J2" s="137"/>
+      <c r="K2" s="137"/>
+      <c r="L2" s="137"/>
+      <c r="M2" s="137"/>
+      <c r="N2" s="137"/>
+      <c r="O2" s="137"/>
+      <c r="P2" s="137"/>
+      <c r="Q2" s="137"/>
+      <c r="R2" s="138"/>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.45">
+      <c r="B3" s="123"/>
+      <c r="C3" s="124"/>
+      <c r="D3" s="128"/>
+      <c r="E3" s="128"/>
+      <c r="F3" s="133" t="s">
+        <v>96</v>
+      </c>
+      <c r="G3" s="134"/>
+      <c r="H3" s="135"/>
+      <c r="I3" s="139"/>
+      <c r="J3" s="140"/>
+      <c r="K3" s="140"/>
+      <c r="L3" s="140"/>
+      <c r="M3" s="140"/>
+      <c r="N3" s="140"/>
+      <c r="O3" s="140"/>
+      <c r="P3" s="140"/>
+      <c r="Q3" s="140"/>
+      <c r="R3" s="141"/>
+    </row>
+    <row r="4" spans="1:20" ht="36.6" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B4" s="125"/>
+      <c r="C4" s="126"/>
+      <c r="D4" s="129"/>
+      <c r="E4" s="129"/>
+      <c r="F4" s="101" t="s">
+        <v>140</v>
+      </c>
+      <c r="G4" s="102" t="s">
+        <v>147</v>
+      </c>
+      <c r="H4" s="103" t="s">
+        <v>57</v>
+      </c>
+      <c r="I4" s="104" t="s">
+        <v>58</v>
+      </c>
+      <c r="J4" s="105" t="s">
+        <v>59</v>
+      </c>
+      <c r="K4" s="105" t="s">
+        <v>60</v>
+      </c>
+      <c r="L4" s="105" t="s">
+        <v>139</v>
+      </c>
+      <c r="M4" s="105" t="s">
+        <v>61</v>
+      </c>
+      <c r="N4" s="105" t="s">
+        <v>62</v>
+      </c>
+      <c r="O4" s="105" t="s">
+        <v>63</v>
+      </c>
+      <c r="P4" s="105" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q4" s="105" t="s">
+        <v>65</v>
+      </c>
+      <c r="R4" s="106" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" ht="20.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B5" s="100" t="s">
+        <v>149</v>
+      </c>
+      <c r="C5" s="119"/>
+      <c r="D5" s="117"/>
+      <c r="E5" s="111"/>
+      <c r="F5" s="112"/>
+      <c r="G5" s="113"/>
+      <c r="H5" s="114"/>
+      <c r="I5" s="115"/>
+      <c r="J5" s="113"/>
+      <c r="K5" s="113"/>
+      <c r="L5" s="113"/>
+      <c r="M5" s="113"/>
+      <c r="N5" s="113"/>
+      <c r="O5" s="113"/>
+      <c r="P5" s="113"/>
+      <c r="Q5" s="113"/>
+      <c r="R5" s="116"/>
+      <c r="T5" s="95"/>
+    </row>
+    <row r="6" spans="1:20" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B6" s="98"/>
+      <c r="C6" s="120"/>
+      <c r="D6" s="118"/>
+      <c r="E6" s="107"/>
+      <c r="F6" s="108"/>
+      <c r="G6" s="109"/>
+      <c r="H6" s="110"/>
+      <c r="I6" s="99"/>
+      <c r="J6" s="96"/>
+      <c r="K6" s="96"/>
+      <c r="L6" s="96"/>
+      <c r="M6" s="96"/>
+      <c r="N6" s="96"/>
+      <c r="O6" s="96"/>
+      <c r="P6" s="96"/>
+      <c r="Q6" s="96"/>
+      <c r="R6" s="97"/>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.45">
+      <c r="I7" s="94"/>
+      <c r="J7" s="94"/>
+      <c r="K7" s="94"/>
+      <c r="L7" s="94"/>
+      <c r="M7" s="94"/>
+      <c r="N7" s="94"/>
+      <c r="O7" s="94"/>
+      <c r="P7" s="94"/>
+      <c r="Q7" s="94"/>
+      <c r="R7" s="94"/>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="B2:C4"/>
+    <mergeCell ref="D2:D4"/>
+    <mergeCell ref="E2:E4"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="I2:R3"/>
+    <mergeCell ref="F3:H3"/>
+  </mergeCells>
+  <phoneticPr fontId="1"/>
+  <conditionalFormatting sqref="I5:R5">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
+      <formula>3.4</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
+      <x14:conditionalFormattings>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="2" id="{F355311C-C976-4C8B-91DC-0E2F7B1F093C}">
+            <x14:iconSet iconSet="3Arrows" custom="1">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num" gte="0">
+                <xm:f>-0.25</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>0.25</xm:f>
+              </x14:cfvo>
+              <x14:cfIcon iconSet="3Arrows" iconId="0"/>
+              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
+              <x14:cfIcon iconSet="3Arrows" iconId="2"/>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>I6:R6</xm:sqref>
+        </x14:conditionalFormatting>
+      </x14:conditionalFormattings>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5C06947-9AD3-4764-A00F-59E09793C545}">
   <sheetPr>
     <tabColor theme="8" tint="0.39997558519241921"/>
@@ -3391,40 +3622,40 @@
   <sheetData>
     <row r="1" spans="2:29" ht="15.6" thickBot="1" x14ac:dyDescent="0.5"/>
     <row r="2" spans="2:29" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B2" s="141" t="s">
+      <c r="B2" s="142" t="s">
         <v>53</v>
       </c>
-      <c r="C2" s="142"/>
-      <c r="D2" s="150" t="s">
+      <c r="C2" s="143"/>
+      <c r="D2" s="154" t="s">
         <v>54</v>
       </c>
-      <c r="E2" s="158" t="s">
+      <c r="E2" s="162" t="s">
         <v>55</v>
       </c>
-      <c r="F2" s="159"/>
-      <c r="G2" s="160"/>
-      <c r="H2" s="152" t="s">
+      <c r="F2" s="163"/>
+      <c r="G2" s="164"/>
+      <c r="H2" s="156" t="s">
         <v>56</v>
       </c>
-      <c r="I2" s="153"/>
-      <c r="J2" s="153"/>
-      <c r="K2" s="153"/>
-      <c r="L2" s="153"/>
-      <c r="M2" s="153"/>
-      <c r="N2" s="153"/>
-      <c r="O2" s="153"/>
-      <c r="P2" s="153"/>
-      <c r="Q2" s="154"/>
+      <c r="I2" s="157"/>
+      <c r="J2" s="157"/>
+      <c r="K2" s="157"/>
+      <c r="L2" s="157"/>
+      <c r="M2" s="157"/>
+      <c r="N2" s="157"/>
+      <c r="O2" s="157"/>
+      <c r="P2" s="157"/>
+      <c r="Q2" s="158"/>
     </row>
     <row r="3" spans="2:29" x14ac:dyDescent="0.45">
-      <c r="B3" s="143"/>
-      <c r="C3" s="144"/>
-      <c r="D3" s="151"/>
-      <c r="E3" s="155" t="s">
+      <c r="B3" s="144"/>
+      <c r="C3" s="145"/>
+      <c r="D3" s="155"/>
+      <c r="E3" s="159" t="s">
         <v>96</v>
       </c>
-      <c r="F3" s="156"/>
-      <c r="G3" s="157"/>
+      <c r="F3" s="160"/>
+      <c r="G3" s="161"/>
       <c r="H3" s="22"/>
       <c r="I3" s="21"/>
       <c r="J3" s="21"/>
@@ -3437,9 +3668,9 @@
       <c r="Q3" s="20"/>
     </row>
     <row r="4" spans="2:29" ht="30.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B4" s="145"/>
-      <c r="C4" s="146"/>
-      <c r="D4" s="151"/>
+      <c r="B4" s="146"/>
+      <c r="C4" s="147"/>
+      <c r="D4" s="155"/>
       <c r="E4" s="85" t="s">
         <v>140</v>
       </c>
@@ -3481,10 +3712,10 @@
       </c>
     </row>
     <row r="5" spans="2:29" x14ac:dyDescent="0.45">
-      <c r="B5" s="147" t="s">
+      <c r="B5" s="151" t="s">
         <v>89</v>
       </c>
-      <c r="C5" s="138" t="s">
+      <c r="C5" s="148" t="s">
         <v>137</v>
       </c>
       <c r="D5" s="33" t="s">
@@ -3538,8 +3769,8 @@
       </c>
     </row>
     <row r="6" spans="2:29" x14ac:dyDescent="0.45">
-      <c r="B6" s="148"/>
-      <c r="C6" s="139"/>
+      <c r="B6" s="152"/>
+      <c r="C6" s="149"/>
       <c r="D6" s="26" t="s">
         <v>102</v>
       </c>
@@ -3592,8 +3823,8 @@
       <c r="AC6" s="19"/>
     </row>
     <row r="7" spans="2:29" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B7" s="148"/>
-      <c r="C7" s="140"/>
+      <c r="B7" s="152"/>
+      <c r="C7" s="150"/>
       <c r="D7" s="83" t="s">
         <v>70</v>
       </c>
@@ -3644,7 +3875,7 @@
       <c r="AC7" s="19"/>
     </row>
     <row r="8" spans="2:29" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B8" s="148"/>
+      <c r="B8" s="152"/>
       <c r="C8" s="36" t="s">
         <v>91</v>
       </c>
@@ -3698,8 +3929,8 @@
       </c>
     </row>
     <row r="9" spans="2:29" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B9" s="148"/>
-      <c r="C9" s="138" t="s">
+      <c r="B9" s="152"/>
+      <c r="C9" s="148" t="s">
         <v>101</v>
       </c>
       <c r="D9" s="33" t="s">
@@ -3750,8 +3981,8 @@
       </c>
     </row>
     <row r="10" spans="2:29" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B10" s="148"/>
-      <c r="C10" s="139"/>
+      <c r="B10" s="152"/>
+      <c r="C10" s="149"/>
       <c r="D10" s="26" t="s">
         <v>102</v>
       </c>
@@ -3802,8 +4033,8 @@
       <c r="AC10" s="19"/>
     </row>
     <row r="11" spans="2:29" ht="15.6" hidden="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B11" s="148"/>
-      <c r="C11" s="140"/>
+      <c r="B11" s="152"/>
+      <c r="C11" s="150"/>
       <c r="D11" s="34" t="s">
         <v>70</v>
       </c>
@@ -3854,7 +4085,7 @@
       <c r="AC11" s="19"/>
     </row>
     <row r="12" spans="2:29" ht="15.6" hidden="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B12" s="148"/>
+      <c r="B12" s="152"/>
       <c r="C12" s="36" t="s">
         <v>91</v>
       </c>
@@ -3908,8 +4139,8 @@
       </c>
     </row>
     <row r="13" spans="2:29" x14ac:dyDescent="0.45">
-      <c r="B13" s="148"/>
-      <c r="C13" s="138" t="s">
+      <c r="B13" s="152"/>
+      <c r="C13" s="148" t="s">
         <v>142</v>
       </c>
       <c r="D13" s="33" t="s">
@@ -3960,8 +4191,8 @@
       </c>
     </row>
     <row r="14" spans="2:29" x14ac:dyDescent="0.45">
-      <c r="B14" s="148"/>
-      <c r="C14" s="139"/>
+      <c r="B14" s="152"/>
+      <c r="C14" s="149"/>
       <c r="D14" s="26" t="s">
         <v>102</v>
       </c>
@@ -4012,8 +4243,8 @@
       <c r="AC14" s="19"/>
     </row>
     <row r="15" spans="2:29" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B15" s="148"/>
-      <c r="C15" s="140"/>
+      <c r="B15" s="152"/>
+      <c r="C15" s="150"/>
       <c r="D15" s="83" t="s">
         <v>70</v>
       </c>
@@ -4064,7 +4295,7 @@
       <c r="AC15" s="19"/>
     </row>
     <row r="16" spans="2:29" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B16" s="149"/>
+      <c r="B16" s="153"/>
       <c r="C16" s="32" t="s">
         <v>91</v>
       </c>
@@ -4130,40 +4361,40 @@
       <c r="Q17" s="12"/>
     </row>
     <row r="18" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B18" s="141" t="s">
+      <c r="B18" s="142" t="s">
         <v>53</v>
       </c>
-      <c r="C18" s="142"/>
-      <c r="D18" s="150" t="s">
+      <c r="C18" s="143"/>
+      <c r="D18" s="154" t="s">
         <v>54</v>
       </c>
-      <c r="E18" s="158" t="s">
+      <c r="E18" s="162" t="s">
         <v>55</v>
       </c>
-      <c r="F18" s="159"/>
-      <c r="G18" s="160"/>
-      <c r="H18" s="164" t="s">
+      <c r="F18" s="163"/>
+      <c r="G18" s="164"/>
+      <c r="H18" s="168" t="s">
         <v>56</v>
       </c>
-      <c r="I18" s="165"/>
-      <c r="J18" s="165"/>
-      <c r="K18" s="165"/>
-      <c r="L18" s="165"/>
-      <c r="M18" s="165"/>
-      <c r="N18" s="165"/>
-      <c r="O18" s="165"/>
-      <c r="P18" s="165"/>
-      <c r="Q18" s="166"/>
+      <c r="I18" s="169"/>
+      <c r="J18" s="169"/>
+      <c r="K18" s="169"/>
+      <c r="L18" s="169"/>
+      <c r="M18" s="169"/>
+      <c r="N18" s="169"/>
+      <c r="O18" s="169"/>
+      <c r="P18" s="169"/>
+      <c r="Q18" s="170"/>
     </row>
     <row r="19" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B19" s="143"/>
-      <c r="C19" s="144"/>
-      <c r="D19" s="151"/>
-      <c r="E19" s="155" t="s">
+      <c r="B19" s="144"/>
+      <c r="C19" s="145"/>
+      <c r="D19" s="155"/>
+      <c r="E19" s="159" t="s">
         <v>96</v>
       </c>
-      <c r="F19" s="156"/>
-      <c r="G19" s="157"/>
+      <c r="F19" s="160"/>
+      <c r="G19" s="161"/>
       <c r="H19" s="67"/>
       <c r="I19" s="68"/>
       <c r="J19" s="68"/>
@@ -4176,9 +4407,9 @@
       <c r="Q19" s="69"/>
     </row>
     <row r="20" spans="2:28" ht="30.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B20" s="145"/>
-      <c r="C20" s="146"/>
-      <c r="D20" s="151"/>
+      <c r="B20" s="146"/>
+      <c r="C20" s="147"/>
+      <c r="D20" s="155"/>
       <c r="E20" s="85" t="s">
         <v>140</v>
       </c>
@@ -4220,10 +4451,10 @@
       </c>
     </row>
     <row r="21" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B21" s="147" t="s">
+      <c r="B21" s="151" t="s">
         <v>100</v>
       </c>
-      <c r="C21" s="138" t="s">
+      <c r="C21" s="148" t="s">
         <v>99</v>
       </c>
       <c r="D21" s="33" t="s">
@@ -4283,8 +4514,8 @@
       </c>
     </row>
     <row r="22" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B22" s="148"/>
-      <c r="C22" s="139"/>
+      <c r="B22" s="152"/>
+      <c r="C22" s="149"/>
       <c r="D22" s="26" t="s">
         <v>102</v>
       </c>
@@ -4338,8 +4569,8 @@
       <c r="AB22" s="19"/>
     </row>
     <row r="23" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B23" s="148"/>
-      <c r="C23" s="140"/>
+      <c r="B23" s="152"/>
+      <c r="C23" s="150"/>
       <c r="D23" s="83" t="s">
         <v>70</v>
       </c>
@@ -4393,7 +4624,7 @@
       <c r="AB23" s="19"/>
     </row>
     <row r="24" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B24" s="148"/>
+      <c r="B24" s="152"/>
       <c r="C24" s="36" t="s">
         <v>91</v>
       </c>
@@ -4449,8 +4680,8 @@
       </c>
     </row>
     <row r="25" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B25" s="148"/>
-      <c r="C25" s="138" t="s">
+      <c r="B25" s="152"/>
+      <c r="C25" s="148" t="s">
         <v>98</v>
       </c>
       <c r="D25" s="33" t="s">
@@ -4510,8 +4741,8 @@
       </c>
     </row>
     <row r="26" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B26" s="148"/>
-      <c r="C26" s="139"/>
+      <c r="B26" s="152"/>
+      <c r="C26" s="149"/>
       <c r="D26" s="26" t="s">
         <v>102</v>
       </c>
@@ -4565,8 +4796,8 @@
       <c r="AB26" s="19"/>
     </row>
     <row r="27" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B27" s="148"/>
-      <c r="C27" s="140"/>
+      <c r="B27" s="152"/>
+      <c r="C27" s="150"/>
       <c r="D27" s="83" t="s">
         <v>70</v>
       </c>
@@ -4620,7 +4851,7 @@
       <c r="AB27" s="19"/>
     </row>
     <row r="28" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B28" s="148"/>
+      <c r="B28" s="152"/>
       <c r="C28" s="36" t="s">
         <v>91</v>
       </c>
@@ -4676,8 +4907,8 @@
       </c>
     </row>
     <row r="29" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B29" s="148"/>
-      <c r="C29" s="138" t="s">
+      <c r="B29" s="152"/>
+      <c r="C29" s="148" t="s">
         <v>97</v>
       </c>
       <c r="D29" s="33" t="s">
@@ -4737,8 +4968,8 @@
       </c>
     </row>
     <row r="30" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B30" s="148"/>
-      <c r="C30" s="139"/>
+      <c r="B30" s="152"/>
+      <c r="C30" s="149"/>
       <c r="D30" s="26" t="s">
         <v>102</v>
       </c>
@@ -4792,8 +5023,8 @@
       <c r="AB30" s="19"/>
     </row>
     <row r="31" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B31" s="148"/>
-      <c r="C31" s="140"/>
+      <c r="B31" s="152"/>
+      <c r="C31" s="150"/>
       <c r="D31" s="83" t="s">
         <v>70</v>
       </c>
@@ -4847,7 +5078,7 @@
       <c r="AB31" s="19"/>
     </row>
     <row r="32" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B32" s="149"/>
+      <c r="B32" s="153"/>
       <c r="C32" s="32" t="s">
         <v>91</v>
       </c>
@@ -4915,40 +5146,40 @@
       <c r="Q33" s="12"/>
     </row>
     <row r="34" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B34" s="141" t="s">
+      <c r="B34" s="142" t="s">
         <v>53</v>
       </c>
-      <c r="C34" s="142"/>
-      <c r="D34" s="150" t="s">
+      <c r="C34" s="143"/>
+      <c r="D34" s="154" t="s">
         <v>54</v>
       </c>
-      <c r="E34" s="158" t="s">
+      <c r="E34" s="162" t="s">
         <v>55</v>
       </c>
-      <c r="F34" s="159"/>
-      <c r="G34" s="160"/>
-      <c r="H34" s="164" t="s">
+      <c r="F34" s="163"/>
+      <c r="G34" s="164"/>
+      <c r="H34" s="168" t="s">
         <v>56</v>
       </c>
-      <c r="I34" s="165"/>
-      <c r="J34" s="165"/>
-      <c r="K34" s="165"/>
-      <c r="L34" s="165"/>
-      <c r="M34" s="165"/>
-      <c r="N34" s="165"/>
-      <c r="O34" s="165"/>
-      <c r="P34" s="165"/>
-      <c r="Q34" s="166"/>
+      <c r="I34" s="169"/>
+      <c r="J34" s="169"/>
+      <c r="K34" s="169"/>
+      <c r="L34" s="169"/>
+      <c r="M34" s="169"/>
+      <c r="N34" s="169"/>
+      <c r="O34" s="169"/>
+      <c r="P34" s="169"/>
+      <c r="Q34" s="170"/>
     </row>
     <row r="35" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B35" s="143"/>
-      <c r="C35" s="144"/>
-      <c r="D35" s="151"/>
-      <c r="E35" s="155" t="s">
+      <c r="B35" s="144"/>
+      <c r="C35" s="145"/>
+      <c r="D35" s="155"/>
+      <c r="E35" s="159" t="s">
         <v>96</v>
       </c>
-      <c r="F35" s="156"/>
-      <c r="G35" s="157"/>
+      <c r="F35" s="160"/>
+      <c r="G35" s="161"/>
       <c r="H35" s="67"/>
       <c r="I35" s="68"/>
       <c r="J35" s="68"/>
@@ -4961,9 +5192,9 @@
       <c r="Q35" s="69"/>
     </row>
     <row r="36" spans="2:28" ht="30.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B36" s="145"/>
-      <c r="C36" s="146"/>
-      <c r="D36" s="151"/>
+      <c r="B36" s="146"/>
+      <c r="C36" s="147"/>
+      <c r="D36" s="155"/>
       <c r="E36" s="85" t="s">
         <v>140</v>
       </c>
@@ -5005,10 +5236,10 @@
       </c>
     </row>
     <row r="37" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B37" s="147" t="s">
+      <c r="B37" s="151" t="s">
         <v>95</v>
       </c>
-      <c r="C37" s="138" t="s">
+      <c r="C37" s="148" t="s">
         <v>94</v>
       </c>
       <c r="D37" s="33" t="s">
@@ -5068,8 +5299,8 @@
       </c>
     </row>
     <row r="38" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B38" s="148"/>
-      <c r="C38" s="139"/>
+      <c r="B38" s="152"/>
+      <c r="C38" s="149"/>
       <c r="D38" s="26" t="s">
         <v>102</v>
       </c>
@@ -5123,8 +5354,8 @@
       <c r="AB38" s="19"/>
     </row>
     <row r="39" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B39" s="148"/>
-      <c r="C39" s="140"/>
+      <c r="B39" s="152"/>
+      <c r="C39" s="150"/>
       <c r="D39" s="83" t="s">
         <v>70</v>
       </c>
@@ -5178,7 +5409,7 @@
       <c r="AB39" s="19"/>
     </row>
     <row r="40" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B40" s="148"/>
+      <c r="B40" s="152"/>
       <c r="C40" s="36" t="s">
         <v>91</v>
       </c>
@@ -5234,8 +5465,8 @@
       </c>
     </row>
     <row r="41" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B41" s="148"/>
-      <c r="C41" s="138" t="s">
+      <c r="B41" s="152"/>
+      <c r="C41" s="148" t="s">
         <v>79</v>
       </c>
       <c r="D41" s="33" t="s">
@@ -5295,8 +5526,8 @@
       </c>
     </row>
     <row r="42" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B42" s="148"/>
-      <c r="C42" s="139"/>
+      <c r="B42" s="152"/>
+      <c r="C42" s="149"/>
       <c r="D42" s="26" t="s">
         <v>102</v>
       </c>
@@ -5350,8 +5581,8 @@
       <c r="AB42" s="19"/>
     </row>
     <row r="43" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B43" s="148"/>
-      <c r="C43" s="140"/>
+      <c r="B43" s="152"/>
+      <c r="C43" s="150"/>
       <c r="D43" s="83" t="s">
         <v>70</v>
       </c>
@@ -5405,7 +5636,7 @@
       <c r="AB43" s="19"/>
     </row>
     <row r="44" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B44" s="148"/>
+      <c r="B44" s="152"/>
       <c r="C44" s="36" t="s">
         <v>91</v>
       </c>
@@ -5461,8 +5692,8 @@
       </c>
     </row>
     <row r="45" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B45" s="148"/>
-      <c r="C45" s="138" t="s">
+      <c r="B45" s="152"/>
+      <c r="C45" s="148" t="s">
         <v>93</v>
       </c>
       <c r="D45" s="33" t="s">
@@ -5522,8 +5753,8 @@
       </c>
     </row>
     <row r="46" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B46" s="148"/>
-      <c r="C46" s="139"/>
+      <c r="B46" s="152"/>
+      <c r="C46" s="149"/>
       <c r="D46" s="26" t="s">
         <v>102</v>
       </c>
@@ -5577,8 +5808,8 @@
       <c r="AB46" s="19"/>
     </row>
     <row r="47" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B47" s="148"/>
-      <c r="C47" s="140"/>
+      <c r="B47" s="152"/>
+      <c r="C47" s="150"/>
       <c r="D47" s="83" t="s">
         <v>70</v>
       </c>
@@ -5632,7 +5863,7 @@
       <c r="AB47" s="19"/>
     </row>
     <row r="48" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B48" s="148"/>
+      <c r="B48" s="152"/>
       <c r="C48" s="36" t="s">
         <v>91</v>
       </c>
@@ -5688,14 +5919,14 @@
       </c>
     </row>
     <row r="49" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B49" s="148"/>
-      <c r="C49" s="138" t="s">
+      <c r="B49" s="152"/>
+      <c r="C49" s="148" t="s">
         <v>92</v>
       </c>
       <c r="D49" s="33" t="s">
         <v>143</v>
       </c>
-      <c r="E49" s="161"/>
+      <c r="E49" s="165"/>
       <c r="F49" s="87"/>
       <c r="G49" s="31"/>
       <c r="H49" s="64" t="e">
@@ -5740,12 +5971,12 @@
       </c>
     </row>
     <row r="50" spans="2:28" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B50" s="148"/>
-      <c r="C50" s="139"/>
+      <c r="B50" s="152"/>
+      <c r="C50" s="149"/>
       <c r="D50" s="26" t="s">
         <v>102</v>
       </c>
-      <c r="E50" s="162"/>
+      <c r="E50" s="166"/>
       <c r="F50" s="88"/>
       <c r="G50" s="28"/>
       <c r="H50" s="73">
@@ -5791,12 +6022,12 @@
       <c r="AB50" s="19"/>
     </row>
     <row r="51" spans="2:28" ht="18.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B51" s="148"/>
-      <c r="C51" s="140"/>
+      <c r="B51" s="152"/>
+      <c r="C51" s="150"/>
       <c r="D51" s="83" t="s">
         <v>70</v>
       </c>
-      <c r="E51" s="163"/>
+      <c r="E51" s="167"/>
       <c r="F51" s="89"/>
       <c r="G51" s="54"/>
       <c r="H51" s="75">
@@ -5842,7 +6073,7 @@
       <c r="AB51" s="19"/>
     </row>
     <row r="52" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B52" s="149"/>
+      <c r="B52" s="153"/>
       <c r="C52" s="32" t="s">
         <v>91</v>
       </c>
@@ -6294,16 +6525,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B2:C4"/>
-    <mergeCell ref="C9:C11"/>
-    <mergeCell ref="C13:C15"/>
-    <mergeCell ref="C21:C23"/>
-    <mergeCell ref="B18:C20"/>
-    <mergeCell ref="B5:B16"/>
-    <mergeCell ref="B21:B32"/>
-    <mergeCell ref="C5:C7"/>
-    <mergeCell ref="C29:C31"/>
-    <mergeCell ref="C25:C27"/>
+    <mergeCell ref="C41:C43"/>
+    <mergeCell ref="C45:C47"/>
+    <mergeCell ref="C49:C51"/>
+    <mergeCell ref="B34:C36"/>
+    <mergeCell ref="B37:B52"/>
+    <mergeCell ref="C37:C39"/>
     <mergeCell ref="D2:D4"/>
     <mergeCell ref="H2:Q2"/>
     <mergeCell ref="E3:G3"/>
@@ -6317,86 +6544,90 @@
     <mergeCell ref="D18:D20"/>
     <mergeCell ref="E18:G18"/>
     <mergeCell ref="E19:G19"/>
-    <mergeCell ref="C41:C43"/>
-    <mergeCell ref="C45:C47"/>
-    <mergeCell ref="C49:C51"/>
-    <mergeCell ref="B34:C36"/>
-    <mergeCell ref="B37:B52"/>
-    <mergeCell ref="C37:C39"/>
+    <mergeCell ref="B2:C4"/>
+    <mergeCell ref="C9:C11"/>
+    <mergeCell ref="C13:C15"/>
+    <mergeCell ref="C21:C23"/>
+    <mergeCell ref="B18:C20"/>
+    <mergeCell ref="B5:B16"/>
+    <mergeCell ref="B21:B32"/>
+    <mergeCell ref="C5:C7"/>
+    <mergeCell ref="C29:C31"/>
+    <mergeCell ref="C25:C27"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <conditionalFormatting sqref="H5:Q7">
-    <cfRule type="cellIs" dxfId="14" priority="11" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="15" priority="11" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H9:Q9">
-    <cfRule type="cellIs" dxfId="13" priority="10" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="14" priority="10" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H10:Q10">
-    <cfRule type="cellIs" dxfId="12" priority="12" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="13" priority="12" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H11:Q11">
-    <cfRule type="cellIs" dxfId="11" priority="14" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="12" priority="14" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H13:Q13">
-    <cfRule type="cellIs" dxfId="10" priority="9" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="11" priority="9" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H14:Q14 H22:Q22 H26:Q26 H30:Q30 H38:Q38 H42:Q42 H46:Q46 H50:Q50">
-    <cfRule type="cellIs" dxfId="9" priority="16" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="10" priority="16" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H15:Q15 H23:Q23 H31:Q31 H39:Q39 H43:Q43">
-    <cfRule type="cellIs" dxfId="8" priority="18" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="9" priority="18" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H21:Q21">
-    <cfRule type="cellIs" dxfId="7" priority="8" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="8" priority="8" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H25:Q25">
-    <cfRule type="cellIs" dxfId="6" priority="7" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="7" priority="7" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H27:Q27 H47:Q47 H51:Q51">
-    <cfRule type="cellIs" dxfId="5" priority="15" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="6" priority="15" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H29:Q29">
-    <cfRule type="cellIs" dxfId="4" priority="6" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="5" priority="6" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H37:Q37">
-    <cfRule type="cellIs" dxfId="3" priority="5" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="4" priority="5" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H41:Q41">
-    <cfRule type="cellIs" dxfId="2" priority="4" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="3" priority="4" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H45:Q45">
-    <cfRule type="cellIs" dxfId="1" priority="3" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H49:Q49">
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6430,7 +6661,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <tabColor theme="4" tint="0.39997558519241921"/>

--- a/tool/track-aggregator/template/年度比較結果.xlsx
+++ b/tool/track-aggregator/template/年度比較結果.xlsx
@@ -5,27 +5,23 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ishid\Desktop\project_management\tool\track-aggregator\template\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="c:\Users\ishid\Desktop\project_management\tool\track-aggregator\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B70F2EC-B76F-4FFB-9F18-86FA2EEF6F2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0FA76F8-A0BB-45B6-8A44-ECB99FEEBB15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="760" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="760" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="経年比較" sheetId="31" r:id="rId1"/>
-    <sheet name="経年比較-会社別" sheetId="32" r:id="rId2"/>
-    <sheet name="経年比較-ランク別" sheetId="33" r:id="rId3"/>
-    <sheet name="経年比較-クラス別" sheetId="34" r:id="rId4"/>
-    <sheet name="経年比較（前年同じFMT）" sheetId="22" state="hidden" r:id="rId5"/>
-    <sheet name="ビジネス基礎（Day5)" sheetId="13" state="hidden" r:id="rId6"/>
+    <sheet name="経年比較-属性別" sheetId="32" r:id="rId2"/>
+    <sheet name="経年比較（前年同じFMT）" sheetId="22" state="hidden" r:id="rId3"/>
+    <sheet name="ビジネス基礎（Day5)" sheetId="13" state="hidden" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">経年比較!$B$2:$Q$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'経年比較（前年同じFMT）'!$B$2:$Q$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'経年比較-クラス別'!$B$2:$R$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'経年比較-ランク別'!$B$2:$R$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'経年比較-会社別'!$B$2:$R$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'経年比較（前年同じFMT）'!$B$2:$Q$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'経年比較-属性別'!$B$2:$R$6</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="151">
   <si>
     <t>目的達成</t>
     <rPh sb="0" eb="2">
@@ -879,19 +875,8 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>会社名</t>
-    <rPh sb="0" eb="3">
-      <t>カイシャメイ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>ランク</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>クラス</t>
-    <phoneticPr fontId="3"/>
+    <t>{属性名}</t>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
@@ -2191,6 +2176,15 @@
     <xf numFmtId="0" fontId="10" fillId="8" borderId="54" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="27" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="30" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="32" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2208,15 +2202,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="16" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="27" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="30" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="32" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="15" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
@@ -2285,17 +2270,7 @@
     <cellStyle name="標準" xfId="0" builtinId="0"/>
     <cellStyle name="標準 2" xfId="2" xr:uid="{35DECEAB-A874-4A31-B6F5-75B712B64A43}"/>
   </cellStyles>
-  <dxfs count="19">
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="17">
     <dxf>
       <font>
         <color rgb="FFFF0000"/>
@@ -2417,16 +2392,6 @@
       <font>
         <color rgb="FFFF0000"/>
       </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <font>
@@ -2922,7 +2887,7 @@
   </mergeCells>
   <phoneticPr fontId="1"/>
   <conditionalFormatting sqref="H5:Q5">
-    <cfRule type="cellIs" dxfId="18" priority="1" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="16" priority="1" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3137,7 +3102,7 @@
   </mergeCells>
   <phoneticPr fontId="1"/>
   <conditionalFormatting sqref="I5:R5">
-    <cfRule type="cellIs" dxfId="17" priority="1" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="15" priority="1" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3172,436 +3137,6 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D0D5B12-79D9-42EC-8039-D2A663034F34}">
-  <dimension ref="A1:T7"/>
-  <sheetFormatPr defaultColWidth="8.19921875" defaultRowHeight="18" x14ac:dyDescent="0.45"/>
-  <cols>
-    <col min="1" max="1" width="2.59765625" style="93" customWidth="1"/>
-    <col min="2" max="2" width="2.796875" style="93" customWidth="1"/>
-    <col min="3" max="3" width="30.69921875" style="93" customWidth="1"/>
-    <col min="4" max="4" width="13.3984375" style="93" customWidth="1"/>
-    <col min="5" max="5" width="10.296875" style="93" customWidth="1"/>
-    <col min="6" max="7" width="10.69921875" style="94" customWidth="1"/>
-    <col min="8" max="8" width="10.69921875" style="93" customWidth="1"/>
-    <col min="9" max="9" width="14.19921875" style="93" bestFit="1" customWidth="1"/>
-    <col min="10" max="18" width="9.5" style="93" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="8.19921875" style="93"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:20" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="93" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="2" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B2" s="121" t="s">
-        <v>53</v>
-      </c>
-      <c r="C2" s="122"/>
-      <c r="D2" s="127" t="s">
-        <v>151</v>
-      </c>
-      <c r="E2" s="127" t="s">
-        <v>54</v>
-      </c>
-      <c r="F2" s="130" t="s">
-        <v>55</v>
-      </c>
-      <c r="G2" s="131"/>
-      <c r="H2" s="132"/>
-      <c r="I2" s="136" t="s">
-        <v>56</v>
-      </c>
-      <c r="J2" s="137"/>
-      <c r="K2" s="137"/>
-      <c r="L2" s="137"/>
-      <c r="M2" s="137"/>
-      <c r="N2" s="137"/>
-      <c r="O2" s="137"/>
-      <c r="P2" s="137"/>
-      <c r="Q2" s="137"/>
-      <c r="R2" s="138"/>
-    </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.45">
-      <c r="B3" s="123"/>
-      <c r="C3" s="124"/>
-      <c r="D3" s="128"/>
-      <c r="E3" s="128"/>
-      <c r="F3" s="133" t="s">
-        <v>96</v>
-      </c>
-      <c r="G3" s="134"/>
-      <c r="H3" s="135"/>
-      <c r="I3" s="139"/>
-      <c r="J3" s="140"/>
-      <c r="K3" s="140"/>
-      <c r="L3" s="140"/>
-      <c r="M3" s="140"/>
-      <c r="N3" s="140"/>
-      <c r="O3" s="140"/>
-      <c r="P3" s="140"/>
-      <c r="Q3" s="140"/>
-      <c r="R3" s="141"/>
-    </row>
-    <row r="4" spans="1:20" ht="36.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B4" s="125"/>
-      <c r="C4" s="126"/>
-      <c r="D4" s="129"/>
-      <c r="E4" s="129"/>
-      <c r="F4" s="101" t="s">
-        <v>140</v>
-      </c>
-      <c r="G4" s="102" t="s">
-        <v>147</v>
-      </c>
-      <c r="H4" s="103" t="s">
-        <v>57</v>
-      </c>
-      <c r="I4" s="104" t="s">
-        <v>58</v>
-      </c>
-      <c r="J4" s="105" t="s">
-        <v>59</v>
-      </c>
-      <c r="K4" s="105" t="s">
-        <v>60</v>
-      </c>
-      <c r="L4" s="105" t="s">
-        <v>139</v>
-      </c>
-      <c r="M4" s="105" t="s">
-        <v>61</v>
-      </c>
-      <c r="N4" s="105" t="s">
-        <v>62</v>
-      </c>
-      <c r="O4" s="105" t="s">
-        <v>63</v>
-      </c>
-      <c r="P4" s="105" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q4" s="105" t="s">
-        <v>65</v>
-      </c>
-      <c r="R4" s="106" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="5" spans="1:20" ht="20.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B5" s="100" t="s">
-        <v>149</v>
-      </c>
-      <c r="C5" s="119"/>
-      <c r="D5" s="117"/>
-      <c r="E5" s="111"/>
-      <c r="F5" s="112"/>
-      <c r="G5" s="113"/>
-      <c r="H5" s="114"/>
-      <c r="I5" s="115"/>
-      <c r="J5" s="113"/>
-      <c r="K5" s="113"/>
-      <c r="L5" s="113"/>
-      <c r="M5" s="113"/>
-      <c r="N5" s="113"/>
-      <c r="O5" s="113"/>
-      <c r="P5" s="113"/>
-      <c r="Q5" s="113"/>
-      <c r="R5" s="116"/>
-      <c r="T5" s="95"/>
-    </row>
-    <row r="6" spans="1:20" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B6" s="98"/>
-      <c r="C6" s="120"/>
-      <c r="D6" s="118"/>
-      <c r="E6" s="107"/>
-      <c r="F6" s="108"/>
-      <c r="G6" s="109"/>
-      <c r="H6" s="110"/>
-      <c r="I6" s="99"/>
-      <c r="J6" s="96"/>
-      <c r="K6" s="96"/>
-      <c r="L6" s="96"/>
-      <c r="M6" s="96"/>
-      <c r="N6" s="96"/>
-      <c r="O6" s="96"/>
-      <c r="P6" s="96"/>
-      <c r="Q6" s="96"/>
-      <c r="R6" s="97"/>
-    </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.45">
-      <c r="I7" s="94"/>
-      <c r="J7" s="94"/>
-      <c r="K7" s="94"/>
-      <c r="L7" s="94"/>
-      <c r="M7" s="94"/>
-      <c r="N7" s="94"/>
-      <c r="O7" s="94"/>
-      <c r="P7" s="94"/>
-      <c r="Q7" s="94"/>
-      <c r="R7" s="94"/>
-    </row>
-  </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="B2:C4"/>
-    <mergeCell ref="E2:E4"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="I2:R3"/>
-    <mergeCell ref="F3:H3"/>
-    <mergeCell ref="D2:D4"/>
-  </mergeCells>
-  <phoneticPr fontId="1"/>
-  <conditionalFormatting sqref="I5:R5">
-    <cfRule type="cellIs" dxfId="16" priority="1" operator="lessThanOrEqual">
-      <formula>3.4</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
-      <x14:conditionalFormattings>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="2" id="{E3CFEB59-5C73-49AB-BE2A-0F88EC39808A}">
-            <x14:iconSet iconSet="3Arrows" custom="1">
-              <x14:cfvo type="percent">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num" gte="0">
-                <xm:f>-0.25</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>0.25</xm:f>
-              </x14:cfvo>
-              <x14:cfIcon iconSet="3Arrows" iconId="0"/>
-              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
-              <x14:cfIcon iconSet="3Arrows" iconId="2"/>
-            </x14:iconSet>
-          </x14:cfRule>
-          <xm:sqref>I6:R6</xm:sqref>
-        </x14:conditionalFormatting>
-      </x14:conditionalFormattings>
-    </ext>
-  </extLst>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26F3C566-D88E-4FE9-88CC-F9B5102F0878}">
-  <dimension ref="A1:T7"/>
-  <sheetFormatPr defaultColWidth="8.19921875" defaultRowHeight="18" x14ac:dyDescent="0.45"/>
-  <cols>
-    <col min="1" max="1" width="2.59765625" style="93" customWidth="1"/>
-    <col min="2" max="2" width="2.796875" style="93" customWidth="1"/>
-    <col min="3" max="3" width="30.69921875" style="93" customWidth="1"/>
-    <col min="4" max="4" width="13.3984375" style="93" customWidth="1"/>
-    <col min="5" max="5" width="10.296875" style="93" customWidth="1"/>
-    <col min="6" max="7" width="10.69921875" style="94" customWidth="1"/>
-    <col min="8" max="8" width="10.69921875" style="93" customWidth="1"/>
-    <col min="9" max="9" width="14.19921875" style="93" bestFit="1" customWidth="1"/>
-    <col min="10" max="18" width="9.5" style="93" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="8.19921875" style="93"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:20" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="93" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="2" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B2" s="121" t="s">
-        <v>53</v>
-      </c>
-      <c r="C2" s="122"/>
-      <c r="D2" s="127" t="s">
-        <v>152</v>
-      </c>
-      <c r="E2" s="127" t="s">
-        <v>54</v>
-      </c>
-      <c r="F2" s="130" t="s">
-        <v>55</v>
-      </c>
-      <c r="G2" s="131"/>
-      <c r="H2" s="132"/>
-      <c r="I2" s="136" t="s">
-        <v>56</v>
-      </c>
-      <c r="J2" s="137"/>
-      <c r="K2" s="137"/>
-      <c r="L2" s="137"/>
-      <c r="M2" s="137"/>
-      <c r="N2" s="137"/>
-      <c r="O2" s="137"/>
-      <c r="P2" s="137"/>
-      <c r="Q2" s="137"/>
-      <c r="R2" s="138"/>
-    </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.45">
-      <c r="B3" s="123"/>
-      <c r="C3" s="124"/>
-      <c r="D3" s="128"/>
-      <c r="E3" s="128"/>
-      <c r="F3" s="133" t="s">
-        <v>96</v>
-      </c>
-      <c r="G3" s="134"/>
-      <c r="H3" s="135"/>
-      <c r="I3" s="139"/>
-      <c r="J3" s="140"/>
-      <c r="K3" s="140"/>
-      <c r="L3" s="140"/>
-      <c r="M3" s="140"/>
-      <c r="N3" s="140"/>
-      <c r="O3" s="140"/>
-      <c r="P3" s="140"/>
-      <c r="Q3" s="140"/>
-      <c r="R3" s="141"/>
-    </row>
-    <row r="4" spans="1:20" ht="36.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B4" s="125"/>
-      <c r="C4" s="126"/>
-      <c r="D4" s="129"/>
-      <c r="E4" s="129"/>
-      <c r="F4" s="101" t="s">
-        <v>140</v>
-      </c>
-      <c r="G4" s="102" t="s">
-        <v>147</v>
-      </c>
-      <c r="H4" s="103" t="s">
-        <v>57</v>
-      </c>
-      <c r="I4" s="104" t="s">
-        <v>58</v>
-      </c>
-      <c r="J4" s="105" t="s">
-        <v>59</v>
-      </c>
-      <c r="K4" s="105" t="s">
-        <v>60</v>
-      </c>
-      <c r="L4" s="105" t="s">
-        <v>139</v>
-      </c>
-      <c r="M4" s="105" t="s">
-        <v>61</v>
-      </c>
-      <c r="N4" s="105" t="s">
-        <v>62</v>
-      </c>
-      <c r="O4" s="105" t="s">
-        <v>63</v>
-      </c>
-      <c r="P4" s="105" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q4" s="105" t="s">
-        <v>65</v>
-      </c>
-      <c r="R4" s="106" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="5" spans="1:20" ht="20.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B5" s="100" t="s">
-        <v>149</v>
-      </c>
-      <c r="C5" s="119"/>
-      <c r="D5" s="117"/>
-      <c r="E5" s="111"/>
-      <c r="F5" s="112"/>
-      <c r="G5" s="113"/>
-      <c r="H5" s="114"/>
-      <c r="I5" s="115"/>
-      <c r="J5" s="113"/>
-      <c r="K5" s="113"/>
-      <c r="L5" s="113"/>
-      <c r="M5" s="113"/>
-      <c r="N5" s="113"/>
-      <c r="O5" s="113"/>
-      <c r="P5" s="113"/>
-      <c r="Q5" s="113"/>
-      <c r="R5" s="116"/>
-      <c r="T5" s="95"/>
-    </row>
-    <row r="6" spans="1:20" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B6" s="98"/>
-      <c r="C6" s="120"/>
-      <c r="D6" s="118"/>
-      <c r="E6" s="107"/>
-      <c r="F6" s="108"/>
-      <c r="G6" s="109"/>
-      <c r="H6" s="110"/>
-      <c r="I6" s="99"/>
-      <c r="J6" s="96"/>
-      <c r="K6" s="96"/>
-      <c r="L6" s="96"/>
-      <c r="M6" s="96"/>
-      <c r="N6" s="96"/>
-      <c r="O6" s="96"/>
-      <c r="P6" s="96"/>
-      <c r="Q6" s="96"/>
-      <c r="R6" s="97"/>
-    </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.45">
-      <c r="I7" s="94"/>
-      <c r="J7" s="94"/>
-      <c r="K7" s="94"/>
-      <c r="L7" s="94"/>
-      <c r="M7" s="94"/>
-      <c r="N7" s="94"/>
-      <c r="O7" s="94"/>
-      <c r="P7" s="94"/>
-      <c r="Q7" s="94"/>
-      <c r="R7" s="94"/>
-    </row>
-  </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="B2:C4"/>
-    <mergeCell ref="D2:D4"/>
-    <mergeCell ref="E2:E4"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="I2:R3"/>
-    <mergeCell ref="F3:H3"/>
-  </mergeCells>
-  <phoneticPr fontId="1"/>
-  <conditionalFormatting sqref="I5:R5">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
-      <formula>3.4</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
-      <x14:conditionalFormattings>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="2" id="{F355311C-C976-4C8B-91DC-0E2F7B1F093C}">
-            <x14:iconSet iconSet="3Arrows" custom="1">
-              <x14:cfvo type="percent">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num" gte="0">
-                <xm:f>-0.25</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>0.25</xm:f>
-              </x14:cfvo>
-              <x14:cfIcon iconSet="3Arrows" iconId="0"/>
-              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
-              <x14:cfIcon iconSet="3Arrows" iconId="2"/>
-            </x14:iconSet>
-          </x14:cfRule>
-          <xm:sqref>I6:R6</xm:sqref>
-        </x14:conditionalFormatting>
-      </x14:conditionalFormattings>
-    </ext>
-  </extLst>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5C06947-9AD3-4764-A00F-59E09793C545}">
   <sheetPr>
     <tabColor theme="8" tint="0.39997558519241921"/>
@@ -3622,10 +3157,10 @@
   <sheetData>
     <row r="1" spans="2:29" ht="15.6" thickBot="1" x14ac:dyDescent="0.5"/>
     <row r="2" spans="2:29" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B2" s="142" t="s">
+      <c r="B2" s="145" t="s">
         <v>53</v>
       </c>
-      <c r="C2" s="143"/>
+      <c r="C2" s="146"/>
       <c r="D2" s="154" t="s">
         <v>54</v>
       </c>
@@ -3648,8 +3183,8 @@
       <c r="Q2" s="158"/>
     </row>
     <row r="3" spans="2:29" x14ac:dyDescent="0.45">
-      <c r="B3" s="144"/>
-      <c r="C3" s="145"/>
+      <c r="B3" s="147"/>
+      <c r="C3" s="148"/>
       <c r="D3" s="155"/>
       <c r="E3" s="159" t="s">
         <v>96</v>
@@ -3668,8 +3203,8 @@
       <c r="Q3" s="20"/>
     </row>
     <row r="4" spans="2:29" ht="30.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B4" s="146"/>
-      <c r="C4" s="147"/>
+      <c r="B4" s="149"/>
+      <c r="C4" s="150"/>
       <c r="D4" s="155"/>
       <c r="E4" s="85" t="s">
         <v>140</v>
@@ -3715,7 +3250,7 @@
       <c r="B5" s="151" t="s">
         <v>89</v>
       </c>
-      <c r="C5" s="148" t="s">
+      <c r="C5" s="142" t="s">
         <v>137</v>
       </c>
       <c r="D5" s="33" t="s">
@@ -3770,7 +3305,7 @@
     </row>
     <row r="6" spans="2:29" x14ac:dyDescent="0.45">
       <c r="B6" s="152"/>
-      <c r="C6" s="149"/>
+      <c r="C6" s="143"/>
       <c r="D6" s="26" t="s">
         <v>102</v>
       </c>
@@ -3824,7 +3359,7 @@
     </row>
     <row r="7" spans="2:29" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B7" s="152"/>
-      <c r="C7" s="150"/>
+      <c r="C7" s="144"/>
       <c r="D7" s="83" t="s">
         <v>70</v>
       </c>
@@ -3930,7 +3465,7 @@
     </row>
     <row r="9" spans="2:29" hidden="1" x14ac:dyDescent="0.45">
       <c r="B9" s="152"/>
-      <c r="C9" s="148" t="s">
+      <c r="C9" s="142" t="s">
         <v>101</v>
       </c>
       <c r="D9" s="33" t="s">
@@ -3982,7 +3517,7 @@
     </row>
     <row r="10" spans="2:29" hidden="1" x14ac:dyDescent="0.45">
       <c r="B10" s="152"/>
-      <c r="C10" s="149"/>
+      <c r="C10" s="143"/>
       <c r="D10" s="26" t="s">
         <v>102</v>
       </c>
@@ -4034,7 +3569,7 @@
     </row>
     <row r="11" spans="2:29" ht="15.6" hidden="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B11" s="152"/>
-      <c r="C11" s="150"/>
+      <c r="C11" s="144"/>
       <c r="D11" s="34" t="s">
         <v>70</v>
       </c>
@@ -4140,7 +3675,7 @@
     </row>
     <row r="13" spans="2:29" x14ac:dyDescent="0.45">
       <c r="B13" s="152"/>
-      <c r="C13" s="148" t="s">
+      <c r="C13" s="142" t="s">
         <v>142</v>
       </c>
       <c r="D13" s="33" t="s">
@@ -4192,7 +3727,7 @@
     </row>
     <row r="14" spans="2:29" x14ac:dyDescent="0.45">
       <c r="B14" s="152"/>
-      <c r="C14" s="149"/>
+      <c r="C14" s="143"/>
       <c r="D14" s="26" t="s">
         <v>102</v>
       </c>
@@ -4244,7 +3779,7 @@
     </row>
     <row r="15" spans="2:29" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B15" s="152"/>
-      <c r="C15" s="150"/>
+      <c r="C15" s="144"/>
       <c r="D15" s="83" t="s">
         <v>70</v>
       </c>
@@ -4361,10 +3896,10 @@
       <c r="Q17" s="12"/>
     </row>
     <row r="18" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B18" s="142" t="s">
+      <c r="B18" s="145" t="s">
         <v>53</v>
       </c>
-      <c r="C18" s="143"/>
+      <c r="C18" s="146"/>
       <c r="D18" s="154" t="s">
         <v>54</v>
       </c>
@@ -4387,8 +3922,8 @@
       <c r="Q18" s="170"/>
     </row>
     <row r="19" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B19" s="144"/>
-      <c r="C19" s="145"/>
+      <c r="B19" s="147"/>
+      <c r="C19" s="148"/>
       <c r="D19" s="155"/>
       <c r="E19" s="159" t="s">
         <v>96</v>
@@ -4407,8 +3942,8 @@
       <c r="Q19" s="69"/>
     </row>
     <row r="20" spans="2:28" ht="30.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B20" s="146"/>
-      <c r="C20" s="147"/>
+      <c r="B20" s="149"/>
+      <c r="C20" s="150"/>
       <c r="D20" s="155"/>
       <c r="E20" s="85" t="s">
         <v>140</v>
@@ -4454,7 +3989,7 @@
       <c r="B21" s="151" t="s">
         <v>100</v>
       </c>
-      <c r="C21" s="148" t="s">
+      <c r="C21" s="142" t="s">
         <v>99</v>
       </c>
       <c r="D21" s="33" t="s">
@@ -4515,7 +4050,7 @@
     </row>
     <row r="22" spans="2:28" x14ac:dyDescent="0.45">
       <c r="B22" s="152"/>
-      <c r="C22" s="149"/>
+      <c r="C22" s="143"/>
       <c r="D22" s="26" t="s">
         <v>102</v>
       </c>
@@ -4570,7 +4105,7 @@
     </row>
     <row r="23" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B23" s="152"/>
-      <c r="C23" s="150"/>
+      <c r="C23" s="144"/>
       <c r="D23" s="83" t="s">
         <v>70</v>
       </c>
@@ -4681,7 +4216,7 @@
     </row>
     <row r="25" spans="2:28" x14ac:dyDescent="0.45">
       <c r="B25" s="152"/>
-      <c r="C25" s="148" t="s">
+      <c r="C25" s="142" t="s">
         <v>98</v>
       </c>
       <c r="D25" s="33" t="s">
@@ -4742,7 +4277,7 @@
     </row>
     <row r="26" spans="2:28" x14ac:dyDescent="0.45">
       <c r="B26" s="152"/>
-      <c r="C26" s="149"/>
+      <c r="C26" s="143"/>
       <c r="D26" s="26" t="s">
         <v>102</v>
       </c>
@@ -4797,7 +4332,7 @@
     </row>
     <row r="27" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B27" s="152"/>
-      <c r="C27" s="150"/>
+      <c r="C27" s="144"/>
       <c r="D27" s="83" t="s">
         <v>70</v>
       </c>
@@ -4908,7 +4443,7 @@
     </row>
     <row r="29" spans="2:28" x14ac:dyDescent="0.45">
       <c r="B29" s="152"/>
-      <c r="C29" s="148" t="s">
+      <c r="C29" s="142" t="s">
         <v>97</v>
       </c>
       <c r="D29" s="33" t="s">
@@ -4969,7 +4504,7 @@
     </row>
     <row r="30" spans="2:28" x14ac:dyDescent="0.45">
       <c r="B30" s="152"/>
-      <c r="C30" s="149"/>
+      <c r="C30" s="143"/>
       <c r="D30" s="26" t="s">
         <v>102</v>
       </c>
@@ -5024,7 +4559,7 @@
     </row>
     <row r="31" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B31" s="152"/>
-      <c r="C31" s="150"/>
+      <c r="C31" s="144"/>
       <c r="D31" s="83" t="s">
         <v>70</v>
       </c>
@@ -5146,10 +4681,10 @@
       <c r="Q33" s="12"/>
     </row>
     <row r="34" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B34" s="142" t="s">
+      <c r="B34" s="145" t="s">
         <v>53</v>
       </c>
-      <c r="C34" s="143"/>
+      <c r="C34" s="146"/>
       <c r="D34" s="154" t="s">
         <v>54</v>
       </c>
@@ -5172,8 +4707,8 @@
       <c r="Q34" s="170"/>
     </row>
     <row r="35" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B35" s="144"/>
-      <c r="C35" s="145"/>
+      <c r="B35" s="147"/>
+      <c r="C35" s="148"/>
       <c r="D35" s="155"/>
       <c r="E35" s="159" t="s">
         <v>96</v>
@@ -5192,8 +4727,8 @@
       <c r="Q35" s="69"/>
     </row>
     <row r="36" spans="2:28" ht="30.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B36" s="146"/>
-      <c r="C36" s="147"/>
+      <c r="B36" s="149"/>
+      <c r="C36" s="150"/>
       <c r="D36" s="155"/>
       <c r="E36" s="85" t="s">
         <v>140</v>
@@ -5239,7 +4774,7 @@
       <c r="B37" s="151" t="s">
         <v>95</v>
       </c>
-      <c r="C37" s="148" t="s">
+      <c r="C37" s="142" t="s">
         <v>94</v>
       </c>
       <c r="D37" s="33" t="s">
@@ -5300,7 +4835,7 @@
     </row>
     <row r="38" spans="2:28" x14ac:dyDescent="0.45">
       <c r="B38" s="152"/>
-      <c r="C38" s="149"/>
+      <c r="C38" s="143"/>
       <c r="D38" s="26" t="s">
         <v>102</v>
       </c>
@@ -5355,7 +4890,7 @@
     </row>
     <row r="39" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B39" s="152"/>
-      <c r="C39" s="150"/>
+      <c r="C39" s="144"/>
       <c r="D39" s="83" t="s">
         <v>70</v>
       </c>
@@ -5466,7 +5001,7 @@
     </row>
     <row r="41" spans="2:28" x14ac:dyDescent="0.45">
       <c r="B41" s="152"/>
-      <c r="C41" s="148" t="s">
+      <c r="C41" s="142" t="s">
         <v>79</v>
       </c>
       <c r="D41" s="33" t="s">
@@ -5527,7 +5062,7 @@
     </row>
     <row r="42" spans="2:28" x14ac:dyDescent="0.45">
       <c r="B42" s="152"/>
-      <c r="C42" s="149"/>
+      <c r="C42" s="143"/>
       <c r="D42" s="26" t="s">
         <v>102</v>
       </c>
@@ -5582,7 +5117,7 @@
     </row>
     <row r="43" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B43" s="152"/>
-      <c r="C43" s="150"/>
+      <c r="C43" s="144"/>
       <c r="D43" s="83" t="s">
         <v>70</v>
       </c>
@@ -5693,7 +5228,7 @@
     </row>
     <row r="45" spans="2:28" x14ac:dyDescent="0.45">
       <c r="B45" s="152"/>
-      <c r="C45" s="148" t="s">
+      <c r="C45" s="142" t="s">
         <v>93</v>
       </c>
       <c r="D45" s="33" t="s">
@@ -5754,7 +5289,7 @@
     </row>
     <row r="46" spans="2:28" x14ac:dyDescent="0.45">
       <c r="B46" s="152"/>
-      <c r="C46" s="149"/>
+      <c r="C46" s="143"/>
       <c r="D46" s="26" t="s">
         <v>102</v>
       </c>
@@ -5809,7 +5344,7 @@
     </row>
     <row r="47" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B47" s="152"/>
-      <c r="C47" s="150"/>
+      <c r="C47" s="144"/>
       <c r="D47" s="83" t="s">
         <v>70</v>
       </c>
@@ -5920,7 +5455,7 @@
     </row>
     <row r="49" spans="2:28" x14ac:dyDescent="0.45">
       <c r="B49" s="152"/>
-      <c r="C49" s="148" t="s">
+      <c r="C49" s="142" t="s">
         <v>92</v>
       </c>
       <c r="D49" s="33" t="s">
@@ -5972,7 +5507,7 @@
     </row>
     <row r="50" spans="2:28" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B50" s="152"/>
-      <c r="C50" s="149"/>
+      <c r="C50" s="143"/>
       <c r="D50" s="26" t="s">
         <v>102</v>
       </c>
@@ -6023,7 +5558,7 @@
     </row>
     <row r="51" spans="2:28" ht="18.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B51" s="152"/>
-      <c r="C51" s="150"/>
+      <c r="C51" s="144"/>
       <c r="D51" s="83" t="s">
         <v>70</v>
       </c>
@@ -6525,12 +6060,16 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="C41:C43"/>
-    <mergeCell ref="C45:C47"/>
-    <mergeCell ref="C49:C51"/>
-    <mergeCell ref="B34:C36"/>
-    <mergeCell ref="B37:B52"/>
-    <mergeCell ref="C37:C39"/>
+    <mergeCell ref="B2:C4"/>
+    <mergeCell ref="C9:C11"/>
+    <mergeCell ref="C13:C15"/>
+    <mergeCell ref="C21:C23"/>
+    <mergeCell ref="B18:C20"/>
+    <mergeCell ref="B5:B16"/>
+    <mergeCell ref="B21:B32"/>
+    <mergeCell ref="C5:C7"/>
+    <mergeCell ref="C29:C31"/>
+    <mergeCell ref="C25:C27"/>
     <mergeCell ref="D2:D4"/>
     <mergeCell ref="H2:Q2"/>
     <mergeCell ref="E3:G3"/>
@@ -6544,90 +6083,86 @@
     <mergeCell ref="D18:D20"/>
     <mergeCell ref="E18:G18"/>
     <mergeCell ref="E19:G19"/>
-    <mergeCell ref="B2:C4"/>
-    <mergeCell ref="C9:C11"/>
-    <mergeCell ref="C13:C15"/>
-    <mergeCell ref="C21:C23"/>
-    <mergeCell ref="B18:C20"/>
-    <mergeCell ref="B5:B16"/>
-    <mergeCell ref="B21:B32"/>
-    <mergeCell ref="C5:C7"/>
-    <mergeCell ref="C29:C31"/>
-    <mergeCell ref="C25:C27"/>
+    <mergeCell ref="C41:C43"/>
+    <mergeCell ref="C45:C47"/>
+    <mergeCell ref="C49:C51"/>
+    <mergeCell ref="B34:C36"/>
+    <mergeCell ref="B37:B52"/>
+    <mergeCell ref="C37:C39"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <conditionalFormatting sqref="H5:Q7">
-    <cfRule type="cellIs" dxfId="15" priority="11" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="14" priority="11" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H9:Q9">
-    <cfRule type="cellIs" dxfId="14" priority="10" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="13" priority="10" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H10:Q10">
-    <cfRule type="cellIs" dxfId="13" priority="12" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="12" priority="12" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H11:Q11">
-    <cfRule type="cellIs" dxfId="12" priority="14" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="11" priority="14" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H13:Q13">
-    <cfRule type="cellIs" dxfId="11" priority="9" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="10" priority="9" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H14:Q14 H22:Q22 H26:Q26 H30:Q30 H38:Q38 H42:Q42 H46:Q46 H50:Q50">
-    <cfRule type="cellIs" dxfId="10" priority="16" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="9" priority="16" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H15:Q15 H23:Q23 H31:Q31 H39:Q39 H43:Q43">
-    <cfRule type="cellIs" dxfId="9" priority="18" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="8" priority="18" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H21:Q21">
-    <cfRule type="cellIs" dxfId="8" priority="8" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="7" priority="8" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H25:Q25">
-    <cfRule type="cellIs" dxfId="7" priority="7" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="6" priority="7" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H27:Q27 H47:Q47 H51:Q51">
-    <cfRule type="cellIs" dxfId="6" priority="15" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="5" priority="15" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H29:Q29">
-    <cfRule type="cellIs" dxfId="5" priority="6" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="4" priority="6" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H37:Q37">
-    <cfRule type="cellIs" dxfId="4" priority="5" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="3" priority="5" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H41:Q41">
-    <cfRule type="cellIs" dxfId="3" priority="4" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="2" priority="4" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H45:Q45">
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="1" priority="3" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H49:Q49">
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6661,7 +6196,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <tabColor theme="4" tint="0.39997558519241921"/>

--- a/tool/track-aggregator/template/年度比較結果.xlsx
+++ b/tool/track-aggregator/template/年度比較結果.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="c:\Users\ishid\Desktop\project_management\tool\track-aggregator\template\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ishid\Desktop\project_management\tool\track-aggregator\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0FA76F8-A0BB-45B6-8A44-ECB99FEEBB15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3A77A9F-8C36-4528-AE17-73AB6C519DB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="760" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2176,6 +2176,24 @@
     <xf numFmtId="0" fontId="10" fillId="8" borderId="54" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="16" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="27" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2184,24 +2202,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="32" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="16" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="15" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
@@ -2722,12 +2722,11 @@
   <cols>
     <col min="1" max="1" width="2.59765625" style="93" customWidth="1"/>
     <col min="2" max="2" width="2.796875" style="93" customWidth="1"/>
-    <col min="3" max="3" width="30.69921875" style="93" customWidth="1"/>
+    <col min="3" max="3" width="40.69921875" style="93" customWidth="1"/>
     <col min="4" max="4" width="10.296875" style="93" customWidth="1"/>
     <col min="5" max="6" width="10.69921875" style="94" customWidth="1"/>
     <col min="7" max="7" width="10.69921875" style="93" customWidth="1"/>
-    <col min="8" max="8" width="14.19921875" style="93" bestFit="1" customWidth="1"/>
-    <col min="9" max="17" width="9.5" style="93" bestFit="1" customWidth="1"/>
+    <col min="8" max="17" width="12.69921875" style="93" customWidth="1"/>
     <col min="18" max="16384" width="8.19921875" style="93"/>
   </cols>
   <sheetData>
@@ -2928,13 +2927,11 @@
   <cols>
     <col min="1" max="1" width="2.59765625" style="93" customWidth="1"/>
     <col min="2" max="2" width="2.796875" style="93" customWidth="1"/>
-    <col min="3" max="3" width="30.69921875" style="93" customWidth="1"/>
-    <col min="4" max="4" width="40.69921875" style="93" customWidth="1"/>
+    <col min="3" max="4" width="40.69921875" style="93" customWidth="1"/>
     <col min="5" max="5" width="10.296875" style="93" customWidth="1"/>
     <col min="6" max="7" width="10.69921875" style="94" customWidth="1"/>
     <col min="8" max="8" width="10.69921875" style="93" customWidth="1"/>
-    <col min="9" max="9" width="14.19921875" style="93" bestFit="1" customWidth="1"/>
-    <col min="10" max="18" width="9.5" style="93" bestFit="1" customWidth="1"/>
+    <col min="9" max="18" width="12.69921875" style="93" customWidth="1"/>
     <col min="19" max="16384" width="8.19921875" style="93"/>
   </cols>
   <sheetData>
@@ -3157,10 +3154,10 @@
   <sheetData>
     <row r="1" spans="2:29" ht="15.6" thickBot="1" x14ac:dyDescent="0.5"/>
     <row r="2" spans="2:29" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B2" s="145" t="s">
+      <c r="B2" s="142" t="s">
         <v>53</v>
       </c>
-      <c r="C2" s="146"/>
+      <c r="C2" s="143"/>
       <c r="D2" s="154" t="s">
         <v>54</v>
       </c>
@@ -3183,8 +3180,8 @@
       <c r="Q2" s="158"/>
     </row>
     <row r="3" spans="2:29" x14ac:dyDescent="0.45">
-      <c r="B3" s="147"/>
-      <c r="C3" s="148"/>
+      <c r="B3" s="144"/>
+      <c r="C3" s="145"/>
       <c r="D3" s="155"/>
       <c r="E3" s="159" t="s">
         <v>96</v>
@@ -3203,8 +3200,8 @@
       <c r="Q3" s="20"/>
     </row>
     <row r="4" spans="2:29" ht="30.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B4" s="149"/>
-      <c r="C4" s="150"/>
+      <c r="B4" s="146"/>
+      <c r="C4" s="147"/>
       <c r="D4" s="155"/>
       <c r="E4" s="85" t="s">
         <v>140</v>
@@ -3250,7 +3247,7 @@
       <c r="B5" s="151" t="s">
         <v>89</v>
       </c>
-      <c r="C5" s="142" t="s">
+      <c r="C5" s="148" t="s">
         <v>137</v>
       </c>
       <c r="D5" s="33" t="s">
@@ -3305,7 +3302,7 @@
     </row>
     <row r="6" spans="2:29" x14ac:dyDescent="0.45">
       <c r="B6" s="152"/>
-      <c r="C6" s="143"/>
+      <c r="C6" s="149"/>
       <c r="D6" s="26" t="s">
         <v>102</v>
       </c>
@@ -3359,7 +3356,7 @@
     </row>
     <row r="7" spans="2:29" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B7" s="152"/>
-      <c r="C7" s="144"/>
+      <c r="C7" s="150"/>
       <c r="D7" s="83" t="s">
         <v>70</v>
       </c>
@@ -3465,7 +3462,7 @@
     </row>
     <row r="9" spans="2:29" hidden="1" x14ac:dyDescent="0.45">
       <c r="B9" s="152"/>
-      <c r="C9" s="142" t="s">
+      <c r="C9" s="148" t="s">
         <v>101</v>
       </c>
       <c r="D9" s="33" t="s">
@@ -3517,7 +3514,7 @@
     </row>
     <row r="10" spans="2:29" hidden="1" x14ac:dyDescent="0.45">
       <c r="B10" s="152"/>
-      <c r="C10" s="143"/>
+      <c r="C10" s="149"/>
       <c r="D10" s="26" t="s">
         <v>102</v>
       </c>
@@ -3569,7 +3566,7 @@
     </row>
     <row r="11" spans="2:29" ht="15.6" hidden="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B11" s="152"/>
-      <c r="C11" s="144"/>
+      <c r="C11" s="150"/>
       <c r="D11" s="34" t="s">
         <v>70</v>
       </c>
@@ -3675,7 +3672,7 @@
     </row>
     <row r="13" spans="2:29" x14ac:dyDescent="0.45">
       <c r="B13" s="152"/>
-      <c r="C13" s="142" t="s">
+      <c r="C13" s="148" t="s">
         <v>142</v>
       </c>
       <c r="D13" s="33" t="s">
@@ -3727,7 +3724,7 @@
     </row>
     <row r="14" spans="2:29" x14ac:dyDescent="0.45">
       <c r="B14" s="152"/>
-      <c r="C14" s="143"/>
+      <c r="C14" s="149"/>
       <c r="D14" s="26" t="s">
         <v>102</v>
       </c>
@@ -3779,7 +3776,7 @@
     </row>
     <row r="15" spans="2:29" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B15" s="152"/>
-      <c r="C15" s="144"/>
+      <c r="C15" s="150"/>
       <c r="D15" s="83" t="s">
         <v>70</v>
       </c>
@@ -3896,10 +3893,10 @@
       <c r="Q17" s="12"/>
     </row>
     <row r="18" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B18" s="145" t="s">
+      <c r="B18" s="142" t="s">
         <v>53</v>
       </c>
-      <c r="C18" s="146"/>
+      <c r="C18" s="143"/>
       <c r="D18" s="154" t="s">
         <v>54</v>
       </c>
@@ -3922,8 +3919,8 @@
       <c r="Q18" s="170"/>
     </row>
     <row r="19" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B19" s="147"/>
-      <c r="C19" s="148"/>
+      <c r="B19" s="144"/>
+      <c r="C19" s="145"/>
       <c r="D19" s="155"/>
       <c r="E19" s="159" t="s">
         <v>96</v>
@@ -3942,8 +3939,8 @@
       <c r="Q19" s="69"/>
     </row>
     <row r="20" spans="2:28" ht="30.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B20" s="149"/>
-      <c r="C20" s="150"/>
+      <c r="B20" s="146"/>
+      <c r="C20" s="147"/>
       <c r="D20" s="155"/>
       <c r="E20" s="85" t="s">
         <v>140</v>
@@ -3989,7 +3986,7 @@
       <c r="B21" s="151" t="s">
         <v>100</v>
       </c>
-      <c r="C21" s="142" t="s">
+      <c r="C21" s="148" t="s">
         <v>99</v>
       </c>
       <c r="D21" s="33" t="s">
@@ -4050,7 +4047,7 @@
     </row>
     <row r="22" spans="2:28" x14ac:dyDescent="0.45">
       <c r="B22" s="152"/>
-      <c r="C22" s="143"/>
+      <c r="C22" s="149"/>
       <c r="D22" s="26" t="s">
         <v>102</v>
       </c>
@@ -4105,7 +4102,7 @@
     </row>
     <row r="23" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B23" s="152"/>
-      <c r="C23" s="144"/>
+      <c r="C23" s="150"/>
       <c r="D23" s="83" t="s">
         <v>70</v>
       </c>
@@ -4216,7 +4213,7 @@
     </row>
     <row r="25" spans="2:28" x14ac:dyDescent="0.45">
       <c r="B25" s="152"/>
-      <c r="C25" s="142" t="s">
+      <c r="C25" s="148" t="s">
         <v>98</v>
       </c>
       <c r="D25" s="33" t="s">
@@ -4277,7 +4274,7 @@
     </row>
     <row r="26" spans="2:28" x14ac:dyDescent="0.45">
       <c r="B26" s="152"/>
-      <c r="C26" s="143"/>
+      <c r="C26" s="149"/>
       <c r="D26" s="26" t="s">
         <v>102</v>
       </c>
@@ -4332,7 +4329,7 @@
     </row>
     <row r="27" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B27" s="152"/>
-      <c r="C27" s="144"/>
+      <c r="C27" s="150"/>
       <c r="D27" s="83" t="s">
         <v>70</v>
       </c>
@@ -4443,7 +4440,7 @@
     </row>
     <row r="29" spans="2:28" x14ac:dyDescent="0.45">
       <c r="B29" s="152"/>
-      <c r="C29" s="142" t="s">
+      <c r="C29" s="148" t="s">
         <v>97</v>
       </c>
       <c r="D29" s="33" t="s">
@@ -4504,7 +4501,7 @@
     </row>
     <row r="30" spans="2:28" x14ac:dyDescent="0.45">
       <c r="B30" s="152"/>
-      <c r="C30" s="143"/>
+      <c r="C30" s="149"/>
       <c r="D30" s="26" t="s">
         <v>102</v>
       </c>
@@ -4559,7 +4556,7 @@
     </row>
     <row r="31" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B31" s="152"/>
-      <c r="C31" s="144"/>
+      <c r="C31" s="150"/>
       <c r="D31" s="83" t="s">
         <v>70</v>
       </c>
@@ -4681,10 +4678,10 @@
       <c r="Q33" s="12"/>
     </row>
     <row r="34" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B34" s="145" t="s">
+      <c r="B34" s="142" t="s">
         <v>53</v>
       </c>
-      <c r="C34" s="146"/>
+      <c r="C34" s="143"/>
       <c r="D34" s="154" t="s">
         <v>54</v>
       </c>
@@ -4707,8 +4704,8 @@
       <c r="Q34" s="170"/>
     </row>
     <row r="35" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B35" s="147"/>
-      <c r="C35" s="148"/>
+      <c r="B35" s="144"/>
+      <c r="C35" s="145"/>
       <c r="D35" s="155"/>
       <c r="E35" s="159" t="s">
         <v>96</v>
@@ -4727,8 +4724,8 @@
       <c r="Q35" s="69"/>
     </row>
     <row r="36" spans="2:28" ht="30.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B36" s="149"/>
-      <c r="C36" s="150"/>
+      <c r="B36" s="146"/>
+      <c r="C36" s="147"/>
       <c r="D36" s="155"/>
       <c r="E36" s="85" t="s">
         <v>140</v>
@@ -4774,7 +4771,7 @@
       <c r="B37" s="151" t="s">
         <v>95</v>
       </c>
-      <c r="C37" s="142" t="s">
+      <c r="C37" s="148" t="s">
         <v>94</v>
       </c>
       <c r="D37" s="33" t="s">
@@ -4835,7 +4832,7 @@
     </row>
     <row r="38" spans="2:28" x14ac:dyDescent="0.45">
       <c r="B38" s="152"/>
-      <c r="C38" s="143"/>
+      <c r="C38" s="149"/>
       <c r="D38" s="26" t="s">
         <v>102</v>
       </c>
@@ -4890,7 +4887,7 @@
     </row>
     <row r="39" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B39" s="152"/>
-      <c r="C39" s="144"/>
+      <c r="C39" s="150"/>
       <c r="D39" s="83" t="s">
         <v>70</v>
       </c>
@@ -5001,7 +4998,7 @@
     </row>
     <row r="41" spans="2:28" x14ac:dyDescent="0.45">
       <c r="B41" s="152"/>
-      <c r="C41" s="142" t="s">
+      <c r="C41" s="148" t="s">
         <v>79</v>
       </c>
       <c r="D41" s="33" t="s">
@@ -5062,7 +5059,7 @@
     </row>
     <row r="42" spans="2:28" x14ac:dyDescent="0.45">
       <c r="B42" s="152"/>
-      <c r="C42" s="143"/>
+      <c r="C42" s="149"/>
       <c r="D42" s="26" t="s">
         <v>102</v>
       </c>
@@ -5117,7 +5114,7 @@
     </row>
     <row r="43" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B43" s="152"/>
-      <c r="C43" s="144"/>
+      <c r="C43" s="150"/>
       <c r="D43" s="83" t="s">
         <v>70</v>
       </c>
@@ -5228,7 +5225,7 @@
     </row>
     <row r="45" spans="2:28" x14ac:dyDescent="0.45">
       <c r="B45" s="152"/>
-      <c r="C45" s="142" t="s">
+      <c r="C45" s="148" t="s">
         <v>93</v>
       </c>
       <c r="D45" s="33" t="s">
@@ -5289,7 +5286,7 @@
     </row>
     <row r="46" spans="2:28" x14ac:dyDescent="0.45">
       <c r="B46" s="152"/>
-      <c r="C46" s="143"/>
+      <c r="C46" s="149"/>
       <c r="D46" s="26" t="s">
         <v>102</v>
       </c>
@@ -5344,7 +5341,7 @@
     </row>
     <row r="47" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B47" s="152"/>
-      <c r="C47" s="144"/>
+      <c r="C47" s="150"/>
       <c r="D47" s="83" t="s">
         <v>70</v>
       </c>
@@ -5455,7 +5452,7 @@
     </row>
     <row r="49" spans="2:28" x14ac:dyDescent="0.45">
       <c r="B49" s="152"/>
-      <c r="C49" s="142" t="s">
+      <c r="C49" s="148" t="s">
         <v>92</v>
       </c>
       <c r="D49" s="33" t="s">
@@ -5507,7 +5504,7 @@
     </row>
     <row r="50" spans="2:28" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B50" s="152"/>
-      <c r="C50" s="143"/>
+      <c r="C50" s="149"/>
       <c r="D50" s="26" t="s">
         <v>102</v>
       </c>
@@ -5558,7 +5555,7 @@
     </row>
     <row r="51" spans="2:28" ht="18.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B51" s="152"/>
-      <c r="C51" s="144"/>
+      <c r="C51" s="150"/>
       <c r="D51" s="83" t="s">
         <v>70</v>
       </c>
@@ -6060,16 +6057,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B2:C4"/>
-    <mergeCell ref="C9:C11"/>
-    <mergeCell ref="C13:C15"/>
-    <mergeCell ref="C21:C23"/>
-    <mergeCell ref="B18:C20"/>
-    <mergeCell ref="B5:B16"/>
-    <mergeCell ref="B21:B32"/>
-    <mergeCell ref="C5:C7"/>
-    <mergeCell ref="C29:C31"/>
-    <mergeCell ref="C25:C27"/>
+    <mergeCell ref="C41:C43"/>
+    <mergeCell ref="C45:C47"/>
+    <mergeCell ref="C49:C51"/>
+    <mergeCell ref="B34:C36"/>
+    <mergeCell ref="B37:B52"/>
+    <mergeCell ref="C37:C39"/>
     <mergeCell ref="D2:D4"/>
     <mergeCell ref="H2:Q2"/>
     <mergeCell ref="E3:G3"/>
@@ -6083,12 +6076,16 @@
     <mergeCell ref="D18:D20"/>
     <mergeCell ref="E18:G18"/>
     <mergeCell ref="E19:G19"/>
-    <mergeCell ref="C41:C43"/>
-    <mergeCell ref="C45:C47"/>
-    <mergeCell ref="C49:C51"/>
-    <mergeCell ref="B34:C36"/>
-    <mergeCell ref="B37:B52"/>
-    <mergeCell ref="C37:C39"/>
+    <mergeCell ref="B2:C4"/>
+    <mergeCell ref="C9:C11"/>
+    <mergeCell ref="C13:C15"/>
+    <mergeCell ref="C21:C23"/>
+    <mergeCell ref="B18:C20"/>
+    <mergeCell ref="B5:B16"/>
+    <mergeCell ref="B21:B32"/>
+    <mergeCell ref="C5:C7"/>
+    <mergeCell ref="C29:C31"/>
+    <mergeCell ref="C25:C27"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <conditionalFormatting sqref="H5:Q7">
